--- a/data/theme_strength_latest.xlsx
+++ b/data/theme_strength_latest.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'汇总'!$A$4:$T$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明细'!$A$3:$T$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明细'!$A$3:$T$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -218,9 +218,6 @@
     <xf numFmtId="2" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -234,6 +231,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -636,7 +636,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>截至 2026-10-26  2026-10-26 12:02｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：东财概念板块日线</t>
+          <t>截至 2026-10-26  2026-10-26 14:21｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：东财概念板块日线</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>1</v>
@@ -1007,7 +1007,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>2</v>
@@ -1055,7 +1055,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>快递概念</t>
+          <t>乳业</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="12" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>3</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>3</v>
@@ -1103,7 +1103,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>电子竞技</t>
+          <t>快递概念</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="L11" s="10" t="n">
         <v>4</v>
@@ -1151,7 +1151,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>租售同权</t>
+          <t>免税概念</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>5</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>5</v>
@@ -1851,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T103"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
@@ -2052,13 +2052,13 @@
         <v>7.79</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>5.14</v>
+        <v>3.19</v>
       </c>
       <c r="P4" s="16" t="n">
-        <v>5.31</v>
+        <v>3.66</v>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="R4" s="16" t="n">
         <v>-23.93</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="T4" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.76%</t>
+          <t>SPD概念 +2.72%</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         <v>12.62</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>13.92</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="P5" s="16" t="n">
-        <v>2.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R5" s="16" t="n">
         <v>-44.79</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="T5" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.76%</t>
+          <t>SPD概念 +2.72%</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
@@ -2203,112 +2203,112 @@
         </is>
       </c>
       <c r="L6" s="16" t="n">
-        <v>16.77</v>
+        <v>16.84</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>3.71</v>
+        <v>4.14</v>
       </c>
       <c r="N6" s="19" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1.22</v>
+        <v>0.91</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>2.69</v>
+        <v>2.07</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="R6" s="16" t="n">
-        <v>-6</v>
+        <v>-5.61</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>13.01</v>
+        <v>13.48</v>
       </c>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.76%</t>
+          <t>SPD概念 +2.72%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SPD概念</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>SPD概念</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>603108</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>润达医疗</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>医疗服务</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>内贸流通、华为概念、精准诊断、SPD概念、互联网医疗、病原体防治、体外诊断概念、创新医疗服务、医疗器械概念、幽门螺杆菌概念、AI制药（医疗）</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="M7" s="19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N7" s="19" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="O7" s="16" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="P7" s="16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q7" s="16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R7" s="16" t="n">
-        <v>-48.45</v>
-      </c>
-      <c r="S7" s="16" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>SPD概念 +2.76%</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>601808</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>中海油服</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>油服工程</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰、天然气、油气设服、油气资源、海工装备、行业龙头、资源开采概念</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P7" s="20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q7" s="20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R7" s="20" t="n">
+        <v>-33.63</v>
+      </c>
+      <c r="S7" s="20" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰 +2.06%</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>2.14</v>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>2.06</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -2340,55 +2340,55 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>001219</t>
+        <v>2</v>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>002278</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>青岛食品</t>
+          <t>神开股份</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>休闲食品</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>乳业、婴童概念、电商概念、网红经济、调味品概念</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q8" s="21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R8" s="21" t="n">
-        <v>-12.36</v>
-      </c>
-      <c r="S8" s="21" t="n">
-        <v>18.85</v>
+          <t>可燃冰、无人机、氢能源、碳纤维、页岩气、低空经济、商业航天、油气设服、油气资源、海工装备、长江三角、中俄贸易概念</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O8" s="20" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="P8" s="20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q8" s="20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R8" s="20" t="n">
+        <v>-49.75</v>
+      </c>
+      <c r="S8" s="20" t="n">
+        <v>10.72</v>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>乳业 +2.14%</t>
+          <t>可燃冰 +2.06%</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -2408,11 +2408,11 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>2.14</v>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>2.06</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
@@ -2420,55 +2420,55 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>001318</t>
+        <v>3</v>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>000039</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>中集集团</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>饮料乳品</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>乳业、味蕾经济、婴童概念</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M9" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" s="24" t="n">
-        <v>-11.94</v>
-      </c>
-      <c r="O9" s="21" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="P9" s="21" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Q9" s="21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R9" s="21" t="n">
-        <v>-30.22</v>
-      </c>
-      <c r="S9" s="21" t="n">
-        <v>26.57</v>
+          <t>风能、可燃冰、天然气、氢能源、物联网、冷链物流、商业航天、数据中心、油气资源、海工装备、深圳特区、社保新进、雄安新区</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="O9" s="20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P9" s="20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q9" s="20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R9" s="20" t="n">
+        <v>-36.17</v>
+      </c>
+      <c r="S9" s="20" t="n">
+        <v>18.54</v>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>乳业 +2.14%</t>
+          <t>可燃冰 +2.06%</t>
         </is>
       </c>
     </row>
@@ -2484,231 +2484,231 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>001219</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>青岛食品</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>休闲食品</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>乳业、婴童概念、电商概念、网红经济、调味品概念</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="O10" s="20" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="P10" s="20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q10" s="20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R10" s="20" t="n">
+        <v>-12.36</v>
+      </c>
+      <c r="S10" s="20" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>乳业 +2.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10-26午盘</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>001318</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>饮料乳品</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>乳业、味蕾经济、婴童概念</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>-11.94</v>
+      </c>
+      <c r="O11" s="20" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="P11" s="20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" s="20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R11" s="20" t="n">
+        <v>-30.22</v>
+      </c>
+      <c r="S11" s="20" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>乳业 +2.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>10-26午盘</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>乳业</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>603719</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>良品铺子</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>休闲食品</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>乳业、内贸流通、电商概念、社区团购、网红经济、谷子经济</t>
         </is>
       </c>
-      <c r="L10" s="21" t="n">
+      <c r="L12" s="20" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="M10" s="23" t="n">
+      <c r="M12" s="22" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="N10" s="23" t="n">
+      <c r="N12" s="22" t="n">
         <v>6.7</v>
       </c>
-      <c r="O10" s="21" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="P10" s="21" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R10" s="21" t="n">
+      <c r="O12" s="20" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P12" s="20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q12" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R12" s="20" t="n">
         <v>-26.35</v>
       </c>
-      <c r="S10" s="21" t="n">
+      <c r="S12" s="20" t="n">
         <v>14.65</v>
       </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>乳业 +2.14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>601598</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>中国外运</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>中盘价值、冷链物流、快递概念、跨境电商、统一大市场</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="M11" s="19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="N11" s="25" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O11" s="16" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="P11" s="16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q11" s="16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="R11" s="16" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="S11" s="16" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>002468</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>申通快递</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>大数据、小盘价值、快递概念、阿里概念</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="N12" s="19" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="O12" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P12" s="16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q12" s="16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R12" s="16" t="n">
-        <v>-18.91</v>
-      </c>
-      <c r="S12" s="16" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.97%</t>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>乳业 +2.04%</t>
         </is>
       </c>
     </row>
@@ -2724,231 +2724,231 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>001317</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>铁路公路</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
+        </is>
+      </c>
+      <c r="L13" s="16" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R13" s="16" t="n">
+        <v>-23.79</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +1.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>10-26午盘</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>601598</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>中国外运</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>中盘价值、冷链物流、快递概念、跨境电商、统一大市场</t>
+        </is>
+      </c>
+      <c r="L14" s="16" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P14" s="16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q14" s="16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +1.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>10-26午盘</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>001317</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>三羊马</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>铁路公路</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="O13" s="16" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="P13" s="16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q13" s="16" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="R13" s="16" t="n">
-        <v>-25.07</v>
-      </c>
-      <c r="S13" s="16" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>603258</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>电魂网络</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>游戏Ⅱ</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>文娱消费、电子竞技、网络游戏、虚拟现实、谷子经济、AIGC概念、短剧互动游戏</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="M14" s="23" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N14" s="23" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q14" s="21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R14" s="21" t="n">
-        <v>-26.02</v>
-      </c>
-      <c r="S14" s="21" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技 +1.94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>002354</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>天娱数科</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>广告营销</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>信创、AI语料、东数西算、国产芯片、在线教育、小盘价值、文娱消费、电子竞技、百度概念、网络游戏、股权分散、虚拟现实、谷子经济、跨境电商、互联网服务、互联网金融、多模态AI、小红书概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、ChatGPT概念、DeepSeek概念、抖音概念(字节概念)</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M15" s="23" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="N15" s="23" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="O15" s="21" t="n">
-        <v>67.14</v>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q15" s="21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R15" s="21" t="n">
-        <v>-18.76</v>
-      </c>
-      <c r="S15" s="21" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>电子竞技 +1.94%</t>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>002468</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>申通快递</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>大数据、小盘价值、快递概念、阿里概念</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O15" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q15" s="16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R15" s="16" t="n">
+        <v>-18.63</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +1.84%</t>
         </is>
       </c>
     </row>
@@ -2960,19 +2960,19 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>电子竞技</t>
+          <t>免税概念</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>电子竞技</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>1.94</v>
+          <t>免税概念</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>1.77</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
@@ -2980,55 +2980,55 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>001308</t>
+        <v>1</v>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>001979</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>康冠科技</t>
+          <t>招商蛇口</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>光学光电子</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>AIPC、AI眼镜、OLED、华为概念、小盘价值、智能电视、智能穿戴、深圳特区、电子竞技、虚拟现实、贬值受益、医疗器械概念、消费电子概念、MiniLED、抖音概念(字节概念)</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="M16" s="23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N16" s="23" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Q16" s="21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R16" s="21" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="S16" s="21" t="n">
-        <v>17.46</v>
+          <t>低市净率、免税概念、养老概念、大盘价值、深圳特区、租售同权、行业龙头、雄安新区、零售概念、REITs概念</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="O16" s="20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P16" s="20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" s="20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R16" s="20" t="n">
+        <v>-24.56</v>
+      </c>
+      <c r="S16" s="20" t="n">
+        <v>30.78</v>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>电子竞技 +1.94%</t>
+          <t>免税概念 +1.77%</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>租售同权</t>
+          <t>免税概念</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -3048,67 +3048,67 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>租售同权</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n">
+          <t>免税概念</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>600009</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>上海机场</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>航空机场</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>免税概念、大盘成长、社保新进、长江三角、零售概念</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N17" s="22" t="n">
         <v>1.85</v>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>001979</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>招商蛇口</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>低市净率、免税概念、养老概念、大盘价值、深圳特区、租售同权、行业龙头、雄安新区、零售概念、REITs概念</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="M17" s="23" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="N17" s="23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q17" s="21" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="R17" s="21" t="n">
-        <v>-23.55</v>
-      </c>
-      <c r="S17" s="21" t="n">
-        <v>32.54</v>
+      <c r="O17" s="20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P17" s="20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q17" s="20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R17" s="20" t="n">
+        <v>-30.39</v>
+      </c>
+      <c r="S17" s="20" t="n">
+        <v>7.59</v>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>租售同权 +1.85%</t>
+          <t>免税概念 +1.77%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>租售同权</t>
+          <t>免税概念</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>租售同权</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>1.85</v>
+          <t>免税概念</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>1.77</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
@@ -3140,135 +3140,135 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>000560</t>
+        <v>3</v>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>600694</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>大商股份</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>房地产服务</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>低市净率、华为概念、租售同权、鸿蒙概念、西部大开发、AIGC概念</t>
-        </is>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="P18" s="21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R18" s="21" t="n">
-        <v>-20.98</v>
-      </c>
-      <c r="S18" s="21" t="n">
-        <v>52.5</v>
+          <t>东北振兴、低市净率、免税概念、内贸流通、电商概念、社保新进、零售概念</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O18" s="20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P18" s="20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R18" s="20" t="n">
+        <v>-12.99</v>
+      </c>
+      <c r="S18" s="20" t="n">
+        <v>13.91</v>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>租售同权 +1.85%</t>
+          <t>免税概念 +1.77%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>租售同权</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>租售同权</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>1.85</v>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>10-23</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>PLC概念</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>PLC概念</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>6.14</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>600605</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>汇通能源</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>一般零售</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>内贸流通、存储芯片、私募重仓、租售同权、长江三角、半导体概念、液冷服务器</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="M19" s="23" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="N19" s="23" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="O19" s="21" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="P19" s="21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Q19" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R19" s="21" t="n">
-        <v>-21.13</v>
-      </c>
-      <c r="S19" s="21" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>租售同权 +1.85%</t>
+      <c r="G19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>002979</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>雷赛智能</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>自动化设备</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>华为概念、小盘成长、深圳特区、PLC概念、机器人执行器</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N19" s="19" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q19" s="16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R19" s="16" t="n">
+        <v>-25.84</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>PLC概念 +6.14%</t>
         </is>
       </c>
     </row>
@@ -3300,51 +3300,51 @@
         </is>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>002979</t>
+          <t>603933</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>其他电子Ⅱ</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>华为概念、小盘成长、深圳特区、PLC概念、机器人执行器</t>
+          <t>ETC、无人机、PLC概念、半导体概念</t>
         </is>
       </c>
       <c r="L20" s="16" t="n">
-        <v>54.15</v>
+        <v>20.94</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="N20" s="19" t="n">
-        <v>11.19</v>
+        <v>23.32</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>8.81</v>
+        <v>1.97</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>2.01</v>
+        <v>1.43</v>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="R20" s="16" t="n">
-        <v>-25.84</v>
+        <v>-33.5</v>
       </c>
       <c r="S20" s="16" t="n">
-        <v>56.41</v>
+        <v>27.29</v>
       </c>
       <c r="T20" s="11" t="inlineStr">
         <is>
@@ -3380,51 +3380,51 @@
         </is>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>603933</t>
+          <t>603416</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>信捷电气</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>其他电子Ⅱ</t>
+          <t>自动化设备</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>ETC、无人机、PLC概念、半导体概念</t>
+          <t>私募重仓、PLC概念</t>
         </is>
       </c>
       <c r="L21" s="16" t="n">
-        <v>20.94</v>
+        <v>47.07</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>9.98</v>
+        <v>5.87</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>23.32</v>
+        <v>11.01</v>
       </c>
       <c r="O21" s="16" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" s="16" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="R21" s="16" t="n">
-        <v>-33.5</v>
+        <v>-27.35</v>
       </c>
       <c r="S21" s="16" t="n">
-        <v>27.29</v>
+        <v>11.28</v>
       </c>
       <c r="T21" s="11" t="inlineStr">
         <is>
@@ -3454,13 +3454,13 @@
       <c r="E22" s="16" t="n">
         <v>6.14</v>
       </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
@@ -3520,23 +3520,23 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PLC概念</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>PLC概念</t>
+          <t>机器人执行器</t>
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
+        <v>5.92</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
@@ -3544,51 +3544,51 @@
       </c>
       <c r="H23" s="18" t="inlineStr">
         <is>
-          <t>603416</t>
+          <t>003021</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>信捷电气</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>电机Ⅱ</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>私募重仓、PLC概念</t>
+          <t>减速器、5G概念、华为汽车、小盘成长、小米概念、深圳特区、荣耀概念、通信技术</t>
         </is>
       </c>
       <c r="L23" s="16" t="n">
-        <v>47.07</v>
+        <v>91.73</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>5.87</v>
+        <v>10</v>
       </c>
       <c r="N23" s="19" t="n">
-        <v>11.01</v>
+        <v>50.11</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>2.39</v>
+        <v>12.57</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>2.32</v>
+        <v>5.24</v>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>1.34</v>
+        <v>2.37</v>
       </c>
       <c r="R23" s="16" t="n">
-        <v>-27.35</v>
+        <v>-30.62</v>
       </c>
       <c r="S23" s="16" t="n">
-        <v>11.28</v>
+        <v>52</v>
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>PLC概念 +6.14%</t>
+          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
         </is>
       </c>
     </row>
@@ -3620,51 +3620,51 @@
         </is>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>003021</t>
+          <t>002979</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>电机Ⅱ</t>
+          <t>自动化设备</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>减速器、5G概念、华为汽车、小盘成长、小米概念、深圳特区、荣耀概念、通信技术</t>
+          <t>华为概念、小盘成长、深圳特区、PLC概念、机器人执行器</t>
         </is>
       </c>
       <c r="L24" s="16" t="n">
-        <v>91.73</v>
+        <v>54.15</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="N24" s="19" t="n">
-        <v>50.11</v>
+        <v>11.19</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>12.57</v>
+        <v>8.81</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>5.24</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>2.37</v>
+        <v>1.38</v>
       </c>
       <c r="R24" s="16" t="n">
-        <v>-30.62</v>
+        <v>-25.84</v>
       </c>
       <c r="S24" s="16" t="n">
-        <v>52</v>
+        <v>56.41</v>
       </c>
       <c r="T24" s="11" t="inlineStr">
         <is>
@@ -3700,16 +3700,16 @@
         </is>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>002979</t>
+          <t>002747</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -3719,32 +3719,32 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>华为概念、小盘成长、深圳特区、PLC概念、机器人执行器</t>
+          <t>养老概念、密集调研、工业母机、机器视觉、工业互联网、医疗器械概念</t>
         </is>
       </c>
       <c r="L25" s="16" t="n">
-        <v>54.15</v>
+        <v>29.18</v>
       </c>
       <c r="M25" s="19" t="n">
         <v>9.99</v>
       </c>
       <c r="N25" s="19" t="n">
-        <v>11.19</v>
+        <v>20.38</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>8.81</v>
+        <v>10.51</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" s="16" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="R25" s="16" t="n">
-        <v>-25.84</v>
+        <v>-40.45</v>
       </c>
       <c r="S25" s="16" t="n">
-        <v>56.41</v>
+        <v>50.33</v>
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
@@ -3774,57 +3774,57 @@
       <c r="E26" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>002747</t>
+          <t>002526</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>山东矿机</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>养老概念、密集调研、工业母机、机器视觉、工业互联网、医疗器械概念</t>
+          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
         </is>
       </c>
       <c r="L26" s="16" t="n">
-        <v>29.18</v>
+        <v>2.8</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>9.99</v>
+        <v>3.7</v>
       </c>
       <c r="N26" s="19" t="n">
-        <v>20.38</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>10.51</v>
+        <v>5.69</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>2.48</v>
+        <v>3.53</v>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="R26" s="16" t="n">
-        <v>-40.45</v>
+        <v>-30.35</v>
       </c>
       <c r="S26" s="16" t="n">
-        <v>50.33</v>
+        <v>13.36</v>
       </c>
       <c r="T26" s="11" t="inlineStr">
         <is>
@@ -3854,57 +3854,57 @@
       <c r="E27" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>002526</t>
+          <t>002530</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>山东矿机</t>
+          <t>金财互联</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
+          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
         </is>
       </c>
       <c r="L27" s="16" t="n">
-        <v>2.8</v>
+        <v>7.54</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="N27" s="19" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>5.69</v>
+        <v>6.35</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>3.53</v>
+        <v>3.13</v>
       </c>
       <c r="Q27" s="16" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R27" s="16" t="n">
-        <v>-30.35</v>
+        <v>-34.43</v>
       </c>
       <c r="S27" s="16" t="n">
-        <v>13.36</v>
+        <v>17.63</v>
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
@@ -3934,22 +3934,22 @@
       <c r="E28" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>002530</t>
+          <t>000837</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>金财互联</t>
+          <t>秦川机床</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -3959,32 +3959,32 @@
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
+          <t>减速器、3D打印、工业母机、海工装备、西部大开发、机器人执行器、化债(AMC)概念</t>
         </is>
       </c>
       <c r="L28" s="16" t="n">
-        <v>7.54</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>3.43</v>
+        <v>4.44</v>
       </c>
       <c r="N28" s="19" t="n">
-        <v>4.14</v>
+        <v>12.29</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>6.35</v>
+        <v>3.18</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>3.13</v>
+        <v>2.84</v>
       </c>
       <c r="Q28" s="16" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="R28" s="16" t="n">
-        <v>-34.43</v>
+        <v>-27.96</v>
       </c>
       <c r="S28" s="16" t="n">
-        <v>17.63</v>
+        <v>15.03</v>
       </c>
       <c r="T28" s="11" t="inlineStr">
         <is>
@@ -4014,57 +4014,57 @@
       <c r="E29" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="18" t="inlineStr">
         <is>
-          <t>000837</t>
+          <t>002527</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>秦川机床</t>
+          <t>新时达</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>减速器、3D打印、工业母机、海工装备、西部大开发、机器人执行器、化债(AMC)概念</t>
+          <t>减速器、基金减仓、数字孪生、机器视觉、电池技术、股权转让、液冷服务器、同步磁阻电机、燃料电池概念</t>
         </is>
       </c>
       <c r="L29" s="16" t="n">
-        <v>9.869999999999999</v>
+        <v>11.23</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>4.44</v>
+        <v>5.84</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>12.29</v>
+        <v>9.35</v>
       </c>
       <c r="O29" s="16" t="n">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="P29" s="16" t="n">
         <v>2.84</v>
       </c>
       <c r="Q29" s="16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R29" s="16" t="n">
-        <v>-27.96</v>
+        <v>-38.73</v>
       </c>
       <c r="S29" s="16" t="n">
-        <v>15.03</v>
+        <v>16.49</v>
       </c>
       <c r="T29" s="11" t="inlineStr">
         <is>
@@ -4094,57 +4094,57 @@
       <c r="E30" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>002527</t>
+          <t>603915</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>新时达</t>
+          <t>国茂股份</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>减速器、基金减仓、数字孪生、机器视觉、电池技术、股权转让、液冷服务器、同步磁阻电机、燃料电池概念</t>
+          <t>减速器、机器人执行器</t>
         </is>
       </c>
       <c r="L30" s="16" t="n">
-        <v>11.23</v>
+        <v>13.89</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>5.84</v>
+        <v>4.04</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>9.35</v>
+        <v>14.42</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>3.37</v>
+        <v>2.21</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>2.84</v>
+        <v>2.49</v>
       </c>
       <c r="Q30" s="16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R30" s="16" t="n">
-        <v>-38.73</v>
+        <v>-26.66</v>
       </c>
       <c r="S30" s="16" t="n">
-        <v>16.49</v>
+        <v>17.22</v>
       </c>
       <c r="T30" s="11" t="inlineStr">
         <is>
@@ -4174,57 +4174,57 @@
       <c r="E31" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>603915</t>
+          <t>002401</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>国茂股份</t>
+          <t>中远海科</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>减速器、机器人执行器</t>
+          <t>ETC、云计算、大数据、基金减仓、安防概念、数据中心、智慧城市、机器视觉、长江三角、阿里概念、互联网服务、统一大市场</t>
         </is>
       </c>
       <c r="L31" s="16" t="n">
-        <v>13.89</v>
+        <v>12.3</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>4.04</v>
+        <v>2.07</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>14.42</v>
+        <v>2.07</v>
       </c>
       <c r="O31" s="16" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" s="16" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R31" s="16" t="n">
-        <v>-26.66</v>
+        <v>-30.74</v>
       </c>
       <c r="S31" s="16" t="n">
-        <v>17.22</v>
+        <v>9.92</v>
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
@@ -4254,57 +4254,57 @@
       <c r="E32" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>002401</t>
+          <t>002139</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>中远海科</t>
+          <t>拓邦股份</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>ETC、云计算、大数据、基金减仓、安防概念、数据中心、智慧城市、机器视觉、长江三角、阿里概念、互联网服务、统一大市场</t>
+          <t>无人机、物联网、储能概念、华为概念、华为汽车、安防概念、无线充电、无线耳机、智能电网、机器视觉、深圳特区、激光雷达、电池技术、电网概念、私募新进、高压快充、鸿蒙概念、半导体概念、新型工业化、液冷服务器、空气能热泵、钠离子电池、锂电池概念、消费电子概念、DeepSeek概念</t>
         </is>
       </c>
       <c r="L32" s="16" t="n">
-        <v>12.3</v>
+        <v>9.92</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>2.07</v>
+        <v>4.64</v>
       </c>
       <c r="N32" s="19" t="n">
-        <v>2.07</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O32" s="16" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" s="16" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="R32" s="16" t="n">
-        <v>-30.74</v>
+        <v>-31.63</v>
       </c>
       <c r="S32" s="16" t="n">
-        <v>9.92</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="T32" s="11" t="inlineStr">
         <is>
@@ -4334,57 +4334,57 @@
       <c r="E33" s="16" t="n">
         <v>5.92</v>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G33" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>002139</t>
+          <t>002896</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>拓邦股份</t>
+          <t>中大力德</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
         <is>
-          <t>无人机、物联网、储能概念、华为概念、华为汽车、安防概念、无线充电、无线耳机、智能电网、机器视觉、深圳特区、激光雷达、电池技术、电网概念、私募新进、高压快充、鸿蒙概念、半导体概念、新型工业化、液冷服务器、空气能热泵、钠离子电池、锂电池概念、消费电子概念、DeepSeek概念</t>
+          <t>减速器、基金减仓、小盘成长、机器人执行器</t>
         </is>
       </c>
       <c r="L33" s="16" t="n">
-        <v>9.92</v>
+        <v>60.98</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>4.64</v>
+        <v>8.49</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>9.369999999999999</v>
+        <v>19.33</v>
       </c>
       <c r="O33" s="16" t="n">
-        <v>2.55</v>
+        <v>6.85</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" s="16" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="R33" s="16" t="n">
-        <v>-31.63</v>
+        <v>-35.86</v>
       </c>
       <c r="S33" s="16" t="n">
-        <v>9.369999999999999</v>
+        <v>21.47</v>
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
@@ -4400,75 +4400,75 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
+        <v>5.45</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
         </is>
       </c>
       <c r="G34" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>605398</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>新炬网络</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>减速器、基金减仓、小盘成长、机器人执行器</t>
+          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
         </is>
       </c>
       <c r="L34" s="16" t="n">
-        <v>60.98</v>
+        <v>22.68</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="N34" s="19" t="n">
-        <v>19.33</v>
+        <v>3.85</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>-0.53</v>
       </c>
       <c r="O34" s="16" t="n">
-        <v>6.85</v>
+        <v>4.01</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>2.18</v>
+        <v>0.9</v>
       </c>
       <c r="Q34" s="16" t="n">
-        <v>1.46</v>
+        <v>0.8</v>
       </c>
       <c r="R34" s="16" t="n">
-        <v>-35.86</v>
+        <v>-35.55</v>
       </c>
       <c r="S34" s="16" t="n">
-        <v>21.47</v>
+        <v>25.44</v>
       </c>
       <c r="T34" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>MLOps概念 +5.45%</t>
         </is>
       </c>
     </row>
@@ -4500,16 +4500,16 @@
         </is>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>605398</t>
+          <t>002232</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>新炬网络</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
@@ -4519,32 +4519,32 @@
       </c>
       <c r="K35" s="11" t="inlineStr">
         <is>
-          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
+          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L35" s="16" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N35" s="25" t="n">
-        <v>-0.53</v>
+        <v>14.3</v>
+      </c>
+      <c r="M35" s="24" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>-6.9</v>
       </c>
       <c r="O35" s="16" t="n">
-        <v>4.01</v>
+        <v>5.16</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" s="16" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="R35" s="16" t="n">
-        <v>-35.55</v>
+        <v>-35.24</v>
       </c>
       <c r="S35" s="16" t="n">
-        <v>25.44</v>
+        <v>8.75</v>
       </c>
       <c r="T35" s="11" t="inlineStr">
         <is>
@@ -4553,82 +4553,82 @@
       </c>
     </row>
     <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>10-23</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>5.45</v>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>5.34</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>002232</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>启明信息</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
-        </is>
-      </c>
-      <c r="L36" s="16" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M36" s="25" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="N36" s="25" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="P36" s="16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q36" s="16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="R36" s="16" t="n">
-        <v>-35.24</v>
-      </c>
-      <c r="S36" s="16" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="T36" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念 +5.45%</t>
+      <c r="G36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>603528</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>多伦科技</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>软件开发</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>大数据、物联网、华为昇腾、华为概念、卫星导航、国产芯片、国产软件、智慧城市、职业教育、虚拟机器人、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="O36" s="20" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="P36" s="20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q36" s="20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R36" s="20" t="n">
+        <v>-28.47</v>
+      </c>
+      <c r="S36" s="20" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人 +5.34%</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
           <t>虚拟机器人</t>
         </is>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="20" t="n">
         <v>5.34</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
@@ -4660,16 +4660,16 @@
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>603528</t>
+        <v>2</v>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>601519</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>大智慧</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -4679,32 +4679,32 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>大数据、物联网、华为昇腾、华为概念、卫星导航、国产芯片、国产软件、智慧城市、职业教育、虚拟机器人、车联网(车路云)</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="M37" s="23" t="n">
-        <v>10</v>
+          <t>大数据、华为概念、国产软件、小盘成长、数据中心、私募重仓、网红经济、长江三角、阿里概念、高市净率、鸿蒙概念、互联网金融、虚拟机器人</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <v>9.99</v>
       </c>
       <c r="N37" s="23" t="n">
-        <v>24.66</v>
-      </c>
-      <c r="O37" s="21" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Q37" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R37" s="21" t="n">
-        <v>-28.47</v>
-      </c>
-      <c r="S37" s="21" t="n">
-        <v>49.91</v>
+        <v>-2.43</v>
+      </c>
+      <c r="O37" s="20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P37" s="20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q37" s="20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R37" s="20" t="n">
+        <v>-39.62</v>
+      </c>
+      <c r="S37" s="20" t="n">
+        <v>24.33</v>
       </c>
       <c r="T37" s="5" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
           <t>虚拟机器人</t>
         </is>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="20" t="n">
         <v>5.34</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -4740,51 +4740,51 @@
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t>601519</t>
+        <v>3</v>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>001314</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>大智慧</t>
+          <t>亿道信息</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>软件开发</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>大数据、华为概念、国产软件、小盘成长、数据中心、私募重仓、网红经济、长江三角、阿里概念、高市净率、鸿蒙概念、互联网金融、虚拟机器人</t>
-        </is>
-      </c>
-      <c r="L38" s="21" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="M38" s="23" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N38" s="24" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="O38" s="21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P38" s="21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q38" s="21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R38" s="21" t="n">
-        <v>-39.62</v>
-      </c>
-      <c r="S38" s="21" t="n">
-        <v>24.33</v>
+          <t>PCB、物联网、AIPC、AI眼镜、在线教育、增强现实、智能穿戴、虚拟现实、虚拟机器人、消费电子概念</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="O38" s="20" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="P38" s="20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q38" s="20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R38" s="20" t="n">
+        <v>-29.48</v>
+      </c>
+      <c r="S38" s="20" t="n">
+        <v>18.05</v>
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
@@ -4800,19 +4800,19 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>虚拟机器人</t>
+          <t>ChatGPT概念</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="n">
-        <v>5.34</v>
+          <t>ChatGPT概念</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>5.2</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
@@ -4820,55 +4820,55 @@
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
-        <is>
-          <t>001314</t>
+        <v>1</v>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>603466</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>亿道信息</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>数字媒体</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>PCB、物联网、AIPC、AI眼镜、在线教育、增强现实、智能穿戴、虚拟现实、虚拟机器人、消费电子概念</t>
-        </is>
-      </c>
-      <c r="L39" s="21" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="M39" s="23" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="N39" s="23" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="O39" s="21" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q39" s="21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R39" s="21" t="n">
-        <v>-29.48</v>
-      </c>
-      <c r="S39" s="21" t="n">
-        <v>18.05</v>
+          <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="M39" s="22" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="N39" s="22" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="O39" s="20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="P39" s="20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q39" s="20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="20" t="n">
+        <v>66.36</v>
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>虚拟机器人 +5.34%</t>
+          <t>ChatGPT概念 +5.20%</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="20" t="n">
         <v>5.2</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -4900,51 +4900,51 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t>603466</t>
+        <v>2</v>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>002354</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>数字媒体</t>
+          <t>广告营销</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
-        </is>
-      </c>
-      <c r="L40" s="21" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="M40" s="23" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="N40" s="23" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="O40" s="21" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="P40" s="21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q40" s="21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R40" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="21" t="n">
-        <v>66.36</v>
+          <t>信创、AI语料、东数西算、国产芯片、在线教育、小盘价值、文娱消费、电子竞技、百度概念、网络游戏、股权分散、虚拟现实、谷子经济、跨境电商、互联网服务、互联网金融、多模态AI、小红书概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、ChatGPT概念、DeepSeek概念、抖音概念(字节概念)</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="M40" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N40" s="22" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="O40" s="20" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="P40" s="20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q40" s="20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R40" s="20" t="n">
+        <v>-22.34</v>
+      </c>
+      <c r="S40" s="20" t="n">
+        <v>48.43</v>
       </c>
       <c r="T40" s="5" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="20" t="n">
         <v>5.2</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -4980,135 +4980,135 @@
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
-        <is>
-          <t>002354</t>
+        <v>3</v>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>600446</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>金证股份</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>广告营销</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>信创、AI语料、东数西算、国产芯片、在线教育、小盘价值、文娱消费、电子竞技、百度概念、网络游戏、股权分散、虚拟现实、谷子经济、跨境电商、互联网服务、互联网金融、多模态AI、小红书概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、ChatGPT概念、DeepSeek概念、抖音概念(字节概念)</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="M41" s="23" t="n">
+          <t>信创、国产软件、数据安全、智慧城市、深圳特区、电商概念、网络安全、股权分散、互联网服务、虚拟机器人、ChatGPT概念</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O41" s="20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P41" s="20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q41" s="20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R41" s="20" t="n">
+        <v>-40.62</v>
+      </c>
+      <c r="S41" s="20" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>ChatGPT概念 +5.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>10-22</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>机器人执行器</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>003021</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>兆威机电</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>电机Ⅱ</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>减速器、5G概念、华为汽车、小盘成长、小米概念、深圳特区、荣耀概念、通信技术</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="M42" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="N41" s="23" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="O41" s="21" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="P41" s="21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q41" s="21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R41" s="21" t="n">
-        <v>-22.34</v>
-      </c>
-      <c r="S41" s="21" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>ChatGPT概念 +5.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>10-23</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>ChatGPT概念</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>ChatGPT概念</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="22" t="inlineStr">
-        <is>
-          <t>600446</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>金证股份</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>信创、国产软件、数据安全、智慧城市、深圳特区、电商概念、网络安全、股权分散、互联网服务、虚拟机器人、ChatGPT概念</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M42" s="23" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="N42" s="23" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="O42" s="21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P42" s="21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q42" s="21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R42" s="21" t="n">
-        <v>-40.62</v>
-      </c>
-      <c r="S42" s="21" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>ChatGPT概念 +5.20%</t>
+      <c r="N42" s="19" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q42" s="16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R42" s="16" t="n">
+        <v>-36.93</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="T42" s="11" t="inlineStr">
+        <is>
+          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
         </is>
       </c>
     </row>
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>003021</t>
+          <t>603728</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>鸣志电器</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -5159,32 +5159,32 @@
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>减速器、5G概念、华为汽车、小盘成长、小米概念、深圳特区、荣耀概念、通信技术</t>
+          <t>减速器、5G概念、安防概念、小盘成长、通信技术、LED概念、液冷服务器、机器人执行器</t>
         </is>
       </c>
       <c r="L43" s="16" t="n">
-        <v>83.39</v>
+        <v>54.47</v>
       </c>
       <c r="M43" s="19" t="n">
         <v>10</v>
       </c>
       <c r="N43" s="19" t="n">
-        <v>38.18</v>
+        <v>23.74</v>
       </c>
       <c r="O43" s="16" t="n">
-        <v>3.62</v>
+        <v>4.56</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>1.96</v>
+        <v>2.99</v>
       </c>
       <c r="Q43" s="16" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="R43" s="16" t="n">
-        <v>-36.93</v>
+        <v>-28.6</v>
       </c>
       <c r="S43" s="16" t="n">
-        <v>38.18</v>
+        <v>23.74</v>
       </c>
       <c r="T43" s="11" t="inlineStr">
         <is>
@@ -5220,51 +5220,51 @@
         </is>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>603728</t>
+          <t>000678</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>鸣志电器</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>电机Ⅱ</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>减速器、5G概念、安防概念、小盘成长、通信技术、LED概念、液冷服务器、机器人执行器</t>
+          <t>军工、减速器</t>
         </is>
       </c>
       <c r="L44" s="16" t="n">
-        <v>54.47</v>
+        <v>12.03</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N44" s="19" t="n">
-        <v>23.74</v>
+        <v>21.03</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>4.56</v>
+        <v>15.95</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>2.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q44" s="16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R44" s="16" t="n">
-        <v>-28.6</v>
+        <v>-24.2</v>
       </c>
       <c r="S44" s="16" t="n">
-        <v>23.74</v>
+        <v>57.05</v>
       </c>
       <c r="T44" s="11" t="inlineStr">
         <is>
@@ -5294,57 +5294,57 @@
       <c r="E45" s="16" t="n">
         <v>0.76</v>
       </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>000678</t>
+          <t>002526</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>山东矿机</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>军工、减速器</t>
+          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
         </is>
       </c>
       <c r="L45" s="16" t="n">
-        <v>12.03</v>
+        <v>2.7</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>9.960000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="N45" s="19" t="n">
-        <v>21.03</v>
+        <v>7.14</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>15.95</v>
+        <v>4.89</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>1.35</v>
+        <v>3.56</v>
       </c>
       <c r="Q45" s="16" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="R45" s="16" t="n">
-        <v>-24.2</v>
+        <v>-32.84</v>
       </c>
       <c r="S45" s="16" t="n">
-        <v>57.05</v>
+        <v>9.31</v>
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
@@ -5374,57 +5374,57 @@
       <c r="E46" s="16" t="n">
         <v>0.76</v>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F46" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>002526</t>
+          <t>603728</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>山东矿机</t>
+          <t>鸣志电器</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>电机Ⅱ</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
+          <t>减速器、5G概念、安防概念、小盘成长、通信技术、LED概念、液冷服务器、机器人执行器</t>
         </is>
       </c>
       <c r="L46" s="16" t="n">
-        <v>2.7</v>
+        <v>54.47</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="N46" s="19" t="n">
-        <v>7.14</v>
+        <v>23.74</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>4.89</v>
+        <v>4.56</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="Q46" s="16" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="R46" s="16" t="n">
-        <v>-32.84</v>
+        <v>-28.6</v>
       </c>
       <c r="S46" s="16" t="n">
-        <v>9.31</v>
+        <v>23.74</v>
       </c>
       <c r="T46" s="11" t="inlineStr">
         <is>
@@ -5454,57 +5454,57 @@
       <c r="E47" s="16" t="n">
         <v>0.76</v>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>603728</t>
+          <t>002530</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>鸣志电器</t>
+          <t>金财互联</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>电机Ⅱ</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>减速器、5G概念、安防概念、小盘成长、通信技术、LED概念、液冷服务器、机器人执行器</t>
+          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
         </is>
       </c>
       <c r="L47" s="16" t="n">
-        <v>54.47</v>
-      </c>
-      <c r="M47" s="19" t="n">
-        <v>10</v>
+        <v>7.29</v>
+      </c>
+      <c r="M47" s="24" t="n">
+        <v>-1.62</v>
       </c>
       <c r="N47" s="19" t="n">
-        <v>23.74</v>
+        <v>4.74</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>4.56</v>
+        <v>4.45</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" s="16" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="R47" s="16" t="n">
-        <v>-28.6</v>
+        <v>-36.61</v>
       </c>
       <c r="S47" s="16" t="n">
-        <v>23.74</v>
+        <v>13.73</v>
       </c>
       <c r="T47" s="11" t="inlineStr">
         <is>
@@ -5534,22 +5534,22 @@
       <c r="E48" s="16" t="n">
         <v>0.76</v>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F48" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G48" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>002530</t>
+          <t>603662</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>金财互联</t>
+          <t>柯力传感</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -5559,32 +5559,32 @@
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
+          <t>传感器、大数据、物联网、华为概念、小盘成长、机器视觉、机器人执行器</t>
         </is>
       </c>
       <c r="L48" s="16" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="M48" s="25" t="n">
-        <v>-1.62</v>
+        <v>48.03</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>2.19</v>
       </c>
       <c r="N48" s="19" t="n">
-        <v>4.74</v>
+        <v>18.97</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>4.45</v>
+        <v>3.61</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" s="16" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="R48" s="16" t="n">
-        <v>-36.61</v>
+        <v>-39.69</v>
       </c>
       <c r="S48" s="16" t="n">
-        <v>13.73</v>
+        <v>18.97</v>
       </c>
       <c r="T48" s="11" t="inlineStr">
         <is>
@@ -5614,22 +5614,22 @@
       <c r="E49" s="16" t="n">
         <v>0.76</v>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G49" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>603662</t>
+          <t>000837</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>柯力传感</t>
+          <t>秦川机床</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
@@ -5639,32 +5639,32 @@
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>传感器、大数据、物联网、华为概念、小盘成长、机器视觉、机器人执行器</t>
+          <t>减速器、3D打印、工业母机、海工装备、西部大开发、机器人执行器、化债(AMC)概念</t>
         </is>
       </c>
       <c r="L49" s="16" t="n">
-        <v>48.03</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="N49" s="19" t="n">
-        <v>18.97</v>
+        <v>8.75</v>
       </c>
       <c r="O49" s="16" t="n">
-        <v>3.61</v>
+        <v>2.29</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" s="16" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="R49" s="16" t="n">
-        <v>-39.69</v>
+        <v>-31.02</v>
       </c>
       <c r="S49" s="16" t="n">
-        <v>18.97</v>
+        <v>10.14</v>
       </c>
       <c r="T49" s="11" t="inlineStr">
         <is>
@@ -5673,82 +5673,82 @@
       </c>
     </row>
     <row r="50" ht="38" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>10-22</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>机器人执行器</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
-        <is>
-          <t>000837</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>秦川机床</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>通用设备</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>减速器、3D打印、工业母机、海工装备、西部大开发、机器人执行器、化债(AMC)概念</t>
-        </is>
-      </c>
-      <c r="L50" s="16" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="N50" s="19" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O50" s="16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P50" s="16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q50" s="16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R50" s="16" t="n">
-        <v>-31.02</v>
-      </c>
-      <c r="S50" s="16" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="T50" s="11" t="inlineStr">
-        <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>轮毂电机</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>轮毂电机</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="21" t="inlineStr">
+        <is>
+          <t>603350</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>安乃达</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>电机Ⅱ</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>传感器、轮毂电机</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="M50" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="22" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="O50" s="20" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="P50" s="20" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q50" s="20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R50" s="20" t="n">
+        <v>-27.28</v>
+      </c>
+      <c r="S50" s="20" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>轮毂电机 +0.16%</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E51" s="21" t="n">
+      <c r="E51" s="20" t="n">
         <v>0.16</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
@@ -5780,16 +5780,16 @@
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="22" t="inlineStr">
-        <is>
-          <t>603350</t>
+        <v>2</v>
+      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>603489</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>安乃达</t>
+          <t>八方股份</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>传感器、轮毂电机</t>
-        </is>
-      </c>
-      <c r="L51" s="21" t="n">
-        <v>29.48</v>
-      </c>
-      <c r="M51" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N51" s="23" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="O51" s="21" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="P51" s="21" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="Q51" s="21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R51" s="21" t="n">
-        <v>-27.28</v>
-      </c>
-      <c r="S51" s="21" t="n">
-        <v>13.65</v>
+          <t>交运设备、共享经济、轮毂电机</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M51" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" s="22" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="O51" s="20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P51" s="20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q51" s="20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R51" s="20" t="n">
+        <v>-31.13</v>
+      </c>
+      <c r="S51" s="20" t="n">
+        <v>16.48</v>
       </c>
       <c r="T51" s="5" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="E52" s="20" t="n">
         <v>0.16</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -5860,51 +5860,51 @@
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
-        <is>
-          <t>603489</t>
+        <v>3</v>
+      </c>
+      <c r="H52" s="21" t="inlineStr">
+        <is>
+          <t>002284</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>八方股份</t>
+          <t>亚太股份</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>电机Ⅱ</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>交运设备、共享经济、轮毂电机</t>
-        </is>
-      </c>
-      <c r="L52" s="21" t="n">
-        <v>27.5</v>
+          <t>华为汽车、胎压监测、轮毂电机、长江三角、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="n">
+        <v>8.57</v>
       </c>
       <c r="M52" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="23" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="O52" s="21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P52" s="21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q52" s="21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R52" s="21" t="n">
-        <v>-31.13</v>
-      </c>
-      <c r="S52" s="21" t="n">
-        <v>16.48</v>
+        <v>-0.58</v>
+      </c>
+      <c r="N52" s="22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O52" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P52" s="20" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q52" s="20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="R52" s="20" t="n">
+        <v>-50.58</v>
+      </c>
+      <c r="S52" s="20" t="n">
+        <v>3.38</v>
       </c>
       <c r="T52" s="5" t="inlineStr">
         <is>
@@ -5913,82 +5913,82 @@
       </c>
     </row>
     <row r="53" ht="38" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>10-22</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>轮毂电机</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>轮毂电机</t>
-        </is>
-      </c>
-      <c r="E53" s="21" t="n">
-        <v>0.16</v>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>工程机械概念</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>工程机械概念</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>-0.23</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G53" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="22" t="inlineStr">
-        <is>
-          <t>002284</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>亚太股份</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>汽车零部件</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>华为汽车、胎压监测、轮毂电机、长江三角、车联网(车路云)</t>
-        </is>
-      </c>
-      <c r="L53" s="21" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="M53" s="24" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="N53" s="23" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="O53" s="21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P53" s="21" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="Q53" s="21" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="R53" s="21" t="n">
-        <v>-50.58</v>
-      </c>
-      <c r="S53" s="21" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>轮毂电机 +0.16%</t>
+      <c r="G53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>603028</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>赛福天</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>通用设备</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>新材料、海工装备、知识产权、长江三角、工程机械概念、TOPCon电池</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="N53" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q53" s="16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R53" s="16" t="n">
+        <v>-26.38</v>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
+          <t>工程机械概念 -0.23%</t>
         </is>
       </c>
     </row>
@@ -6020,51 +6020,51 @@
         </is>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>603028</t>
+          <t>002097</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>赛福天</t>
+          <t>山河智能</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>新材料、海工装备、知识产权、长江三角、工程机械概念、TOPCon电池</t>
+          <t>军工、无人机、低空经济、军民融合、电池技术、私募新进、通用航空、锂电池概念、工程机械概念、雅下水电概念、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L54" s="16" t="n">
-        <v>7.76</v>
+        <v>7.26</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="N54" s="19" t="n">
-        <v>19.2</v>
+        <v>13.44</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>3.73</v>
+        <v>5.14</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="Q54" s="16" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="R54" s="16" t="n">
-        <v>-26.38</v>
+        <v>-50.54</v>
       </c>
       <c r="S54" s="16" t="n">
-        <v>34.96</v>
+        <v>13.44</v>
       </c>
       <c r="T54" s="11" t="inlineStr">
         <is>
@@ -6100,16 +6100,16 @@
         </is>
       </c>
       <c r="G55" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>002097</t>
+          <t>603280</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>山河智能</t>
+          <t>南方路机</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -6119,32 +6119,32 @@
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>军工、无人机、低空经济、军民融合、电池技术、私募新进、通用航空、锂电池概念、工程机械概念、雅下水电概念、飞行汽车(eVTOL)</t>
+          <t>物联网、核能核电、跨境电商、中俄贸易概念、工程机械概念、DeepSeek概念</t>
         </is>
       </c>
       <c r="L55" s="16" t="n">
-        <v>7.26</v>
+        <v>29.06</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="N55" s="19" t="n">
-        <v>13.44</v>
+        <v>7.63</v>
       </c>
       <c r="O55" s="16" t="n">
-        <v>5.14</v>
+        <v>5.23</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="Q55" s="16" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="R55" s="16" t="n">
-        <v>-50.54</v>
+        <v>-34.21</v>
       </c>
       <c r="S55" s="16" t="n">
-        <v>13.44</v>
+        <v>25.26</v>
       </c>
       <c r="T55" s="11" t="inlineStr">
         <is>
@@ -6174,22 +6174,22 @@
       <c r="E56" s="16" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F56" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G56" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>603280</t>
+          <t>001239</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>南方路机</t>
+          <t>永达股份</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
@@ -6199,32 +6199,32 @@
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>物联网、核能核电、跨境电商、中俄贸易概念、工程机械概念、DeepSeek概念</t>
+          <t>风能、工程机械概念</t>
         </is>
       </c>
       <c r="L56" s="16" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>9.99</v>
+        <v>13.27</v>
+      </c>
+      <c r="M56" s="24" t="n">
+        <v>-9.970000000000001</v>
       </c>
       <c r="N56" s="19" t="n">
-        <v>7.63</v>
+        <v>11.51</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>5.23</v>
+        <v>19.23</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>2.76</v>
+        <v>4.45</v>
       </c>
       <c r="Q56" s="16" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="R56" s="16" t="n">
-        <v>-34.21</v>
+        <v>-28.11</v>
       </c>
       <c r="S56" s="16" t="n">
-        <v>25.26</v>
+        <v>22.08</v>
       </c>
       <c r="T56" s="11" t="inlineStr">
         <is>
@@ -6254,57 +6254,57 @@
       <c r="E57" s="16" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F57" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>001239</t>
+          <t>002526</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>永达股份</t>
+          <t>山东矿机</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>工程机械</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>风能、工程机械概念</t>
+          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
         </is>
       </c>
       <c r="L57" s="16" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="M57" s="25" t="n">
-        <v>-9.970000000000001</v>
+        <v>2.7</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>2.66</v>
       </c>
       <c r="N57" s="19" t="n">
-        <v>11.51</v>
+        <v>7.14</v>
       </c>
       <c r="O57" s="16" t="n">
-        <v>19.23</v>
+        <v>4.89</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q57" s="16" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="R57" s="16" t="n">
-        <v>-28.11</v>
+        <v>-32.84</v>
       </c>
       <c r="S57" s="16" t="n">
-        <v>22.08</v>
+        <v>9.31</v>
       </c>
       <c r="T57" s="11" t="inlineStr">
         <is>
@@ -6334,57 +6334,57 @@
       <c r="E58" s="16" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F58" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G58" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
-          <t>002526</t>
+          <t>603273</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>山东矿机</t>
+          <t>天元智能</t>
         </is>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>减速器、无人机、低空经济、网络游戏、降解塑料、新型工业化、工程机械概念</t>
+          <t>氢能源、工程机械概念</t>
         </is>
       </c>
       <c r="L58" s="16" t="n">
-        <v>2.7</v>
+        <v>14.89</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>2.66</v>
+        <v>0.88</v>
       </c>
       <c r="N58" s="19" t="n">
-        <v>7.14</v>
+        <v>11.37</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>4.89</v>
+        <v>17.59</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" s="16" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="R58" s="16" t="n">
-        <v>-32.84</v>
+        <v>-28.96</v>
       </c>
       <c r="S58" s="16" t="n">
-        <v>9.31</v>
+        <v>19.79</v>
       </c>
       <c r="T58" s="11" t="inlineStr">
         <is>
@@ -6414,22 +6414,22 @@
       <c r="E59" s="16" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F59" s="20" t="inlineStr">
+      <c r="F59" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G59" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>603273</t>
+          <t>002097</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>天元智能</t>
+          <t>山河智能</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
@@ -6439,32 +6439,32 @@
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>氢能源、工程机械概念</t>
+          <t>军工、无人机、低空经济、军民融合、电池技术、私募新进、通用航空、锂电池概念、工程机械概念、雅下水电概念、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L59" s="16" t="n">
-        <v>14.89</v>
+        <v>7.26</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>0.88</v>
+        <v>10</v>
       </c>
       <c r="N59" s="19" t="n">
-        <v>11.37</v>
+        <v>13.44</v>
       </c>
       <c r="O59" s="16" t="n">
-        <v>17.59</v>
+        <v>5.14</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q59" s="16" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="R59" s="16" t="n">
-        <v>-28.96</v>
+        <v>-50.54</v>
       </c>
       <c r="S59" s="16" t="n">
-        <v>19.79</v>
+        <v>13.44</v>
       </c>
       <c r="T59" s="11" t="inlineStr">
         <is>
@@ -6494,57 +6494,57 @@
       <c r="E60" s="16" t="n">
         <v>-0.23</v>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F60" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G60" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H60" s="18" t="inlineStr">
         <is>
-          <t>002097</t>
+          <t>002530</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>山河智能</t>
+          <t>金财互联</t>
         </is>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>工程机械</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>军工、无人机、低空经济、军民融合、电池技术、私募新进、通用航空、锂电池概念、工程机械概念、雅下水电概念、飞行汽车(eVTOL)</t>
+          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
         </is>
       </c>
       <c r="L60" s="16" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>10</v>
+        <v>7.29</v>
+      </c>
+      <c r="M60" s="24" t="n">
+        <v>-1.62</v>
       </c>
       <c r="N60" s="19" t="n">
-        <v>13.44</v>
+        <v>4.74</v>
       </c>
       <c r="O60" s="16" t="n">
-        <v>5.14</v>
+        <v>4.45</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q60" s="16" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="R60" s="16" t="n">
-        <v>-50.54</v>
+        <v>-36.61</v>
       </c>
       <c r="S60" s="16" t="n">
-        <v>13.44</v>
+        <v>13.73</v>
       </c>
       <c r="T60" s="11" t="inlineStr">
         <is>
@@ -6560,75 +6560,75 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念</t>
+          <t>PLC概念</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念</t>
+          <t>PLC概念</t>
         </is>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
+        <v>-0.64</v>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
         </is>
       </c>
       <c r="G61" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H61" s="18" t="inlineStr">
         <is>
-          <t>002530</t>
+          <t>603933</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>金财互联</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>其他电子Ⅱ</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、智慧政务、核能核电、工程机械概念</t>
+          <t>ETC、无人机、PLC概念、半导体概念</t>
         </is>
       </c>
       <c r="L61" s="16" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="M61" s="25" t="n">
-        <v>-1.62</v>
+        <v>19.04</v>
+      </c>
+      <c r="M61" s="19" t="n">
+        <v>9.99</v>
       </c>
       <c r="N61" s="19" t="n">
-        <v>4.74</v>
+        <v>14.49</v>
       </c>
       <c r="O61" s="16" t="n">
-        <v>4.45</v>
+        <v>2.72</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="Q61" s="16" t="n">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="R61" s="16" t="n">
-        <v>-36.61</v>
+        <v>-39.54</v>
       </c>
       <c r="S61" s="16" t="n">
-        <v>13.73</v>
+        <v>15.74</v>
       </c>
       <c r="T61" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>PLC概念 -0.64%</t>
         </is>
       </c>
     </row>
@@ -6660,51 +6660,51 @@
         </is>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>603933</t>
+          <t>002334</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>英威腾</t>
         </is>
       </c>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>其他电子Ⅱ</t>
+          <t>自动化设备</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>ETC、无人机、PLC概念、半导体概念</t>
+          <t>充电桩、氢能源、物联网、储能概念、换电概念、数据中心、深圳特区、电池技术、股权分散、PLC概念、半导体概念、新型工业化、液冷服务器、同步磁阻电机、燃料电池概念</t>
         </is>
       </c>
       <c r="L62" s="16" t="n">
-        <v>19.04</v>
+        <v>6.42</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>9.99</v>
+        <v>0.16</v>
       </c>
       <c r="N62" s="19" t="n">
-        <v>14.49</v>
+        <v>4.73</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>2.03</v>
+        <v>1.1</v>
       </c>
       <c r="Q62" s="16" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="R62" s="16" t="n">
-        <v>-39.54</v>
+        <v>-37.18</v>
       </c>
       <c r="S62" s="16" t="n">
-        <v>15.74</v>
+        <v>6.12</v>
       </c>
       <c r="T62" s="11" t="inlineStr">
         <is>
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="G63" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>002334</t>
+          <t>002184</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>英威腾</t>
+          <t>海得控制</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
@@ -6759,32 +6759,32 @@
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>充电桩、氢能源、物联网、储能概念、换电概念、数据中心、深圳特区、电池技术、股权分散、PLC概念、半导体概念、新型工业化、液冷服务器、同步磁阻电机、燃料电池概念</t>
+          <t>风能、减速器、大数据、储能概念、国产软件、数据中心、智能电网、机器视觉、电网概念、虚拟电厂、PLC概念、工业互联网、新型工业化</t>
         </is>
       </c>
       <c r="L63" s="16" t="n">
-        <v>6.42</v>
+        <v>10.51</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="N63" s="19" t="n">
-        <v>4.73</v>
+        <v>3.85</v>
       </c>
       <c r="O63" s="16" t="n">
-        <v>1.27</v>
+        <v>5.45</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q63" s="16" t="n">
-        <v>0.99</v>
+        <v>1.61</v>
       </c>
       <c r="R63" s="16" t="n">
-        <v>-37.18</v>
+        <v>-38.72</v>
       </c>
       <c r="S63" s="16" t="n">
-        <v>6.12</v>
+        <v>18.22</v>
       </c>
       <c r="T63" s="11" t="inlineStr">
         <is>
@@ -6800,15 +6800,15 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>PLC概念</t>
+          <t>同步磁阻电机</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>PLC概念</t>
+          <t>同步磁阻电机</t>
         </is>
       </c>
       <c r="E64" s="16" t="n">
@@ -6820,55 +6820,55 @@
         </is>
       </c>
       <c r="G64" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>002184</t>
+          <t>600580</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>海得控制</t>
+          <t>卧龙电驱</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>电机Ⅱ</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、大数据、储能概念、国产软件、数据中心、智能电网、机器视觉、电网概念、虚拟电厂、PLC概念、工业互联网、新型工业化</t>
+          <t>低空经济、数据中心、核能核电、行业龙头、长江三角、工业互联网、特斯拉概念、同步磁阻电机、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L64" s="16" t="n">
-        <v>10.51</v>
+        <v>24.83</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>0.1</v>
+        <v>1.93</v>
       </c>
       <c r="N64" s="19" t="n">
-        <v>3.85</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O64" s="16" t="n">
-        <v>5.45</v>
+        <v>3.28</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q64" s="16" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="R64" s="16" t="n">
-        <v>-38.72</v>
+        <v>-50.43</v>
       </c>
       <c r="S64" s="16" t="n">
-        <v>18.22</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="T64" s="11" t="inlineStr">
         <is>
-          <t>PLC概念 -0.64%</t>
+          <t>同步磁阻电机 -0.64%</t>
         </is>
       </c>
     </row>
@@ -6900,51 +6900,51 @@
         </is>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>600580</t>
+          <t>002334</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>卧龙电驱</t>
+          <t>英威腾</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>电机Ⅱ</t>
+          <t>自动化设备</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>低空经济、数据中心、核能核电、行业龙头、长江三角、工业互联网、特斯拉概念、同步磁阻电机、飞行汽车(eVTOL)</t>
+          <t>充电桩、氢能源、物联网、储能概念、换电概念、数据中心、深圳特区、电池技术、股权分散、PLC概念、半导体概念、新型工业化、液冷服务器、同步磁阻电机、燃料电池概念</t>
         </is>
       </c>
       <c r="L65" s="16" t="n">
-        <v>24.83</v>
+        <v>6.42</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>1.93</v>
+        <v>0.16</v>
       </c>
       <c r="N65" s="19" t="n">
-        <v>8.140000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="O65" s="16" t="n">
-        <v>3.28</v>
+        <v>1.27</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q65" s="16" t="n">
-        <v>1.46</v>
+        <v>0.99</v>
       </c>
       <c r="R65" s="16" t="n">
-        <v>-50.43</v>
+        <v>-37.18</v>
       </c>
       <c r="S65" s="16" t="n">
-        <v>8.140000000000001</v>
+        <v>6.12</v>
       </c>
       <c r="T65" s="11" t="inlineStr">
         <is>
@@ -6980,51 +6980,51 @@
         </is>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="18" t="inlineStr">
         <is>
-          <t>002334</t>
+          <t>002527</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>英威腾</t>
+          <t>新时达</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>自动化设备</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>充电桩、氢能源、物联网、储能概念、换电概念、数据中心、深圳特区、电池技术、股权分散、PLC概念、半导体概念、新型工业化、液冷服务器、同步磁阻电机、燃料电池概念</t>
+          <t>减速器、基金减仓、数字孪生、机器视觉、电池技术、股权转让、液冷服务器、同步磁阻电机、燃料电池概念</t>
         </is>
       </c>
       <c r="L66" s="16" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>0.16</v>
+        <v>10.61</v>
+      </c>
+      <c r="M66" s="24" t="n">
+        <v>-0.47</v>
       </c>
       <c r="N66" s="19" t="n">
-        <v>4.73</v>
+        <v>10.06</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="Q66" s="16" t="n">
-        <v>0.99</v>
+        <v>1.56</v>
       </c>
       <c r="R66" s="16" t="n">
-        <v>-37.18</v>
+        <v>-43.05</v>
       </c>
       <c r="S66" s="16" t="n">
-        <v>6.12</v>
+        <v>10.06</v>
       </c>
       <c r="T66" s="11" t="inlineStr">
         <is>
@@ -7035,24 +7035,24 @@
     <row r="67" ht="38" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>10-22</t>
+          <t>10-21</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>同步磁阻电机</t>
+          <t>DRG/DIP</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>同步磁阻电机</t>
+          <t>DRG/DIP</t>
         </is>
       </c>
       <c r="E67" s="16" t="n">
-        <v>-0.64</v>
+        <v>3.25</v>
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
@@ -7060,55 +7060,55 @@
         </is>
       </c>
       <c r="G67" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>002527</t>
+          <t>002368</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>新时达</t>
+          <t>太极股份</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>减速器、基金减仓、数字孪生、机器视觉、电池技术、股权转让、液冷服务器、同步磁阻电机、燃料电池概念</t>
+          <t>信创、云计算、大数据、军民融合、华为概念、国产软件、小盘价值、智慧城市、智慧政务、水利建设、网络安全、跨境支付、互联网服务、工业互联网、财税数字化、创新医疗服务、DRG/DIP</t>
         </is>
       </c>
       <c r="L67" s="16" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="M67" s="25" t="n">
-        <v>-0.47</v>
+        <v>14.67</v>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>9.970000000000001</v>
       </c>
       <c r="N67" s="19" t="n">
-        <v>10.06</v>
+        <v>21.54</v>
       </c>
       <c r="O67" s="16" t="n">
-        <v>1.39</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>1.32</v>
+        <v>4.44</v>
       </c>
       <c r="Q67" s="16" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="R67" s="16" t="n">
-        <v>-43.05</v>
+        <v>-48.76</v>
       </c>
       <c r="S67" s="16" t="n">
-        <v>10.06</v>
+        <v>26.57</v>
       </c>
       <c r="T67" s="11" t="inlineStr">
         <is>
-          <t>同步磁阻电机 -0.64%</t>
+          <t>DRG/DIP +3.25%</t>
         </is>
       </c>
     </row>
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" s="18" t="inlineStr">
         <is>
-          <t>002368</t>
+          <t>002777</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>太极股份</t>
+          <t>久远银海</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
@@ -7159,32 +7159,32 @@
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>信创、云计算、大数据、军民融合、华为概念、国产软件、小盘价值、智慧城市、智慧政务、水利建设、网络安全、跨境支付、互联网服务、工业互联网、财税数字化、创新医疗服务、DRG/DIP</t>
+          <t>信创、军工、大数据、养老概念、军民融合、华为概念、国产软件、生物识别、网络安全、互联网医疗、互联网服务、西部大开发、创新医疗服务、DRG/DIP、DeepSeek概念</t>
         </is>
       </c>
       <c r="L68" s="16" t="n">
-        <v>14.67</v>
+        <v>14.5</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>9.970000000000001</v>
+        <v>5.99</v>
       </c>
       <c r="N68" s="19" t="n">
-        <v>21.54</v>
+        <v>11.88</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>8.609999999999999</v>
+        <v>14.17</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>4.44</v>
+        <v>5.44</v>
       </c>
       <c r="Q68" s="16" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="R68" s="16" t="n">
-        <v>-48.76</v>
+        <v>-36.68</v>
       </c>
       <c r="S68" s="16" t="n">
-        <v>26.57</v>
+        <v>22.88</v>
       </c>
       <c r="T68" s="11" t="inlineStr">
         <is>
@@ -7220,135 +7220,135 @@
         </is>
       </c>
       <c r="G69" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>603716</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>塞力医疗</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>医药商业</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>信创、创新药、内贸流通、医废处理、工业大麻、生物疫苗、精准医疗、精准诊断、股权分散、脑机接口、鸿蒙概念、SPD概念、互联网医疗、体外诊断概念、创新医疗服务、医疗器械概念、DRG/DIP、AI制药（医疗）</t>
+        </is>
+      </c>
+      <c r="L69" s="16" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="M69" s="19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N69" s="24" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P69" s="16" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q69" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R69" s="16" t="n">
+        <v>-49.16</v>
+      </c>
+      <c r="S69" s="16" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="T69" s="11" t="inlineStr">
+        <is>
+          <t>DRG/DIP +3.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>10-21</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>知识产权</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>002777</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>久远银海</t>
-        </is>
-      </c>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K69" s="11" t="inlineStr">
-        <is>
-          <t>信创、军工、大数据、养老概念、军民融合、华为概念、国产软件、生物识别、网络安全、互联网医疗、互联网服务、西部大开发、创新医疗服务、DRG/DIP、DeepSeek概念</t>
-        </is>
-      </c>
-      <c r="L69" s="16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M69" s="19" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="N69" s="19" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="O69" s="16" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="P69" s="16" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="Q69" s="16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="R69" s="16" t="n">
-        <v>-36.68</v>
-      </c>
-      <c r="S69" s="16" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="T69" s="11" t="inlineStr">
-        <is>
-          <t>DRG/DIP +3.25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="38" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>10-21</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>DRG/DIP</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>DRG/DIP</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>3.25</v>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>知识产权</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="n">
+        <v>2.3</v>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G70" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>603716</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>塞力医疗</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>医药商业</t>
-        </is>
-      </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>信创、创新药、内贸流通、医废处理、工业大麻、生物疫苗、精准医疗、精准诊断、股权分散、脑机接口、鸿蒙概念、SPD概念、互联网医疗、体外诊断概念、创新医疗服务、医疗器械概念、DRG/DIP、AI制药（医疗）</t>
-        </is>
-      </c>
-      <c r="L70" s="16" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="M70" s="19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N70" s="25" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="O70" s="16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P70" s="16" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q70" s="16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R70" s="16" t="n">
-        <v>-49.16</v>
-      </c>
-      <c r="S70" s="16" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="T70" s="11" t="inlineStr">
-        <is>
-          <t>DRG/DIP +3.25%</t>
+      <c r="G70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="21" t="inlineStr">
+        <is>
+          <t>603999</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>出版</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>快手概念、知识产权、西部大开发</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="M70" s="22" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N70" s="22" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="O70" s="20" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="P70" s="20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q70" s="20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R70" s="20" t="n">
+        <v>-15.21</v>
+      </c>
+      <c r="S70" s="20" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="T70" s="5" t="inlineStr">
+        <is>
+          <t>知识产权 +2.30%</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E71" s="21" t="n">
+      <c r="E71" s="20" t="n">
         <v>2.3</v>
       </c>
       <c r="F71" s="17" t="inlineStr">
@@ -7380,16 +7380,16 @@
         </is>
       </c>
       <c r="G71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="22" t="inlineStr">
-        <is>
-          <t>603999</t>
+        <v>2</v>
+      </c>
+      <c r="H71" s="21" t="inlineStr">
+        <is>
+          <t>601999</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>读者传媒</t>
+          <t>出版传媒</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -7399,32 +7399,32 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>快手概念、知识产权、西部大开发</t>
-        </is>
-      </c>
-      <c r="L71" s="21" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="M71" s="23" t="n">
+          <t>东北振兴、在线教育、基金减仓、知识产权</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M71" s="22" t="n">
         <v>10.01</v>
       </c>
-      <c r="N71" s="23" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q71" s="21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R71" s="21" t="n">
-        <v>-15.21</v>
-      </c>
-      <c r="S71" s="21" t="n">
-        <v>51.21</v>
+      <c r="N71" s="22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O71" s="20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P71" s="20" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q71" s="20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R71" s="20" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="S71" s="20" t="n">
+        <v>44.44</v>
       </c>
       <c r="T71" s="5" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E72" s="21" t="n">
+      <c r="E72" s="20" t="n">
         <v>2.3</v>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -7460,51 +7460,51 @@
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t>601999</t>
+        <v>3</v>
+      </c>
+      <c r="H72" s="21" t="inlineStr">
+        <is>
+          <t>603721</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>中广天择</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>出版</t>
+          <t>影视院线</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>东北振兴、在线教育、基金减仓、知识产权</t>
-        </is>
-      </c>
-      <c r="L72" s="21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M72" s="23" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="N72" s="23" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O72" s="21" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="P72" s="21" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q72" s="21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R72" s="21" t="n">
-        <v>-7.14</v>
-      </c>
-      <c r="S72" s="21" t="n">
-        <v>44.44</v>
+          <t>AI语料、体育产业、影视概念、数字水印、文娱消费、旅游概念、知识产权、网红经济、职业教育、虚拟现实、超清视频、小红书概念、短剧互动游戏</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="M72" s="22" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="N72" s="22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O72" s="20" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="P72" s="20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q72" s="20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R72" s="20" t="n">
+        <v>-19.49</v>
+      </c>
+      <c r="S72" s="20" t="n">
+        <v>44.58</v>
       </c>
       <c r="T72" s="5" t="inlineStr">
         <is>
@@ -7513,82 +7513,82 @@
       </c>
     </row>
     <row r="73" ht="38" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>10-21</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>知识产权</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>知识产权</t>
-        </is>
-      </c>
-      <c r="E73" s="21" t="n">
-        <v>2.3</v>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>裸眼3D</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>裸眼3D</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>2.27</v>
       </c>
       <c r="F73" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H73" s="22" t="inlineStr">
-        <is>
-          <t>603721</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>中广天择</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>影视院线</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>AI语料、体育产业、影视概念、数字水印、文娱消费、旅游概念、知识产权、网红经济、职业教育、虚拟现实、超清视频、小红书概念、短剧互动游戏</t>
-        </is>
-      </c>
-      <c r="L73" s="21" t="n">
-        <v>20.82</v>
-      </c>
-      <c r="M73" s="23" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="N73" s="23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="O73" s="21" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="P73" s="21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q73" s="21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R73" s="21" t="n">
-        <v>-19.49</v>
-      </c>
-      <c r="S73" s="21" t="n">
-        <v>44.58</v>
-      </c>
-      <c r="T73" s="5" t="inlineStr">
-        <is>
-          <t>知识产权 +2.30%</t>
+      <c r="G73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>002587</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>奥拓电子</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>光学光电子</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>物联网、体育产业、华为概念、国产软件、在线教育、增强现实、显示技术、智慧城市、智慧灯杆、深圳特区、苹果概念、虚拟现实、裸眼3D、超清视频、LED概念、互联网金融、英伟达概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、MiniLED、MicroLED</t>
+        </is>
+      </c>
+      <c r="L73" s="16" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M73" s="19" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="N73" s="19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O73" s="16" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="P73" s="16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q73" s="16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R73" s="16" t="n">
+        <v>-28.75</v>
+      </c>
+      <c r="S73" s="16" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="T73" s="11" t="inlineStr">
+        <is>
+          <t>裸眼3D +2.27%</t>
         </is>
       </c>
     </row>
@@ -7620,16 +7620,16 @@
         </is>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>002587</t>
+          <t>000727</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>奥拓电子</t>
+          <t>冠捷科技</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
@@ -7639,32 +7639,32 @@
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>物联网、体育产业、华为概念、国产软件、在线教育、增强现实、显示技术、智慧城市、智慧灯杆、深圳特区、苹果概念、虚拟现实、裸眼3D、超清视频、LED概念、互联网金融、英伟达概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、MiniLED、MicroLED</t>
+          <t>PCB、物联网、AIPC、华为概念、在线教育、小米概念、数字阅读、显示技术、电子竞技、私募新进、虚拟现实、裸眼3D、贬值受益、长江三角、阿里概念、电子后视镜、电子纸概念</t>
         </is>
       </c>
       <c r="L74" s="16" t="n">
-        <v>5.55</v>
+        <v>2.13</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="N74" s="19" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
+      </c>
+      <c r="N74" s="24" t="n">
+        <v>-0.93</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>9.15</v>
+        <v>2.04</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q74" s="16" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="R74" s="16" t="n">
-        <v>-28.75</v>
+        <v>-29.24</v>
       </c>
       <c r="S74" s="16" t="n">
-        <v>11.45</v>
+        <v>2.9</v>
       </c>
       <c r="T74" s="11" t="inlineStr">
         <is>
@@ -7700,51 +7700,51 @@
         </is>
       </c>
       <c r="G75" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>000727</t>
+          <t>603466</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>冠捷科技</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>光学光电子</t>
+          <t>数字媒体</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>PCB、物联网、AIPC、华为概念、在线教育、小米概念、数字阅读、显示技术、电子竞技、私募新进、虚拟现实、裸眼3D、贬值受益、长江三角、阿里概念、电子后视镜、电子纸概念</t>
+          <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
         </is>
       </c>
       <c r="L75" s="16" t="n">
-        <v>2.13</v>
+        <v>14.47</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N75" s="25" t="n">
-        <v>-0.93</v>
+        <v>1.69</v>
+      </c>
+      <c r="N75" s="19" t="n">
+        <v>7.11</v>
       </c>
       <c r="O75" s="16" t="n">
-        <v>2.04</v>
+        <v>19.94</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="Q75" s="16" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="R75" s="16" t="n">
-        <v>-29.24</v>
+        <v>0</v>
       </c>
       <c r="S75" s="16" t="n">
-        <v>2.9</v>
+        <v>63.87</v>
       </c>
       <c r="T75" s="11" t="inlineStr">
         <is>
@@ -7760,19 +7760,19 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>裸眼3D</t>
+          <t>AI算力</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>裸眼3D</t>
+          <t>AI语料</t>
         </is>
       </c>
       <c r="E76" s="16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
@@ -7780,55 +7780,55 @@
         </is>
       </c>
       <c r="G76" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>603466</t>
+          <t>002591</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>恒大高新</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>数字媒体</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
+          <t>氢能源、3D打印、噪声防治、算力概念、绿色电力、节能环保、互联网服务、钠离子电池</t>
         </is>
       </c>
       <c r="L76" s="16" t="n">
-        <v>14.47</v>
+        <v>6.88</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>1.69</v>
+        <v>10.08</v>
       </c>
       <c r="N76" s="19" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="O76" s="16" t="n">
-        <v>19.94</v>
+        <v>16.49</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Q76" s="16" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="R76" s="16" t="n">
-        <v>0</v>
+        <v>-24.56</v>
       </c>
       <c r="S76" s="16" t="n">
-        <v>63.87</v>
+        <v>29.57</v>
       </c>
       <c r="T76" s="11" t="inlineStr">
         <is>
-          <t>裸眼3D +2.27%</t>
+          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
         </is>
       </c>
     </row>
@@ -7860,51 +7860,51 @@
         </is>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>002591</t>
+          <t>603330</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>恒大高新</t>
+          <t>天洋新材</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>塑料</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>氢能源、3D打印、噪声防治、算力概念、绿色电力、节能环保、互联网服务、钠离子电池</t>
+          <t>新材料、华为概念、无线耳机、网红经济、CPO概念、光通信模块、半导体概念、消费电子概念</t>
         </is>
       </c>
       <c r="L77" s="16" t="n">
-        <v>6.88</v>
+        <v>10.09</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>10.08</v>
+        <v>10.03</v>
       </c>
       <c r="N77" s="19" t="n">
-        <v>7</v>
+        <v>15.58</v>
       </c>
       <c r="O77" s="16" t="n">
-        <v>16.49</v>
+        <v>15.18</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q77" s="16" t="n">
         <v>1.31</v>
       </c>
       <c r="R77" s="16" t="n">
-        <v>-24.56</v>
+        <v>-14.13</v>
       </c>
       <c r="S77" s="16" t="n">
-        <v>29.57</v>
+        <v>68.17</v>
       </c>
       <c r="T77" s="11" t="inlineStr">
         <is>
@@ -7940,51 +7940,51 @@
         </is>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>603330</t>
+          <t>603138</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>天洋新材</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>新材料、华为概念、无线耳机、网红经济、CPO概念、光通信模块、半导体概念、消费电子概念</t>
+          <t>信创、云计算、大数据、东数西算、华为概念、基金减仓、数据中心、雄安新区</t>
         </is>
       </c>
       <c r="L78" s="16" t="n">
-        <v>10.09</v>
+        <v>15.38</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="N78" s="19" t="n">
-        <v>15.58</v>
+        <v>12.84</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>15.18</v>
+        <v>5.31</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>1.89</v>
+        <v>0.85</v>
       </c>
       <c r="Q78" s="16" t="n">
-        <v>1.31</v>
+        <v>0.67</v>
       </c>
       <c r="R78" s="16" t="n">
-        <v>-14.13</v>
+        <v>-36.18</v>
       </c>
       <c r="S78" s="16" t="n">
-        <v>68.17</v>
+        <v>34.56</v>
       </c>
       <c r="T78" s="11" t="inlineStr">
         <is>
@@ -8014,57 +8014,57 @@
       <c r="E79" s="16" t="n">
         <v>2.25</v>
       </c>
-      <c r="F79" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F79" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G79" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>601778</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>晶科科技</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>信创、云计算、大数据、东数西算、华为概念、基金减仓、数据中心、雄安新区</t>
+          <t>风能、新能源、氢能源、保险新进、储能概念、小盘成长、算力概念、绿色电力、虚拟电厂、阿里概念</t>
         </is>
       </c>
       <c r="L79" s="16" t="n">
-        <v>15.38</v>
+        <v>3.52</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>10.01</v>
+        <v>2.33</v>
       </c>
       <c r="N79" s="19" t="n">
-        <v>12.84</v>
+        <v>6.67</v>
       </c>
       <c r="O79" s="16" t="n">
-        <v>5.31</v>
+        <v>6.18</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.85</v>
+        <v>2.41</v>
       </c>
       <c r="Q79" s="16" t="n">
-        <v>0.67</v>
+        <v>1.75</v>
       </c>
       <c r="R79" s="16" t="n">
-        <v>-36.18</v>
+        <v>-53</v>
       </c>
       <c r="S79" s="16" t="n">
-        <v>34.56</v>
+        <v>10.34</v>
       </c>
       <c r="T79" s="11" t="inlineStr">
         <is>
@@ -8094,57 +8094,57 @@
       <c r="E80" s="16" t="n">
         <v>2.25</v>
       </c>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="F80" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>601778</t>
+          <t>603861</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>晶科科技</t>
+          <t>白云电器</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>风能、新能源、氢能源、保险新进、储能概念、小盘成长、算力概念、绿色电力、虚拟电厂、阿里概念</t>
+          <t>特高压、数据中心、智能电网、电网概念</t>
         </is>
       </c>
       <c r="L80" s="16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="M80" s="19" t="n">
-        <v>2.33</v>
+        <v>11.75</v>
+      </c>
+      <c r="M80" s="24" t="n">
+        <v>-6.52</v>
       </c>
       <c r="N80" s="19" t="n">
-        <v>6.67</v>
+        <v>2.53</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>6.18</v>
+        <v>5.67</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="Q80" s="16" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="R80" s="16" t="n">
-        <v>-53</v>
+        <v>-44.42</v>
       </c>
       <c r="S80" s="16" t="n">
-        <v>10.34</v>
+        <v>9.92</v>
       </c>
       <c r="T80" s="11" t="inlineStr">
         <is>
@@ -8174,57 +8174,57 @@
       <c r="E81" s="16" t="n">
         <v>2.25</v>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F81" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>603861</t>
+          <t>600633</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>白云电器</t>
+          <t>浙数文化</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>游戏Ⅱ</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>特高压、数据中心、智能电网、电网概念</t>
+          <t>大数据、腾讯云、东数西算、小盘价值、数据中心、智慧城市、电子竞技、网红经济、网络游戏、长江三角、阿里概念、互联网医疗</t>
         </is>
       </c>
       <c r="L81" s="16" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="M81" s="25" t="n">
-        <v>-6.52</v>
+        <v>11.1</v>
+      </c>
+      <c r="M81" s="19" t="n">
+        <v>3.74</v>
       </c>
       <c r="N81" s="19" t="n">
-        <v>2.53</v>
+        <v>2.21</v>
       </c>
       <c r="O81" s="16" t="n">
-        <v>5.67</v>
+        <v>3.25</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="Q81" s="16" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="R81" s="16" t="n">
-        <v>-44.42</v>
+        <v>-35.24</v>
       </c>
       <c r="S81" s="16" t="n">
-        <v>9.92</v>
+        <v>12.92</v>
       </c>
       <c r="T81" s="11" t="inlineStr">
         <is>
@@ -8240,75 +8240,75 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>AI算力</t>
+          <t>软件信创</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>AI语料</t>
+          <t>财税数字化</t>
         </is>
       </c>
       <c r="E82" s="16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F82" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
+        <v>2.03</v>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
         </is>
       </c>
       <c r="G82" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>600633</t>
+          <t>603138</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>浙数文化</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>游戏Ⅱ</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>大数据、腾讯云、东数西算、小盘价值、数据中心、智慧城市、电子竞技、网红经济、网络游戏、长江三角、阿里概念、互联网医疗</t>
+          <t>信创、云计算、大数据、东数西算、华为概念、基金减仓、数据中心、雄安新区</t>
         </is>
       </c>
       <c r="L82" s="16" t="n">
-        <v>11.1</v>
+        <v>15.38</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>3.74</v>
+        <v>10.01</v>
       </c>
       <c r="N82" s="19" t="n">
-        <v>2.21</v>
+        <v>12.84</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>3.25</v>
+        <v>5.31</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>2.23</v>
+        <v>0.85</v>
       </c>
       <c r="Q82" s="16" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="R82" s="16" t="n">
-        <v>-35.24</v>
+        <v>-36.18</v>
       </c>
       <c r="S82" s="16" t="n">
-        <v>12.92</v>
+        <v>34.56</v>
       </c>
       <c r="T82" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
         </is>
       </c>
     </row>
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>603636</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -8359,32 +8359,32 @@
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>信创、云计算、大数据、东数西算、华为概念、基金减仓、数据中心、雄安新区</t>
+          <t>云计算、大数据、物联网、乡村振兴、华为昇腾、国产软件、在线教育、房屋检测、数字水印、数据安全、智慧城市、智慧政务、算力概念、网络安全、阿里概念、PPP模式、互联网服务、电子身份证、AIGC概念、短剧互动游戏、蚂蚁金服概念、DeepSeek概念</t>
         </is>
       </c>
       <c r="L83" s="16" t="n">
-        <v>15.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M83" s="19" t="n">
         <v>10.01</v>
       </c>
       <c r="N83" s="19" t="n">
-        <v>12.84</v>
+        <v>30.23</v>
       </c>
       <c r="O83" s="16" t="n">
-        <v>5.31</v>
+        <v>15.92</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q83" s="16" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="R83" s="16" t="n">
-        <v>-36.18</v>
+        <v>-32.74</v>
       </c>
       <c r="S83" s="16" t="n">
-        <v>34.56</v>
+        <v>63</v>
       </c>
       <c r="T83" s="11" t="inlineStr">
         <is>
@@ -8420,51 +8420,51 @@
         </is>
       </c>
       <c r="G84" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>603636</t>
+          <t>002929</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>通信服务</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>云计算、大数据、物联网、乡村振兴、华为昇腾、国产软件、在线教育、房屋检测、数字水印、数据安全、智慧城市、智慧政务、算力概念、网络安全、阿里概念、PPP模式、互联网服务、电子身份证、AIGC概念、短剧互动游戏、蚂蚁金服概念、DeepSeek概念</t>
+          <t>信创、风能、云计算、充电桩、大数据、新能源、无人机、5G概念、东数西算、储能概念、华为概念、基金减仓、数据中心、智慧灯杆、智能电网、电网概念、百度概念、私募重仓、算力概念、虚拟现实、虚拟电厂、通信技术、阿里概念、雄安新区、多模态AI、虚拟机器人、西部大开发</t>
         </is>
       </c>
       <c r="L84" s="16" t="n">
-        <v>9.779999999999999</v>
+        <v>56.14</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="N84" s="19" t="n">
-        <v>30.23</v>
+        <v>32</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>15.92</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q84" s="16" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="R84" s="16" t="n">
-        <v>-32.74</v>
+        <v>-42.55</v>
       </c>
       <c r="S84" s="16" t="n">
-        <v>63</v>
+        <v>46.92</v>
       </c>
       <c r="T84" s="11" t="inlineStr">
         <is>
@@ -8494,141 +8494,141 @@
       <c r="E85" s="16" t="n">
         <v>2.03</v>
       </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>603927</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>中科软</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>软件开发</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>信创、云计算、大数据、华为概念、国产软件、私募新进、网络安全、跨境支付、鸿蒙概念、互联网医疗、互联网金融、车联网(车路云)、DeepSeek概念</t>
+        </is>
+      </c>
+      <c r="L85" s="16" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="M85" s="19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N85" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P85" s="16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q85" s="16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R85" s="16" t="n">
+        <v>-34.53</v>
+      </c>
+      <c r="S85" s="16" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="T85" s="11" t="inlineStr">
+        <is>
+          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="38" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>WiFi</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>WiFi</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G85" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H85" s="18" t="inlineStr">
-        <is>
-          <t>002929</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>润建股份</t>
-        </is>
-      </c>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>通信服务</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr">
-        <is>
-          <t>信创、风能、云计算、充电桩、大数据、新能源、无人机、5G概念、东数西算、储能概念、华为概念、基金减仓、数据中心、智慧灯杆、智能电网、电网概念、百度概念、私募重仓、算力概念、虚拟现实、虚拟电厂、通信技术、阿里概念、雄安新区、多模态AI、虚拟机器人、西部大开发</t>
-        </is>
-      </c>
-      <c r="L85" s="16" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="M85" s="19" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N85" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="O85" s="16" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="P85" s="16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q85" s="16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R85" s="16" t="n">
-        <v>-42.55</v>
-      </c>
-      <c r="S85" s="16" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="T85" s="11" t="inlineStr">
-        <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="38" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>10-21</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>软件信创</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>财税数字化</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F86" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="18" t="inlineStr">
-        <is>
-          <t>603927</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>中科软</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>软件开发</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>信创、云计算、大数据、华为概念、国产软件、私募新进、网络安全、跨境支付、鸿蒙概念、互联网医疗、互联网金融、车联网(车路云)、DeepSeek概念</t>
-        </is>
-      </c>
-      <c r="L86" s="16" t="n">
-        <v>14.37</v>
-      </c>
-      <c r="M86" s="19" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N86" s="19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O86" s="16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P86" s="16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q86" s="16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R86" s="16" t="n">
-        <v>-34.53</v>
-      </c>
-      <c r="S86" s="16" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="T86" s="11" t="inlineStr">
-        <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+      <c r="G86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="21" t="inlineStr">
+        <is>
+          <t>603068</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>博通集成</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
+        </is>
+      </c>
+      <c r="L86" s="20" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="M86" s="22" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N86" s="22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O86" s="20" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="P86" s="20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Q86" s="20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R86" s="20" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="S86" s="20" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="T86" s="5" t="inlineStr">
+        <is>
+          <t>WiFi +4.18%</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E87" s="21" t="n">
+      <c r="E87" s="20" t="n">
         <v>4.18</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
@@ -8660,51 +8660,51 @@
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="22" t="inlineStr">
-        <is>
-          <t>603068</t>
+        <v>2</v>
+      </c>
+      <c r="H87" s="21" t="inlineStr">
+        <is>
+          <t>001388</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>信通电子</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
-        </is>
-      </c>
-      <c r="L87" s="21" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="M87" s="23" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="N87" s="23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O87" s="21" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="P87" s="21" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Q87" s="21" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="R87" s="21" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="S87" s="21" t="n">
-        <v>37.52</v>
+          <t>PCB、物联网、特高压、5G概念、WiFi、国产软件、基金减仓、智能电网、机器视觉、激光雷达、算力概念、通信技术、多模态AI、工业互联网、新型工业化、电子身份证、中俄贸易概念</t>
+        </is>
+      </c>
+      <c r="L87" s="20" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="O87" s="20" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="P87" s="20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q87" s="20" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R87" s="20" t="n">
+        <v>-36.9</v>
+      </c>
+      <c r="S87" s="20" t="n">
+        <v>19.75</v>
       </c>
       <c r="T87" s="5" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E88" s="21" t="n">
+      <c r="E88" s="20" t="n">
         <v>4.18</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -8740,135 +8740,135 @@
         </is>
       </c>
       <c r="G88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" s="21" t="inlineStr">
+        <is>
+          <t>002792</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>通宇通讯</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>通信设备</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>5G概念、6G概念、WiFi、低空经济、储能概念、卫星导航、商业航天、通信技术、F5G概念、UWB概念、光通信模块、卫星互联网、毫米波概念、中俄贸易概念</t>
+        </is>
+      </c>
+      <c r="L88" s="20" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O88" s="20" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="P88" s="20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q88" s="20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R88" s="20" t="n">
+        <v>-58.3</v>
+      </c>
+      <c r="S88" s="20" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="T88" s="5" t="inlineStr">
+        <is>
+          <t>WiFi +4.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="38" customHeight="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t>001388</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>信通电子</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>PCB、物联网、特高压、5G概念、WiFi、国产软件、基金减仓、智能电网、机器视觉、激光雷达、算力概念、通信技术、多模态AI、工业互联网、新型工业化、电子身份证、中俄贸易概念</t>
-        </is>
-      </c>
-      <c r="L88" s="21" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="M88" s="23" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N88" s="23" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="O88" s="21" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="P88" s="21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q88" s="21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="R88" s="21" t="n">
-        <v>-36.9</v>
-      </c>
-      <c r="S88" s="21" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="T88" s="5" t="inlineStr">
-        <is>
-          <t>WiFi +4.18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="38" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>WiFi</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>WiFi</t>
-        </is>
-      </c>
-      <c r="E89" s="21" t="n">
-        <v>4.18</v>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>3.93</v>
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" s="22" t="inlineStr">
-        <is>
-          <t>002792</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>通宇通讯</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>通信设备</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>5G概念、6G概念、WiFi、低空经济、储能概念、卫星导航、商业航天、通信技术、F5G概念、UWB概念、光通信模块、卫星互联网、毫米波概念、中俄贸易概念</t>
-        </is>
-      </c>
-      <c r="L89" s="21" t="n">
-        <v>29.17</v>
-      </c>
-      <c r="M89" s="23" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="N89" s="23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O89" s="21" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="P89" s="21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q89" s="21" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="R89" s="21" t="n">
-        <v>-58.3</v>
-      </c>
-      <c r="S89" s="21" t="n">
-        <v>70.78</v>
-      </c>
-      <c r="T89" s="5" t="inlineStr">
-        <is>
-          <t>WiFi +4.18%</t>
+      <c r="G89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>002164</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>通用设备</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>风能、减速器、长江三角、机器人执行器</t>
+        </is>
+      </c>
+      <c r="L89" s="16" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="M89" s="19" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N89" s="19" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="O89" s="16" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="P89" s="16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q89" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R89" s="16" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="S89" s="16" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="T89" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
         </is>
       </c>
     </row>
@@ -8900,51 +8900,51 @@
         </is>
       </c>
       <c r="G90" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>002164</t>
+          <t>603236</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、长江三角、机器人执行器</t>
+          <t>物联网、5G概念、6G概念、AI眼镜、先进封装、商业航天、小盘成长、智慧城市、智能电网、智能穿戴、机器视觉、水利建设、电网概念、通信技术、卫星互联网、毫米波概念、英伟达概念、车联网(车路云)</t>
         </is>
       </c>
       <c r="L90" s="16" t="n">
-        <v>16.16</v>
+        <v>76.11</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="N90" s="19" t="n">
-        <v>21.05</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O90" s="16" t="n">
-        <v>12.99</v>
+        <v>7.27</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q90" s="16" t="n">
-        <v>1.2</v>
+        <v>0.97</v>
       </c>
       <c r="R90" s="16" t="n">
-        <v>-9.16</v>
+        <v>-0.28</v>
       </c>
       <c r="S90" s="16" t="n">
-        <v>60.32</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="T90" s="11" t="inlineStr">
         <is>
@@ -8980,51 +8980,51 @@
         </is>
       </c>
       <c r="G91" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>603236</t>
+          <t>605389</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>长龄液压</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>物联网、5G概念、6G概念、AI眼镜、先进封装、商业航天、小盘成长、智慧城市、智能电网、智能穿戴、机器视觉、水利建设、电网概念、通信技术、卫星互联网、毫米波概念、英伟达概念、车联网(车路云)</t>
+          <t>减速器、小盘成长、工程机械概念</t>
         </is>
       </c>
       <c r="L91" s="16" t="n">
-        <v>76.11</v>
+        <v>57.97</v>
       </c>
       <c r="M91" s="19" t="n">
         <v>10</v>
       </c>
       <c r="N91" s="19" t="n">
-        <v>8.130000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="O91" s="16" t="n">
-        <v>7.27</v>
+        <v>0.68</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="Q91" s="16" t="n">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="R91" s="16" t="n">
-        <v>-0.28</v>
+        <v>-41.76</v>
       </c>
       <c r="S91" s="16" t="n">
-        <v>69.84999999999999</v>
+        <v>24.99</v>
       </c>
       <c r="T91" s="11" t="inlineStr">
         <is>
@@ -9054,141 +9054,141 @@
       <c r="E92" s="16" t="n">
         <v>3.93</v>
       </c>
-      <c r="F92" s="17" t="inlineStr">
+      <c r="F92" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>002933</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>新兴装备</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>航空装备Ⅱ</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>军工、无人机、低空经济、军民融合、航天航空、机器人执行器</t>
+        </is>
+      </c>
+      <c r="L92" s="16" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="M92" s="24" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="N92" s="19" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="O92" s="16" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="P92" s="16" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q92" s="16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R92" s="16" t="n">
+        <v>-25.41</v>
+      </c>
+      <c r="S92" s="16" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="T92" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="38" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G92" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H92" s="18" t="inlineStr">
-        <is>
-          <t>605389</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>长龄液压</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr">
-        <is>
-          <t>工程机械</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>减速器、小盘成长、工程机械概念</t>
-        </is>
-      </c>
-      <c r="L92" s="16" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="M92" s="19" t="n">
+      <c r="G93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>603893</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>瑞芯微</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>物联网、AI眼镜、AI芯片、华为概念、国产芯片、大盘成长、百度概念、虚拟现实、高市净率、EDR概念、半导体概念</t>
+        </is>
+      </c>
+      <c r="L93" s="20" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="M93" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="N92" s="19" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="O92" s="16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="P92" s="16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q92" s="16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R92" s="16" t="n">
-        <v>-41.76</v>
-      </c>
-      <c r="S92" s="16" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="T92" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="38" customHeight="1">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉</t>
-        </is>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="18" t="inlineStr">
-        <is>
-          <t>002933</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>新兴装备</t>
-        </is>
-      </c>
-      <c r="J93" s="11" t="inlineStr">
-        <is>
-          <t>航空装备Ⅱ</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>军工、无人机、低空经济、军民融合、航天航空、机器人执行器</t>
-        </is>
-      </c>
-      <c r="L93" s="16" t="n">
-        <v>28.18</v>
-      </c>
-      <c r="M93" s="25" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="N93" s="19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="O93" s="16" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="P93" s="16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="Q93" s="16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R93" s="16" t="n">
-        <v>-25.41</v>
-      </c>
-      <c r="S93" s="16" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="T93" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
+      <c r="N93" s="23" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="O93" s="20" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P93" s="20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q93" s="20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R93" s="20" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="S93" s="20" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="T93" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片 +3.93%</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E94" s="21" t="n">
+      <c r="E94" s="20" t="n">
         <v>3.93</v>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -9220,51 +9220,51 @@
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t>603893</t>
+        <v>2</v>
+      </c>
+      <c r="H94" s="21" t="inlineStr">
+        <is>
+          <t>002195</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>岩山科技</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>物联网、AI眼镜、AI芯片、华为概念、国产芯片、大盘成长、百度概念、虚拟现实、高市净率、EDR概念、半导体概念</t>
-        </is>
-      </c>
-      <c r="L94" s="21" t="n">
-        <v>189.04</v>
-      </c>
-      <c r="M94" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N94" s="24" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="O94" s="21" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="P94" s="21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q94" s="21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R94" s="21" t="n">
-        <v>-16.96</v>
-      </c>
-      <c r="S94" s="21" t="n">
-        <v>30.62</v>
+          <t>大数据、AIPC、AI芯片、AI语料、中盘成长、华为概念、国产软件、百度概念、网络安全、网络游戏、股权分散、脑机接口、长江三角、阿里概念、首发经济、鸿蒙概念、互联网服务、互联网金融、多模态AI、AIGC概念、短剧互动游戏、AI制药（医疗）、抖音概念(字节概念)</t>
+        </is>
+      </c>
+      <c r="L94" s="20" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N94" s="23" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="O94" s="20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P94" s="20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q94" s="20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R94" s="20" t="n">
+        <v>-55.42</v>
+      </c>
+      <c r="S94" s="20" t="n">
+        <v>2.8</v>
       </c>
       <c r="T94" s="5" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E95" s="21" t="n">
+      <c r="E95" s="20" t="n">
         <v>3.93</v>
       </c>
       <c r="F95" s="17" t="inlineStr">
@@ -9300,135 +9300,135 @@
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H95" s="22" t="inlineStr">
-        <is>
-          <t>002195</t>
+        <v>3</v>
+      </c>
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>002049</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>岩山科技</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>军工、ETC、大飞机、碳化硅、蓝宝石、5G概念、AI芯片、商业航天、国产芯片、存储芯片、汽车芯片、算力概念、通信技术、半导体概念、卫星互联网、高带宽内存、IGBT概念、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L95" s="20" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N95" s="23" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="O95" s="20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P95" s="20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q95" s="20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R95" s="20" t="n">
+        <v>-41.64</v>
+      </c>
+      <c r="S95" s="20" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="T95" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片 +3.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="38" customHeight="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>605398</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>新炬网络</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
           <t>IT服务Ⅱ</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>大数据、AIPC、AI芯片、AI语料、中盘成长、华为概念、国产软件、百度概念、网络安全、网络游戏、股权分散、脑机接口、长江三角、阿里概念、首发经济、鸿蒙概念、互联网服务、互联网金融、多模态AI、AIGC概念、短剧互动游戏、AI制药（医疗）、抖音概念(字节概念)</t>
-        </is>
-      </c>
-      <c r="L95" s="21" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="M95" s="23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N95" s="24" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="O95" s="21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P95" s="21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q95" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R95" s="21" t="n">
-        <v>-55.42</v>
-      </c>
-      <c r="S95" s="21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T95" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片 +3.93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="38" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="E96" s="21" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F96" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H96" s="22" t="inlineStr">
-        <is>
-          <t>002049</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>紫光国微</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="inlineStr">
-        <is>
-          <t>军工、ETC、大飞机、碳化硅、蓝宝石、5G概念、AI芯片、商业航天、国产芯片、存储芯片、汽车芯片、算力概念、通信技术、半导体概念、卫星互联网、高带宽内存、IGBT概念、车联网(车路云)</t>
-        </is>
-      </c>
-      <c r="L96" s="21" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="M96" s="23" t="n">
-        <v>2.6</v>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
+        </is>
+      </c>
+      <c r="L96" s="16" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="M96" s="19" t="n">
+        <v>0.57</v>
       </c>
       <c r="N96" s="24" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="O96" s="21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P96" s="21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q96" s="21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R96" s="21" t="n">
-        <v>-41.64</v>
-      </c>
-      <c r="S96" s="21" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="T96" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片 +3.93%</t>
+        <v>-3.7</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P96" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q96" s="16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R96" s="16" t="n">
+        <v>-34.9</v>
+      </c>
+      <c r="S96" s="16" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="T96" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念 +3.92%</t>
         </is>
       </c>
     </row>
@@ -9460,16 +9460,16 @@
         </is>
       </c>
       <c r="G97" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>605398</t>
+          <t>002232</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>新炬网络</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
@@ -9479,32 +9479,32 @@
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
+          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L97" s="16" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="M97" s="19" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M97" s="24" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N97" s="24" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="O97" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P97" s="16" t="n">
         <v>0.57</v>
       </c>
-      <c r="N97" s="25" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="O97" s="16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P97" s="16" t="n">
-        <v>0.6</v>
-      </c>
       <c r="Q97" s="16" t="n">
-        <v>0.92</v>
+        <v>0.61</v>
       </c>
       <c r="R97" s="16" t="n">
-        <v>-34.9</v>
+        <v>-29.21</v>
       </c>
       <c r="S97" s="16" t="n">
-        <v>26.71</v>
+        <v>18.86</v>
       </c>
       <c r="T97" s="11" t="inlineStr">
         <is>
@@ -9520,19 +9520,19 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>无线耳机/无线充电</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>无线耳机</t>
         </is>
       </c>
       <c r="E98" s="16" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
@@ -9540,55 +9540,55 @@
         </is>
       </c>
       <c r="G98" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>002232</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>启明信息</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>塑料</t>
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
+          <t>传感器、新材料、AI手机、华为概念、基金减仓、无线充电、智能穿戴、节能环保、苹果概念、降解塑料、消费电子概念</t>
         </is>
       </c>
       <c r="L98" s="16" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="M98" s="25" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="N98" s="25" t="n">
-        <v>-3.28</v>
+        <v>30.99</v>
+      </c>
+      <c r="M98" s="19" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N98" s="19" t="n">
+        <v>13.89</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="Q98" s="16" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="R98" s="16" t="n">
-        <v>-29.21</v>
+        <v>-34.41</v>
       </c>
       <c r="S98" s="16" t="n">
-        <v>18.86</v>
+        <v>37.43</v>
       </c>
       <c r="T98" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念 +3.92%</t>
+          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>
@@ -9620,51 +9620,51 @@
         </is>
       </c>
       <c r="G99" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>603068</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>博通集成</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>塑料</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>传感器、新材料、AI手机、华为概念、基金减仓、无线充电、智能穿戴、节能环保、苹果概念、降解塑料、消费电子概念</t>
+          <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
         </is>
       </c>
       <c r="L99" s="16" t="n">
-        <v>30.99</v>
+        <v>41.67</v>
       </c>
       <c r="M99" s="19" t="n">
         <v>10.01</v>
       </c>
       <c r="N99" s="19" t="n">
-        <v>13.89</v>
+        <v>1.51</v>
       </c>
       <c r="O99" s="16" t="n">
-        <v>1.61</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="Q99" s="16" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="R99" s="16" t="n">
-        <v>-34.41</v>
+        <v>-14.1</v>
       </c>
       <c r="S99" s="16" t="n">
-        <v>37.43</v>
+        <v>37.52</v>
       </c>
       <c r="T99" s="11" t="inlineStr">
         <is>
@@ -9700,51 +9700,51 @@
         </is>
       </c>
       <c r="G100" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>603068</t>
+          <t>603626</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>科森科技</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
+          <t>电子烟、储能概念、华为概念、固态电池、基金减仓、无线耳机、苹果概念、虚拟现实、特斯拉概念、医疗器械概念、消费电子概念、柔性屏(折叠屏)</t>
         </is>
       </c>
       <c r="L100" s="16" t="n">
-        <v>41.67</v>
+        <v>24.43</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="N100" s="19" t="n">
-        <v>1.51</v>
+        <v>4.54</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>8.279999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q100" s="16" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="R100" s="16" t="n">
-        <v>-14.1</v>
+        <v>-12.94</v>
       </c>
       <c r="S100" s="16" t="n">
-        <v>37.52</v>
+        <v>114.11</v>
       </c>
       <c r="T100" s="11" t="inlineStr">
         <is>
@@ -9774,22 +9774,22 @@
       <c r="E101" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="F101" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+      <c r="F101" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G101" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
-          <t>603626</t>
+          <t>002351</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>科森科技</t>
+          <t>漫步者</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
@@ -9799,32 +9799,32 @@
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>电子烟、储能概念、华为概念、固态电池、基金减仓、无线耳机、苹果概念、虚拟现实、特斯拉概念、医疗器械概念、消费电子概念、柔性屏(折叠屏)</t>
+          <t>无线耳机、智能穿戴、深圳特区、电子竞技、社保新进、消费电子概念、DeepSeek概念</t>
         </is>
       </c>
       <c r="L101" s="16" t="n">
-        <v>24.43</v>
+        <v>10.26</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>10</v>
+        <v>3.22</v>
       </c>
       <c r="N101" s="19" t="n">
-        <v>4.54</v>
+        <v>4.16</v>
       </c>
       <c r="O101" s="16" t="n">
-        <v>6.63</v>
+        <v>2.91</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="Q101" s="16" t="n">
-        <v>0.74</v>
+        <v>1.33</v>
       </c>
       <c r="R101" s="16" t="n">
-        <v>-12.94</v>
+        <v>-25.92</v>
       </c>
       <c r="S101" s="16" t="n">
-        <v>114.11</v>
+        <v>13.12</v>
       </c>
       <c r="T101" s="11" t="inlineStr">
         <is>
@@ -9854,57 +9854,57 @@
       <c r="E102" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="F102" s="20" t="inlineStr">
+      <c r="F102" s="25" t="inlineStr">
         <is>
           <t>放量低位反转</t>
         </is>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>002351</t>
+          <t>001696</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>漫步者</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>无线耳机、智能穿戴、深圳特区、电子竞技、社保新进、消费电子概念、DeepSeek概念</t>
+          <t>军工、无人机、氢能源、交运设备、低空经济、保险新进、储能概念、军民融合、地摊经济、成渝特区、数据中心、无线充电、电池技术、通用航空、发电机概念、西部大开发、燃料电池概念</t>
         </is>
       </c>
       <c r="L102" s="16" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="M102" s="19" t="n">
-        <v>3.22</v>
+        <v>15.77</v>
+      </c>
+      <c r="M102" s="24" t="n">
+        <v>-0.88</v>
       </c>
       <c r="N102" s="19" t="n">
-        <v>4.16</v>
+        <v>7.87</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>2.91</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="Q102" s="16" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="R102" s="16" t="n">
-        <v>-25.92</v>
+        <v>-37.77</v>
       </c>
       <c r="S102" s="16" t="n">
-        <v>13.12</v>
+        <v>14.11</v>
       </c>
       <c r="T102" s="11" t="inlineStr">
         <is>
@@ -9912,88 +9912,8 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="38" customHeight="1">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>无线耳机/无线充电</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F103" s="20" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H103" s="18" t="inlineStr">
-        <is>
-          <t>001696</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="inlineStr">
-        <is>
-          <t>宗申动力</t>
-        </is>
-      </c>
-      <c r="J103" s="11" t="inlineStr">
-        <is>
-          <t>通用设备</t>
-        </is>
-      </c>
-      <c r="K103" s="11" t="inlineStr">
-        <is>
-          <t>军工、无人机、氢能源、交运设备、低空经济、保险新进、储能概念、军民融合、地摊经济、成渝特区、数据中心、无线充电、电池技术、通用航空、发电机概念、西部大开发、燃料电池概念</t>
-        </is>
-      </c>
-      <c r="L103" s="16" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="M103" s="25" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="N103" s="19" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="O103" s="16" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="P103" s="16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q103" s="16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R103" s="16" t="n">
-        <v>-37.77</v>
-      </c>
-      <c r="S103" s="16" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="T103" s="11" t="inlineStr">
-        <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:T103"/>
+  <autoFilter ref="A3:T102"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>

--- a/data/theme_strength_latest.xlsx
+++ b/data/theme_strength_latest.xlsx
@@ -218,6 +218,9 @@
     <xf numFmtId="2" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -228,9 +231,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,7 +636,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>截至 2026-10-26  2026-10-26 14:21｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：东财概念板块日线</t>
+          <t>截至 2026-10-26  2026-10-26 14:55｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：成分股等权还原（东财板块日线不完整）</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
         <v>3.54</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>2</v>
@@ -828,13 +828,13 @@
       <c r="K5" s="7" t="n"/>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="9" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="N5" s="10" t="n">
         <v>2</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="P5" s="10" t="n">
         <v>1</v>
@@ -842,10 +842,10 @@
       <c r="Q5" s="7" t="n"/>
       <c r="R5" s="8" t="n"/>
       <c r="S5" s="9" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -924,10 +924,10 @@
         <v>4.69</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
@@ -943,17 +943,17 @@
         <v>5.45</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="8" t="n"/>
       <c r="Q7" s="7" t="n"/>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="9" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="T7" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -973,7 +973,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="12" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>1</v>
@@ -1007,7 +1007,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
+          <t>快递概念</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>2</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="12" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>3</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>3</v>
@@ -1103,7 +1103,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>快递概念</t>
+          <t>电子竞技</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L11" s="10" t="n">
         <v>4</v>
@@ -1151,7 +1151,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>免税概念</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="12" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>5</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>5</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="n">
-        <v>4.18</v>
+        <v>4.02</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>1</v>
@@ -1238,7 +1238,7 @@
       <c r="Q13" s="7" t="n"/>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="9" t="n">
-        <v>4.18</v>
+        <v>4.02</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2</v>
@@ -1332,7 +1332,7 @@
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="8" t="n"/>
       <c r="Q15" s="9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>2</v>
@@ -1391,7 +1391,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>AI芯片</t>
+          <t>虚拟机器人</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="n">
-        <v>3.93</v>
+        <v>5.59</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>3</v>
@@ -1418,28 +1418,28 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>10-23</t>
         </is>
       </c>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="8" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="8" t="n"/>
+      <c r="M17" s="9" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="O17" s="7" t="n"/>
       <c r="P17" s="8" t="n"/>
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="8" t="n"/>
-      <c r="S17" s="9" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="T17" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="8" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>裸眼3D</t>
+          <t>AI芯片</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="12" t="n">
-        <v>2.27</v>
+        <v>3.86</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>3</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>10-21</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="K18" s="7" t="n"/>
@@ -1475,19 +1475,19 @@
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="7" t="n"/>
       <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="R18" s="13" t="n">
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="9" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="T18" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="S18" s="7" t="n"/>
-      <c r="T18" s="8" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>工程机械概念</t>
+          <t>裸眼3D</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="n">
-        <v>-0.23</v>
+        <v>2.27</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>3</v>
@@ -1514,28 +1514,28 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>10-22</t>
+          <t>10-21</t>
         </is>
       </c>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="8" t="n"/>
-      <c r="O19" s="14" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="P19" s="10" t="n">
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="8" t="n"/>
       <c r="S19" s="7" t="n"/>
       <c r="T19" s="8" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>虚拟机器人</t>
+          <t>工程机械概念</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -1549,32 +1549,32 @@
       </c>
       <c r="E20" s="12" t="inlineStr"/>
       <c r="F20" s="12" t="n">
-        <v>5.34</v>
+        <v>-0.5</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>10-23</t>
+          <t>10-22</t>
         </is>
       </c>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="9" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="N20" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="8" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>3</v>
+      </c>
       <c r="Q20" s="7" t="n"/>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="7" t="n"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>4</v>
@@ -1620,7 +1620,7 @@
       <c r="O21" s="7" t="n"/>
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="9" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>4</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>5</v>
@@ -1718,7 +1718,7 @@
       <c r="Q23" s="7" t="n"/>
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T23" s="10" t="n">
         <v>5</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr"/>
       <c r="F24" s="12" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>5</v>
@@ -1764,7 +1764,7 @@
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="9" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>5</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
@@ -2052,13 +2052,13 @@
         <v>7.79</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="P4" s="16" t="n">
-        <v>3.66</v>
+        <v>3.31</v>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="R4" s="16" t="n">
         <v>-23.93</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="T4" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.72%</t>
+          <t>SPD概念 +2.78%</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         <v>12.62</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>8.609999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="P5" s="16" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="R5" s="16" t="n">
         <v>-44.79</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="T5" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.72%</t>
+          <t>SPD概念 +2.78%</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
@@ -2203,272 +2203,272 @@
         </is>
       </c>
       <c r="L6" s="16" t="n">
-        <v>16.84</v>
+        <v>16.83</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
       <c r="N6" s="19" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Q6" s="16" t="n">
         <v>1.06</v>
       </c>
       <c r="R6" s="16" t="n">
-        <v>-5.61</v>
+        <v>-5.66</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>13.48</v>
+        <v>13.41</v>
       </c>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.72%</t>
+          <t>SPD概念 +2.78%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>2.06</v>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>2.08</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>601808</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>中海油服</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>油服工程</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰、天然气、油气设服、油气资源、海工装备、行业龙头、资源开采概念</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="O7" s="20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P7" s="20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q7" s="20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R7" s="20" t="n">
-        <v>-33.63</v>
-      </c>
-      <c r="S7" s="20" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰 +2.06%</t>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>001317</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>铁路公路</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="M7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="20" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>-21.36</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.08%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>2.06</v>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>2.08</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>002278</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>神开股份</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>专用设备</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰、无人机、氢能源、碳纤维、页岩气、低空经济、商业航天、油气设服、油气资源、海工装备、长江三角、中俄贸易概念</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O8" s="20" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="P8" s="20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q8" s="20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R8" s="20" t="n">
-        <v>-49.75</v>
-      </c>
-      <c r="S8" s="20" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰 +2.06%</t>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>002468</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>申通快递</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>大数据、小盘价值、快递概念、阿里概念</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="N8" s="19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O8" s="16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P8" s="16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q8" s="16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R8" s="16" t="n">
+        <v>-18.01</v>
+      </c>
+      <c r="S8" s="16" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.08%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>2.06</v>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>2.08</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>000039</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>中集集团</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>通用设备</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>风能、可燃冰、天然气、氢能源、物联网、冷链物流、商业航天、数据中心、油气资源、海工装备、深圳特区、社保新进、雄安新区</t>
-        </is>
-      </c>
-      <c r="L9" s="20" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="O9" s="20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P9" s="20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q9" s="20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R9" s="20" t="n">
-        <v>-36.17</v>
-      </c>
-      <c r="S9" s="20" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>可燃冰 +2.06%</t>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>601598</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>中国外运</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>中盘价值、冷链物流、快递概念、跨境电商、统一大市场</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M9" s="19" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="N9" s="20" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P9" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R9" s="16" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="S9" s="16" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.08%</t>
         </is>
       </c>
     </row>
@@ -2491,8 +2491,8 @@
           <t>乳业</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
-        <v>2.04</v>
+      <c r="E10" s="21" t="n">
+        <v>1.96</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       <c r="G10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>001219</t>
         </is>
@@ -2522,33 +2522,33 @@
           <t>乳业、婴童概念、电商概念、网红经济、调味品概念</t>
         </is>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="L10" s="21" t="n">
         <v>13.62</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="23" t="n">
         <v>10.02</v>
       </c>
-      <c r="N10" s="22" t="n">
+      <c r="N10" s="23" t="n">
         <v>9.66</v>
       </c>
-      <c r="O10" s="20" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="P10" s="20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Q10" s="20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R10" s="20" t="n">
+      <c r="O10" s="21" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P10" s="21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q10" s="21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R10" s="21" t="n">
         <v>-12.36</v>
       </c>
-      <c r="S10" s="20" t="n">
+      <c r="S10" s="21" t="n">
         <v>18.85</v>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>乳业 +2.04%</t>
+          <t>乳业 +1.96%</t>
         </is>
       </c>
     </row>
@@ -2571,8 +2571,8 @@
           <t>乳业</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
-        <v>2.04</v>
+      <c r="E11" s="21" t="n">
+        <v>1.96</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       <c r="G11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>001318</t>
         </is>
@@ -2602,33 +2602,33 @@
           <t>乳业、味蕾经济、婴童概念</t>
         </is>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" s="21" t="n">
         <v>12.1</v>
       </c>
-      <c r="M11" s="22" t="n">
+      <c r="M11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="24" t="n">
         <v>-11.94</v>
       </c>
-      <c r="O11" s="20" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="P11" s="20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q11" s="20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R11" s="20" t="n">
+      <c r="O11" s="21" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R11" s="21" t="n">
         <v>-30.22</v>
       </c>
-      <c r="S11" s="20" t="n">
+      <c r="S11" s="21" t="n">
         <v>26.57</v>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>乳业 +2.04%</t>
+          <t>乳业 +1.96%</t>
         </is>
       </c>
     </row>
@@ -2651,8 +2651,8 @@
           <t>乳业</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>2.04</v>
+      <c r="E12" s="21" t="n">
+        <v>1.96</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       <c r="G12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>603719</t>
         </is>
@@ -2682,273 +2682,273 @@
           <t>乳业、内贸流通、电商概念、社区团购、网红经济、谷子经济</t>
         </is>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="L12" s="21" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="M12" s="22" t="n">
+      <c r="M12" s="23" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="N12" s="22" t="n">
+      <c r="N12" s="23" t="n">
         <v>6.7</v>
       </c>
-      <c r="O12" s="20" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P12" s="20" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q12" s="20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R12" s="20" t="n">
+      <c r="O12" s="21" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P12" s="21" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="Q12" s="21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R12" s="21" t="n">
         <v>-26.35</v>
       </c>
-      <c r="S12" s="20" t="n">
+      <c r="S12" s="21" t="n">
         <v>14.65</v>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>乳业 +2.04%</t>
+          <t>乳业 +1.96%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>1.84</v>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>1.94</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>001317</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>三羊马</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>铁路公路</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N13" s="24" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="O13" s="16" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="P13" s="16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q13" s="16" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="R13" s="16" t="n">
-        <v>-23.79</v>
-      </c>
-      <c r="S13" s="16" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.84%</t>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>603258</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>电魂网络</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>游戏Ⅱ</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>文娱消费、电子竞技、网络游戏、虚拟现实、谷子经济、AIGC概念、短剧互动游戏</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M13" s="23" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="O13" s="21" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="P13" s="21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q13" s="21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R13" s="21" t="n">
+        <v>-26.02</v>
+      </c>
+      <c r="S13" s="21" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技 +1.94%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1.84</v>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>1.94</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>601598</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>中国外运</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>中盘价值、冷链物流、快递概念、跨境电商、统一大市场</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="O14" s="16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P14" s="16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Q14" s="16" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="R14" s="16" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="S14" s="16" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.84%</t>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>001308</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>康冠科技</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>光学光电子</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>AIPC、AI眼镜、OLED、华为概念、小盘价值、智能电视、智能穿戴、深圳特区、电子竞技、虚拟现实、贬值受益、医疗器械概念、消费电子概念、MiniLED、抖音概念(字节概念)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="M14" s="23" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R14" s="21" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="S14" s="21" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技 +1.94%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>10-26午盘</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>1.84</v>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>1.94</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>002468</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>申通快递</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>大数据、小盘价值、快递概念、阿里概念</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="N15" s="19" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O15" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P15" s="16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q15" s="16" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="R15" s="16" t="n">
-        <v>-18.63</v>
-      </c>
-      <c r="S15" s="16" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +1.84%</t>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>002517</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>恺英网络</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>游戏Ⅱ</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>AI眼镜、华为概念、文娱消费、电子竞技、网络游戏、虚拟现实、短剧互动游戏</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="M15" s="23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O15" s="21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P15" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q15" s="21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R15" s="21" t="n">
+        <v>-43.27</v>
+      </c>
+      <c r="S15" s="21" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>电子竞技 +1.94%</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -2968,11 +2968,11 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>1.77</v>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>1.89</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
@@ -2982,53 +2982,53 @@
       <c r="G16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>001979</t>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>601808</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>招商蛇口</t>
+          <t>中海油服</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>油服工程</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>低市净率、免税概念、养老概念、大盘价值、深圳特区、租售同权、行业龙头、雄安新区、零售概念、REITs概念</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M16" s="22" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="N16" s="22" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="O16" s="20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P16" s="20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q16" s="20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R16" s="20" t="n">
-        <v>-24.56</v>
-      </c>
-      <c r="S16" s="20" t="n">
-        <v>30.78</v>
+          <t>可燃冰、天然气、油气设服、油气资源、海工装备、行业龙头、资源开采概念</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="M16" s="23" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="O16" s="21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" s="21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R16" s="21" t="n">
+        <v>-33.97</v>
+      </c>
+      <c r="S16" s="21" t="n">
+        <v>24.84</v>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>免税概念 +1.77%</t>
+          <t>可燃冰 +1.89%</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>1.77</v>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>1.89</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
@@ -3062,53 +3062,53 @@
       <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>600009</t>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>002278</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>上海机场</t>
+          <t>神开股份</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>航空机场</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>免税概念、大盘成长、社保新进、长江三角、零售概念</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="M17" s="22" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N17" s="22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O17" s="20" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="P17" s="20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Q17" s="20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R17" s="20" t="n">
-        <v>-30.39</v>
-      </c>
-      <c r="S17" s="20" t="n">
-        <v>7.59</v>
+          <t>可燃冰、无人机、氢能源、碳纤维、页岩气、低空经济、商业航天、油气设服、油气资源、海工装备、长江三角、中俄贸易概念</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M17" s="23" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O17" s="21" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q17" s="21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R17" s="21" t="n">
+        <v>-50.06</v>
+      </c>
+      <c r="S17" s="21" t="n">
+        <v>10.03</v>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>免税概念 +1.77%</t>
+          <t>可燃冰 +1.89%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>免税概念</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>1.77</v>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>1.89</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
@@ -3142,53 +3142,53 @@
       <c r="G18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>600694</t>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>000039</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>大商股份</t>
+          <t>中集集团</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>通用设备</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>东北振兴、低市净率、免税概念、内贸流通、电商概念、社保新进、零售概念</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="N18" s="22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O18" s="20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P18" s="20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" s="20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R18" s="20" t="n">
-        <v>-12.99</v>
-      </c>
-      <c r="S18" s="20" t="n">
-        <v>13.91</v>
+          <t>风能、可燃冰、天然气、氢能源、物联网、冷链物流、商业航天、数据中心、油气资源、海工装备、深圳特区、社保新进、雄安新区</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P18" s="21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q18" s="21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R18" s="21" t="n">
+        <v>-36.46</v>
+      </c>
+      <c r="S18" s="21" t="n">
+        <v>17.99</v>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>免税概念 +1.77%</t>
+          <t>可燃冰 +1.89%</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="T24" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="T26" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="T28" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="T29" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="T30" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="T32" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
@@ -4388,167 +4388,167 @@
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +5.92% / 减速器 +5.13% / 机器视觉 +4.89%</t>
+          <t>机器人执行器 +6.01% / 减速器 +5.23% / 机器视觉 +4.60%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>10-23</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>5.45</v>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>5.59</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="18" t="inlineStr">
-        <is>
-          <t>605398</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>新炬网络</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K34" s="11" t="inlineStr">
-        <is>
-          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
-        </is>
-      </c>
-      <c r="L34" s="16" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N34" s="24" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P34" s="16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q34" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R34" s="16" t="n">
-        <v>-35.55</v>
-      </c>
-      <c r="S34" s="16" t="n">
-        <v>25.44</v>
-      </c>
-      <c r="T34" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念 +5.45%</t>
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>603528</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>多伦科技</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>软件开发</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>大数据、物联网、华为昇腾、华为概念、卫星导航、国产芯片、国产软件、智慧城市、职业教育、虚拟机器人、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="23" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="O34" s="21" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q34" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R34" s="21" t="n">
+        <v>-28.47</v>
+      </c>
+      <c r="S34" s="21" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人 +5.59%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="38" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>10-23</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>5.45</v>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>5.59</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>002232</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>启明信息</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
-        </is>
-      </c>
-      <c r="L35" s="16" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M35" s="24" t="n">
-        <v>-4.41</v>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>601519</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>大智慧</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>软件开发</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>大数据、华为概念、国产软件、小盘成长、数据中心、私募重仓、网红经济、长江三角、阿里概念、高市净率、鸿蒙概念、互联网金融、虚拟机器人</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M35" s="23" t="n">
+        <v>9.99</v>
       </c>
       <c r="N35" s="24" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="O35" s="16" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="P35" s="16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q35" s="16" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="R35" s="16" t="n">
-        <v>-35.24</v>
-      </c>
-      <c r="S35" s="16" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="T35" s="11" t="inlineStr">
-        <is>
-          <t>MLOps概念 +5.45%</t>
+        <v>-2.43</v>
+      </c>
+      <c r="O35" s="21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P35" s="21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q35" s="21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R35" s="21" t="n">
+        <v>-39.62</v>
+      </c>
+      <c r="S35" s="21" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人 +5.59%</t>
         </is>
       </c>
     </row>
@@ -4564,231 +4564,231 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>001314</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>亿道信息</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>PCB、物联网、AIPC、AI眼镜、在线教育、增强现实、智能穿戴、虚拟现实、虚拟机器人、消费电子概念</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="M36" s="23" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N36" s="23" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q36" s="21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R36" s="21" t="n">
+        <v>-29.48</v>
+      </c>
+      <c r="S36" s="21" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>虚拟机器人 +5.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>10-23</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>603528</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>多伦科技</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>软件开发</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>大数据、物联网、华为昇腾、华为概念、卫星导航、国产芯片、国产软件、智慧城市、职业教育、虚拟机器人、车联网(车路云)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="M36" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="N36" s="22" t="n">
-        <v>24.66</v>
-      </c>
-      <c r="O36" s="20" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="P36" s="20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Q36" s="20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R36" s="20" t="n">
-        <v>-28.47</v>
-      </c>
-      <c r="S36" s="20" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人 +5.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="G37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>605398</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>新炬网络</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>IT服务Ⅱ</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N37" s="20" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P37" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q37" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R37" s="16" t="n">
+        <v>-35.55</v>
+      </c>
+      <c r="S37" s="16" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念 +5.45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>10-23</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>601519</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>大智慧</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>软件开发</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>大数据、华为概念、国产软件、小盘成长、数据中心、私募重仓、网红经济、长江三角、阿里概念、高市净率、鸿蒙概念、互联网金融、虚拟机器人</t>
-        </is>
-      </c>
-      <c r="L37" s="20" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="M37" s="22" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N37" s="23" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="O37" s="20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P37" s="20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q37" s="20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R37" s="20" t="n">
-        <v>-39.62</v>
-      </c>
-      <c r="S37" s="20" t="n">
-        <v>24.33</v>
-      </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人 +5.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="38" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>10-23</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>001314</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>亿道信息</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>PCB、物联网、AIPC、AI眼镜、在线教育、增强现实、智能穿戴、虚拟现实、虚拟机器人、消费电子概念</t>
-        </is>
-      </c>
-      <c r="L38" s="20" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="M38" s="22" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="N38" s="22" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="O38" s="20" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="P38" s="20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q38" s="20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R38" s="20" t="n">
-        <v>-29.48</v>
-      </c>
-      <c r="S38" s="20" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>虚拟机器人 +5.34%</t>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>002232</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>启明信息</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>IT服务Ⅱ</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
+        <is>
+          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M38" s="20" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="N38" s="20" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q38" s="16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R38" s="16" t="n">
+        <v>-35.24</v>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念 +5.45%</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E39" s="20" t="n">
+      <c r="E39" s="21" t="n">
         <v>5.2</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       <c r="G39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="21" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>603466</t>
         </is>
@@ -4842,28 +4842,28 @@
           <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
         </is>
       </c>
-      <c r="L39" s="20" t="n">
+      <c r="L39" s="21" t="n">
         <v>14.69</v>
       </c>
-      <c r="M39" s="22" t="n">
+      <c r="M39" s="23" t="n">
         <v>10.04</v>
       </c>
-      <c r="N39" s="22" t="n">
+      <c r="N39" s="23" t="n">
         <v>16.22</v>
       </c>
-      <c r="O39" s="20" t="n">
+      <c r="O39" s="21" t="n">
         <v>16.7</v>
       </c>
-      <c r="P39" s="20" t="n">
+      <c r="P39" s="21" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q39" s="20" t="n">
+      <c r="Q39" s="21" t="n">
         <v>1.47</v>
       </c>
-      <c r="R39" s="20" t="n">
+      <c r="R39" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="20" t="n">
+      <c r="S39" s="21" t="n">
         <v>66.36</v>
       </c>
       <c r="T39" s="5" t="inlineStr">
@@ -4891,7 +4891,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E40" s="20" t="n">
+      <c r="E40" s="21" t="n">
         <v>5.2</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -4902,7 +4902,7 @@
       <c r="G40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>002354</t>
         </is>
@@ -4922,28 +4922,28 @@
           <t>信创、AI语料、东数西算、国产芯片、在线教育、小盘价值、文娱消费、电子竞技、百度概念、网络游戏、股权分散、虚拟现实、谷子经济、跨境电商、互联网服务、互联网金融、多模态AI、小红书概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、ChatGPT概念、DeepSeek概念、抖音概念(字节概念)</t>
         </is>
       </c>
-      <c r="L40" s="20" t="n">
+      <c r="L40" s="21" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="M40" s="22" t="n">
+      <c r="M40" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="N40" s="22" t="n">
+      <c r="N40" s="23" t="n">
         <v>11.37</v>
       </c>
-      <c r="O40" s="20" t="n">
+      <c r="O40" s="21" t="n">
         <v>17.93</v>
       </c>
-      <c r="P40" s="20" t="n">
+      <c r="P40" s="21" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q40" s="20" t="n">
+      <c r="Q40" s="21" t="n">
         <v>1.25</v>
       </c>
-      <c r="R40" s="20" t="n">
+      <c r="R40" s="21" t="n">
         <v>-22.34</v>
       </c>
-      <c r="S40" s="20" t="n">
+      <c r="S40" s="21" t="n">
         <v>48.43</v>
       </c>
       <c r="T40" s="5" t="inlineStr">
@@ -4971,7 +4971,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E41" s="20" t="n">
+      <c r="E41" s="21" t="n">
         <v>5.2</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="G41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="21" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>600446</t>
         </is>
@@ -5002,28 +5002,28 @@
           <t>信创、国产软件、数据安全、智慧城市、深圳特区、电商概念、网络安全、股权分散、互联网服务、虚拟机器人、ChatGPT概念</t>
         </is>
       </c>
-      <c r="L41" s="20" t="n">
+      <c r="L41" s="21" t="n">
         <v>10.6</v>
       </c>
-      <c r="M41" s="22" t="n">
+      <c r="M41" s="23" t="n">
         <v>5.37</v>
       </c>
-      <c r="N41" s="22" t="n">
+      <c r="N41" s="23" t="n">
         <v>3.01</v>
       </c>
-      <c r="O41" s="20" t="n">
+      <c r="O41" s="21" t="n">
         <v>3.2</v>
       </c>
-      <c r="P41" s="20" t="n">
+      <c r="P41" s="21" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q41" s="20" t="n">
+      <c r="Q41" s="21" t="n">
         <v>1.14</v>
       </c>
-      <c r="R41" s="20" t="n">
+      <c r="R41" s="21" t="n">
         <v>-40.62</v>
       </c>
-      <c r="S41" s="20" t="n">
+      <c r="S41" s="21" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="T41" s="5" t="inlineStr">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="E42" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="T42" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="T43" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="E44" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="T44" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="T45" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="E46" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T46" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="E47" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       <c r="L47" s="16" t="n">
         <v>7.29</v>
       </c>
-      <c r="M47" s="24" t="n">
+      <c r="M47" s="20" t="n">
         <v>-1.62</v>
       </c>
       <c r="N47" s="19" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="T47" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E48" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="T48" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="E49" s="16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="T49" s="11" t="inlineStr">
         <is>
-          <t>机器人执行器 +0.76% / 减速器 -0.10% / 机器视觉 -2.36%</t>
+          <t>机器人执行器 +0.77% / 减速器 -0.22% / 机器视觉 -2.78%</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E50" s="20" t="n">
+      <c r="E50" s="21" t="n">
         <v>0.16</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -5702,7 +5702,7 @@
       <c r="G50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="21" t="inlineStr">
+      <c r="H50" s="22" t="inlineStr">
         <is>
           <t>603350</t>
         </is>
@@ -5722,28 +5722,28 @@
           <t>传感器、轮毂电机</t>
         </is>
       </c>
-      <c r="L50" s="20" t="n">
+      <c r="L50" s="21" t="n">
         <v>29.48</v>
       </c>
-      <c r="M50" s="22" t="n">
+      <c r="M50" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="N50" s="22" t="n">
+      <c r="N50" s="23" t="n">
         <v>12.01</v>
       </c>
-      <c r="O50" s="20" t="n">
+      <c r="O50" s="21" t="n">
         <v>5.79</v>
       </c>
-      <c r="P50" s="20" t="n">
+      <c r="P50" s="21" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q50" s="20" t="n">
+      <c r="Q50" s="21" t="n">
         <v>1.55</v>
       </c>
-      <c r="R50" s="20" t="n">
+      <c r="R50" s="21" t="n">
         <v>-27.28</v>
       </c>
-      <c r="S50" s="20" t="n">
+      <c r="S50" s="21" t="n">
         <v>13.65</v>
       </c>
       <c r="T50" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E51" s="20" t="n">
+      <c r="E51" s="21" t="n">
         <v>0.16</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="G51" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="21" t="inlineStr">
+      <c r="H51" s="22" t="inlineStr">
         <is>
           <t>603489</t>
         </is>
@@ -5802,28 +5802,28 @@
           <t>交运设备、共享经济、轮毂电机</t>
         </is>
       </c>
-      <c r="L51" s="20" t="n">
+      <c r="L51" s="21" t="n">
         <v>27.5</v>
       </c>
-      <c r="M51" s="22" t="n">
+      <c r="M51" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="N51" s="22" t="n">
+      <c r="N51" s="23" t="n">
         <v>6.51</v>
       </c>
-      <c r="O51" s="20" t="n">
+      <c r="O51" s="21" t="n">
         <v>1.31</v>
       </c>
-      <c r="P51" s="20" t="n">
+      <c r="P51" s="21" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q51" s="20" t="n">
+      <c r="Q51" s="21" t="n">
         <v>1.06</v>
       </c>
-      <c r="R51" s="20" t="n">
+      <c r="R51" s="21" t="n">
         <v>-31.13</v>
       </c>
-      <c r="S51" s="20" t="n">
+      <c r="S51" s="21" t="n">
         <v>16.48</v>
       </c>
       <c r="T51" s="5" t="inlineStr">
@@ -5851,7 +5851,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E52" s="20" t="n">
+      <c r="E52" s="21" t="n">
         <v>0.16</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -5862,7 +5862,7 @@
       <c r="G52" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="21" t="inlineStr">
+      <c r="H52" s="22" t="inlineStr">
         <is>
           <t>002284</t>
         </is>
@@ -5882,28 +5882,28 @@
           <t>华为汽车、胎压监测、轮毂电机、长江三角、车联网(车路云)</t>
         </is>
       </c>
-      <c r="L52" s="20" t="n">
+      <c r="L52" s="21" t="n">
         <v>8.57</v>
       </c>
-      <c r="M52" s="23" t="n">
+      <c r="M52" s="24" t="n">
         <v>-0.58</v>
       </c>
-      <c r="N52" s="22" t="n">
+      <c r="N52" s="23" t="n">
         <v>3.38</v>
       </c>
-      <c r="O52" s="20" t="n">
+      <c r="O52" s="21" t="n">
         <v>1.2</v>
       </c>
-      <c r="P52" s="20" t="n">
+      <c r="P52" s="21" t="n">
         <v>0.64</v>
       </c>
-      <c r="Q52" s="20" t="n">
+      <c r="Q52" s="21" t="n">
         <v>0.77</v>
       </c>
-      <c r="R52" s="20" t="n">
+      <c r="R52" s="21" t="n">
         <v>-50.58</v>
       </c>
-      <c r="S52" s="20" t="n">
+      <c r="S52" s="21" t="n">
         <v>3.38</v>
       </c>
       <c r="T52" s="5" t="inlineStr">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="T53" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="E54" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="T54" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="E55" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="T55" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="E56" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F56" s="25" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       <c r="L56" s="16" t="n">
         <v>13.27</v>
       </c>
-      <c r="M56" s="24" t="n">
+      <c r="M56" s="20" t="n">
         <v>-9.970000000000001</v>
       </c>
       <c r="N56" s="19" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="T56" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="E57" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="T57" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="E58" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F58" s="25" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="T58" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="E59" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="T59" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="E60" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="F60" s="25" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
       <c r="L60" s="16" t="n">
         <v>7.29</v>
       </c>
-      <c r="M60" s="24" t="n">
+      <c r="M60" s="20" t="n">
         <v>-1.62</v>
       </c>
       <c r="N60" s="19" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="T60" s="11" t="inlineStr">
         <is>
-          <t>工程机械概念 -0.23%</t>
+          <t>工程机械概念 -0.50%</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       <c r="L66" s="16" t="n">
         <v>10.61</v>
       </c>
-      <c r="M66" s="24" t="n">
+      <c r="M66" s="20" t="n">
         <v>-0.47</v>
       </c>
       <c r="N66" s="19" t="n">
@@ -7248,7 +7248,7 @@
       <c r="M69" s="19" t="n">
         <v>1.51</v>
       </c>
-      <c r="N69" s="24" t="n">
+      <c r="N69" s="20" t="n">
         <v>-2.44</v>
       </c>
       <c r="O69" s="16" t="n">
@@ -7291,8 +7291,8 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E70" s="20" t="n">
-        <v>2.3</v>
+      <c r="E70" s="21" t="n">
+        <v>2.34</v>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
       <c r="G70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="21" t="inlineStr">
+      <c r="H70" s="22" t="inlineStr">
         <is>
           <t>603999</t>
         </is>
@@ -7322,33 +7322,33 @@
           <t>快手概念、知识产权、西部大开发</t>
         </is>
       </c>
-      <c r="L70" s="20" t="n">
+      <c r="L70" s="21" t="n">
         <v>7.47</v>
       </c>
-      <c r="M70" s="22" t="n">
+      <c r="M70" s="23" t="n">
         <v>10.01</v>
       </c>
-      <c r="N70" s="22" t="n">
+      <c r="N70" s="23" t="n">
         <v>7.79</v>
       </c>
-      <c r="O70" s="20" t="n">
+      <c r="O70" s="21" t="n">
         <v>11.65</v>
       </c>
-      <c r="P70" s="20" t="n">
+      <c r="P70" s="21" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q70" s="20" t="n">
+      <c r="Q70" s="21" t="n">
         <v>1.55</v>
       </c>
-      <c r="R70" s="20" t="n">
+      <c r="R70" s="21" t="n">
         <v>-15.21</v>
       </c>
-      <c r="S70" s="20" t="n">
+      <c r="S70" s="21" t="n">
         <v>51.21</v>
       </c>
       <c r="T70" s="5" t="inlineStr">
         <is>
-          <t>知识产权 +2.30%</t>
+          <t>知识产权 +2.34%</t>
         </is>
       </c>
     </row>
@@ -7371,8 +7371,8 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E71" s="20" t="n">
-        <v>2.3</v>
+      <c r="E71" s="21" t="n">
+        <v>2.34</v>
       </c>
       <c r="F71" s="17" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
       <c r="G71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H71" s="21" t="inlineStr">
+      <c r="H71" s="22" t="inlineStr">
         <is>
           <t>601999</t>
         </is>
@@ -7402,33 +7402,33 @@
           <t>东北振兴、在线教育、基金减仓、知识产权</t>
         </is>
       </c>
-      <c r="L71" s="20" t="n">
+      <c r="L71" s="21" t="n">
         <v>7.8</v>
       </c>
-      <c r="M71" s="22" t="n">
+      <c r="M71" s="23" t="n">
         <v>10.01</v>
       </c>
-      <c r="N71" s="22" t="n">
+      <c r="N71" s="23" t="n">
         <v>6.7</v>
       </c>
-      <c r="O71" s="20" t="n">
+      <c r="O71" s="21" t="n">
         <v>3.24</v>
       </c>
-      <c r="P71" s="20" t="n">
+      <c r="P71" s="21" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q71" s="20" t="n">
+      <c r="Q71" s="21" t="n">
         <v>1.23</v>
       </c>
-      <c r="R71" s="20" t="n">
+      <c r="R71" s="21" t="n">
         <v>-7.14</v>
       </c>
-      <c r="S71" s="20" t="n">
+      <c r="S71" s="21" t="n">
         <v>44.44</v>
       </c>
       <c r="T71" s="5" t="inlineStr">
         <is>
-          <t>知识产权 +2.30%</t>
+          <t>知识产权 +2.34%</t>
         </is>
       </c>
     </row>
@@ -7451,8 +7451,8 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E72" s="20" t="n">
-        <v>2.3</v>
+      <c r="E72" s="21" t="n">
+        <v>2.34</v>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
       <c r="G72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="21" t="inlineStr">
+      <c r="H72" s="22" t="inlineStr">
         <is>
           <t>603721</t>
         </is>
@@ -7482,33 +7482,33 @@
           <t>AI语料、体育产业、影视概念、数字水印、文娱消费、旅游概念、知识产权、网红经济、职业教育、虚拟现实、超清视频、小红书概念、短剧互动游戏</t>
         </is>
       </c>
-      <c r="L72" s="20" t="n">
+      <c r="L72" s="21" t="n">
         <v>20.82</v>
       </c>
-      <c r="M72" s="22" t="n">
+      <c r="M72" s="23" t="n">
         <v>9.98</v>
       </c>
-      <c r="N72" s="22" t="n">
+      <c r="N72" s="23" t="n">
         <v>3.22</v>
       </c>
-      <c r="O72" s="20" t="n">
+      <c r="O72" s="21" t="n">
         <v>9.44</v>
       </c>
-      <c r="P72" s="20" t="n">
+      <c r="P72" s="21" t="n">
         <v>1.37</v>
       </c>
-      <c r="Q72" s="20" t="n">
+      <c r="Q72" s="21" t="n">
         <v>1.18</v>
       </c>
-      <c r="R72" s="20" t="n">
+      <c r="R72" s="21" t="n">
         <v>-19.49</v>
       </c>
-      <c r="S72" s="20" t="n">
+      <c r="S72" s="21" t="n">
         <v>44.58</v>
       </c>
       <c r="T72" s="5" t="inlineStr">
         <is>
-          <t>知识产权 +2.30%</t>
+          <t>知识产权 +2.34%</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       <c r="M74" s="19" t="n">
         <v>2.9</v>
       </c>
-      <c r="N74" s="24" t="n">
+      <c r="N74" s="20" t="n">
         <v>-0.93</v>
       </c>
       <c r="O74" s="16" t="n">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="E76" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="T76" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="E77" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="T77" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="E78" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="T78" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="E79" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="T79" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="E80" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F80" s="25" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
       <c r="L80" s="16" t="n">
         <v>11.75</v>
       </c>
-      <c r="M80" s="24" t="n">
+      <c r="M80" s="20" t="n">
         <v>-6.52</v>
       </c>
       <c r="N80" s="19" t="n">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="T80" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="E81" s="16" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F81" s="25" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="T81" s="11" t="inlineStr">
         <is>
-          <t>AI语料 +2.25% / CPO概念 +1.31% / 算力概念 +1.19% / 数据中心 +0.40% / 液冷服务器 +0.12%</t>
+          <t>AI语料 +2.14% / CPO概念 +1.28% / 算力概念 +1.24% / 数据中心 +0.41% / 液冷服务器 +0.21%</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="E82" s="16" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="T82" s="11" t="inlineStr">
         <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+          <t>财税数字化 +2.08% / 信创 +1.11% / 国产软件 +0.78% / 鸿蒙概念 +0.44%</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E83" s="16" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="T83" s="11" t="inlineStr">
         <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+          <t>财税数字化 +2.08% / 信创 +1.11% / 国产软件 +0.78% / 鸿蒙概念 +0.44%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="E84" s="16" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="T84" s="11" t="inlineStr">
         <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+          <t>财税数字化 +2.08% / 信创 +1.11% / 国产软件 +0.78% / 鸿蒙概念 +0.44%</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="E85" s="16" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="F85" s="25" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="T85" s="11" t="inlineStr">
         <is>
-          <t>财税数字化 +2.03% / 信创 +1.01% / 国产软件 +0.74% / 鸿蒙概念 +0.50%</t>
+          <t>财税数字化 +2.08% / 信创 +1.11% / 国产软件 +0.78% / 鸿蒙概念 +0.44%</t>
         </is>
       </c>
     </row>
@@ -8571,8 +8571,8 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E86" s="20" t="n">
-        <v>4.18</v>
+      <c r="E86" s="21" t="n">
+        <v>4.02</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
       <c r="G86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H86" s="21" t="inlineStr">
+      <c r="H86" s="22" t="inlineStr">
         <is>
           <t>603068</t>
         </is>
@@ -8602,33 +8602,33 @@
           <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
         </is>
       </c>
-      <c r="L86" s="20" t="n">
+      <c r="L86" s="21" t="n">
         <v>41.67</v>
       </c>
-      <c r="M86" s="22" t="n">
+      <c r="M86" s="23" t="n">
         <v>10.01</v>
       </c>
-      <c r="N86" s="22" t="n">
+      <c r="N86" s="23" t="n">
         <v>1.51</v>
       </c>
-      <c r="O86" s="20" t="n">
+      <c r="O86" s="21" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="P86" s="20" t="n">
+      <c r="P86" s="21" t="n">
         <v>0.83</v>
       </c>
-      <c r="Q86" s="20" t="n">
+      <c r="Q86" s="21" t="n">
         <v>0.83</v>
       </c>
-      <c r="R86" s="20" t="n">
+      <c r="R86" s="21" t="n">
         <v>-14.1</v>
       </c>
-      <c r="S86" s="20" t="n">
+      <c r="S86" s="21" t="n">
         <v>37.52</v>
       </c>
       <c r="T86" s="5" t="inlineStr">
         <is>
-          <t>WiFi +4.18%</t>
+          <t>WiFi +4.02%</t>
         </is>
       </c>
     </row>
@@ -8651,8 +8651,8 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E87" s="20" t="n">
-        <v>4.18</v>
+      <c r="E87" s="21" t="n">
+        <v>4.02</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
       <c r="G87" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H87" s="21" t="inlineStr">
+      <c r="H87" s="22" t="inlineStr">
         <is>
           <t>001388</t>
         </is>
@@ -8682,33 +8682,33 @@
           <t>PCB、物联网、特高压、5G概念、WiFi、国产软件、基金减仓、智能电网、机器视觉、激光雷达、算力概念、通信技术、多模态AI、工业互联网、新型工业化、电子身份证、中俄贸易概念</t>
         </is>
       </c>
-      <c r="L87" s="20" t="n">
+      <c r="L87" s="21" t="n">
         <v>20.37</v>
       </c>
-      <c r="M87" s="22" t="n">
+      <c r="M87" s="23" t="n">
         <v>9.99</v>
       </c>
-      <c r="N87" s="22" t="n">
+      <c r="N87" s="23" t="n">
         <v>3.56</v>
       </c>
-      <c r="O87" s="20" t="n">
+      <c r="O87" s="21" t="n">
         <v>8.44</v>
       </c>
-      <c r="P87" s="20" t="n">
+      <c r="P87" s="21" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q87" s="20" t="n">
+      <c r="Q87" s="21" t="n">
         <v>0.97</v>
       </c>
-      <c r="R87" s="20" t="n">
+      <c r="R87" s="21" t="n">
         <v>-36.9</v>
       </c>
-      <c r="S87" s="20" t="n">
+      <c r="S87" s="21" t="n">
         <v>19.75</v>
       </c>
       <c r="T87" s="5" t="inlineStr">
         <is>
-          <t>WiFi +4.18%</t>
+          <t>WiFi +4.02%</t>
         </is>
       </c>
     </row>
@@ -8731,8 +8731,8 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E88" s="20" t="n">
-        <v>4.18</v>
+      <c r="E88" s="21" t="n">
+        <v>4.02</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
       <c r="G88" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H88" s="21" t="inlineStr">
+      <c r="H88" s="22" t="inlineStr">
         <is>
           <t>002792</t>
         </is>
@@ -8762,33 +8762,33 @@
           <t>5G概念、6G概念、WiFi、低空经济、储能概念、卫星导航、商业航天、通信技术、F5G概念、UWB概念、光通信模块、卫星互联网、毫米波概念、中俄贸易概念</t>
         </is>
       </c>
-      <c r="L88" s="20" t="n">
+      <c r="L88" s="21" t="n">
         <v>29.17</v>
       </c>
-      <c r="M88" s="22" t="n">
+      <c r="M88" s="23" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="N88" s="22" t="n">
+      <c r="N88" s="23" t="n">
         <v>6.3</v>
       </c>
-      <c r="O88" s="20" t="n">
+      <c r="O88" s="21" t="n">
         <v>12.75</v>
       </c>
-      <c r="P88" s="20" t="n">
+      <c r="P88" s="21" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q88" s="20" t="n">
+      <c r="Q88" s="21" t="n">
         <v>0.79</v>
       </c>
-      <c r="R88" s="20" t="n">
+      <c r="R88" s="21" t="n">
         <v>-58.3</v>
       </c>
-      <c r="S88" s="20" t="n">
+      <c r="S88" s="21" t="n">
         <v>70.78</v>
       </c>
       <c r="T88" s="5" t="inlineStr">
         <is>
-          <t>WiFi +4.18%</t>
+          <t>WiFi +4.02%</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>机器视觉</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="E89" s="16" t="n">
@@ -8824,51 +8824,51 @@
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>002164</t>
+          <t>605398</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>新炬网络</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>风能、减速器、长江三角、机器人执行器</t>
+          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
         </is>
       </c>
       <c r="L89" s="16" t="n">
-        <v>16.16</v>
+        <v>22.91</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="N89" s="19" t="n">
-        <v>21.05</v>
+        <v>0.57</v>
+      </c>
+      <c r="N89" s="20" t="n">
+        <v>-3.7</v>
       </c>
       <c r="O89" s="16" t="n">
-        <v>12.99</v>
+        <v>2.65</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>1.69</v>
+        <v>0.6</v>
       </c>
       <c r="Q89" s="16" t="n">
-        <v>1.2</v>
+        <v>0.92</v>
       </c>
       <c r="R89" s="16" t="n">
-        <v>-9.16</v>
+        <v>-34.9</v>
       </c>
       <c r="S89" s="16" t="n">
-        <v>60.32</v>
+        <v>26.71</v>
       </c>
       <c r="T89" s="11" t="inlineStr">
         <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
+          <t>MLOps概念 +3.93%</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>机器视觉</t>
+          <t>MLOps概念</t>
         </is>
       </c>
       <c r="E90" s="16" t="n">
@@ -8904,211 +8904,211 @@
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>603236</t>
+          <t>002232</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>IT服务Ⅱ</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>物联网、5G概念、6G概念、AI眼镜、先进封装、商业航天、小盘成长、智慧城市、智能电网、智能穿戴、机器视觉、水利建设、电网概念、通信技术、卫星互联网、毫米波概念、英伟达概念、车联网(车路云)</t>
+          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
         </is>
       </c>
       <c r="L90" s="16" t="n">
-        <v>76.11</v>
-      </c>
-      <c r="M90" s="19" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M90" s="20" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N90" s="20" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q90" s="16" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="R90" s="16" t="n">
+        <v>-29.21</v>
+      </c>
+      <c r="S90" s="16" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="T90" s="11" t="inlineStr">
+        <is>
+          <t>MLOps概念 +3.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="38" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>603893</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>瑞芯微</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>物联网、AI眼镜、AI芯片、华为概念、国产芯片、大盘成长、百度概念、虚拟现实、高市净率、EDR概念、半导体概念</t>
+        </is>
+      </c>
+      <c r="L91" s="21" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="M91" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="N90" s="19" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="O90" s="16" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="P90" s="16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q90" s="16" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="R90" s="16" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="S90" s="16" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="T90" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="38" customHeight="1">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="N91" s="24" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="O91" s="21" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P91" s="21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q91" s="21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R91" s="21" t="n">
+        <v>-16.96</v>
+      </c>
+      <c r="S91" s="21" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="T91" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片 +3.86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="38" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>10-20</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="n">
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉</t>
-        </is>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F91" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H91" s="18" t="inlineStr">
-        <is>
-          <t>605389</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>长龄液压</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>工程机械</t>
-        </is>
-      </c>
-      <c r="K91" s="11" t="inlineStr">
-        <is>
-          <t>减速器、小盘成长、工程机械概念</t>
-        </is>
-      </c>
-      <c r="L91" s="16" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="M91" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N91" s="19" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="O91" s="16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="P91" s="16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q91" s="16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R91" s="16" t="n">
-        <v>-41.76</v>
-      </c>
-      <c r="S91" s="16" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="T91" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="38" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F92" s="25" t="inlineStr">
-        <is>
-          <t>放量低位反转</t>
-        </is>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="18" t="inlineStr">
-        <is>
-          <t>002933</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>新兴装备</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr">
-        <is>
-          <t>航空装备Ⅱ</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>军工、无人机、低空经济、军民融合、航天航空、机器人执行器</t>
-        </is>
-      </c>
-      <c r="L92" s="16" t="n">
-        <v>28.18</v>
-      </c>
-      <c r="M92" s="24" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="N92" s="19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="O92" s="16" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="P92" s="16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="Q92" s="16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R92" s="16" t="n">
-        <v>-25.41</v>
-      </c>
-      <c r="S92" s="16" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="T92" s="11" t="inlineStr">
-        <is>
-          <t>机器视觉 +3.93% / 减速器 +3.43% / 机器人执行器 +3.34%</t>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>IT服务Ⅱ</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>大数据、AIPC、AI芯片、AI语料、中盘成长、华为概念、国产软件、百度概念、网络安全、网络游戏、股权分散、脑机接口、长江三角、阿里概念、首发经济、鸿蒙概念、互联网服务、互联网金融、多模态AI、AIGC概念、短剧互动游戏、AI制药（医疗）、抖音概念(字节概念)</t>
+        </is>
+      </c>
+      <c r="L92" s="21" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M92" s="23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N92" s="24" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="O92" s="21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P92" s="21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q92" s="21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R92" s="21" t="n">
+        <v>-55.42</v>
+      </c>
+      <c r="S92" s="21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T92" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片 +3.86%</t>
         </is>
       </c>
     </row>
@@ -9131,8 +9131,8 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E93" s="20" t="n">
-        <v>3.93</v>
+      <c r="E93" s="21" t="n">
+        <v>3.86</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="G93" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>603893</t>
+        <v>3</v>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>002049</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -9159,196 +9159,196 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>物联网、AI眼镜、AI芯片、华为概念、国产芯片、大盘成长、百度概念、虚拟现实、高市净率、EDR概念、半导体概念</t>
-        </is>
-      </c>
-      <c r="L93" s="20" t="n">
-        <v>189.04</v>
-      </c>
-      <c r="M93" s="22" t="n">
+          <t>军工、ETC、大飞机、碳化硅、蓝宝石、5G概念、AI芯片、商业航天、国产芯片、存储芯片、汽车芯片、算力概念、通信技术、半导体概念、卫星互联网、高带宽内存、IGBT概念、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L93" s="21" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="M93" s="23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N93" s="24" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="O93" s="21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P93" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q93" s="21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R93" s="21" t="n">
+        <v>-41.64</v>
+      </c>
+      <c r="S93" s="21" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="T93" s="5" t="inlineStr">
+        <is>
+          <t>AI芯片 +3.86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="38" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>002164</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>通用设备</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>风能、减速器、长江三角、机器人执行器</t>
+        </is>
+      </c>
+      <c r="L94" s="16" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="M94" s="19" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N94" s="19" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="O94" s="16" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="P94" s="16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q94" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R94" s="16" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="S94" s="16" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="T94" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉 +3.85% / 机器人执行器 +3.37% / 减速器 +3.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="38" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>603236</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>移远通信</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>通信设备</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>物联网、5G概念、6G概念、AI眼镜、先进封装、商业航天、小盘成长、智慧城市、智能电网、智能穿戴、机器视觉、水利建设、电网概念、通信技术、卫星互联网、毫米波概念、英伟达概念、车联网(车路云)</t>
+        </is>
+      </c>
+      <c r="L95" s="16" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="M95" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="N93" s="23" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="O93" s="20" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="P93" s="20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q93" s="20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R93" s="20" t="n">
-        <v>-16.96</v>
-      </c>
-      <c r="S93" s="20" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="T93" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片 +3.93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="38" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="E94" s="20" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F94" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H94" s="21" t="inlineStr">
-        <is>
-          <t>002195</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>岩山科技</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>IT服务Ⅱ</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>大数据、AIPC、AI芯片、AI语料、中盘成长、华为概念、国产软件、百度概念、网络安全、网络游戏、股权分散、脑机接口、长江三角、阿里概念、首发经济、鸿蒙概念、互联网服务、互联网金融、多模态AI、AIGC概念、短剧互动游戏、AI制药（医疗）、抖音概念(字节概念)</t>
-        </is>
-      </c>
-      <c r="L94" s="20" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N94" s="23" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="O94" s="20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P94" s="20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q94" s="20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R94" s="20" t="n">
-        <v>-55.42</v>
-      </c>
-      <c r="S94" s="20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T94" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片 +3.93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="38" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>10-20</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="E95" s="20" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="F95" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H95" s="21" t="inlineStr">
-        <is>
-          <t>002049</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>紫光国微</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>军工、ETC、大飞机、碳化硅、蓝宝石、5G概念、AI芯片、商业航天、国产芯片、存储芯片、汽车芯片、算力概念、通信技术、半导体概念、卫星互联网、高带宽内存、IGBT概念、车联网(车路云)</t>
-        </is>
-      </c>
-      <c r="L95" s="20" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="M95" s="22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N95" s="23" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="O95" s="20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P95" s="20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q95" s="20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R95" s="20" t="n">
-        <v>-41.64</v>
-      </c>
-      <c r="S95" s="20" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="T95" s="5" t="inlineStr">
-        <is>
-          <t>AI芯片 +3.93%</t>
+      <c r="N95" s="19" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="O95" s="16" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="P95" s="16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q95" s="16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R95" s="16" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="S95" s="16" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="T95" s="11" t="inlineStr">
+        <is>
+          <t>机器视觉 +3.85% / 机器人执行器 +3.37% / 减速器 +3.30%</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>机器视觉</t>
         </is>
       </c>
       <c r="E96" s="16" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
@@ -9380,55 +9380,55 @@
         </is>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H96" s="18" t="inlineStr">
         <is>
-          <t>605398</t>
+          <t>605389</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>新炬网络</t>
+          <t>长龄液压</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>信创、大数据、华为概念、数据中心、百度概念、互联网服务、AIGC概念、MLOps概念</t>
+          <t>减速器、小盘成长、工程机械概念</t>
         </is>
       </c>
       <c r="L96" s="16" t="n">
-        <v>22.91</v>
+        <v>57.97</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N96" s="24" t="n">
-        <v>-3.7</v>
+        <v>10</v>
+      </c>
+      <c r="N96" s="19" t="n">
+        <v>5.38</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>2.65</v>
+        <v>0.68</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q96" s="16" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="R96" s="16" t="n">
-        <v>-34.9</v>
+        <v>-41.76</v>
       </c>
       <c r="S96" s="16" t="n">
-        <v>26.71</v>
+        <v>24.99</v>
       </c>
       <c r="T96" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念 +3.92%</t>
+          <t>机器视觉 +3.85% / 机器人执行器 +3.37% / 减速器 +3.30%</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
@@ -9448,67 +9448,67 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念</t>
+          <t>机器视觉</t>
         </is>
       </c>
       <c r="E97" s="16" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="F97" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
+        <v>3.85</v>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>放量低位反转</t>
         </is>
       </c>
       <c r="G97" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>002232</t>
+          <t>002933</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>启明信息</t>
+          <t>新兴装备</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>IT服务Ⅱ</t>
+          <t>航空装备Ⅱ</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>信创、云计算、充电桩、大数据、东北振兴、低空经济、华为概念、华为汽车、国产软件、数字孪生、数据中心、数据安全、智慧城市、百度概念、网络安全、胎压监测、虚拟现实、EDR概念、ERP概念、互联网服务、工业互联网、电子身份证、MLOps概念、车联网(车路云)、飞行汽车(eVTOL)</t>
+          <t>军工、无人机、低空经济、军民融合、航天航空、机器人执行器</t>
         </is>
       </c>
       <c r="L97" s="16" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="M97" s="24" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="N97" s="24" t="n">
-        <v>-3.28</v>
+        <v>28.18</v>
+      </c>
+      <c r="M97" s="20" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="N97" s="19" t="n">
+        <v>5.42</v>
       </c>
       <c r="O97" s="16" t="n">
-        <v>2.5</v>
+        <v>8.02</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.57</v>
+        <v>3.93</v>
       </c>
       <c r="Q97" s="16" t="n">
-        <v>0.61</v>
+        <v>2.25</v>
       </c>
       <c r="R97" s="16" t="n">
-        <v>-29.21</v>
+        <v>-25.41</v>
       </c>
       <c r="S97" s="16" t="n">
-        <v>18.86</v>
+        <v>19.51</v>
       </c>
       <c r="T97" s="11" t="inlineStr">
         <is>
-          <t>MLOps概念 +3.92%</t>
+          <t>机器视觉 +3.85% / 机器人执行器 +3.37% / 减速器 +3.30%</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="E98" s="16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="T98" s="11" t="inlineStr">
         <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
+          <t>无线耳机 +3.75% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="E99" s="16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="T99" s="11" t="inlineStr">
         <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
+          <t>无线耳机 +3.75% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
         </is>
       </c>
       <c r="E100" s="16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="T100" s="11" t="inlineStr">
         <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
+          <t>无线耳机 +3.75% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="E101" s="16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="F101" s="25" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="T101" s="11" t="inlineStr">
         <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
+          <t>无线耳机 +3.75% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="E102" s="16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="F102" s="25" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
       <c r="L102" s="16" t="n">
         <v>15.77</v>
       </c>
-      <c r="M102" s="24" t="n">
+      <c r="M102" s="20" t="n">
         <v>-0.88</v>
       </c>
       <c r="N102" s="19" t="n">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T102" s="11" t="inlineStr">
         <is>
-          <t>无线耳机 +3.80% / 无线充电 +2.09%</t>
+          <t>无线耳机 +3.75% / 无线充电 +2.09%</t>
         </is>
       </c>
     </row>

--- a/data/theme_strength_latest.xlsx
+++ b/data/theme_strength_latest.xlsx
@@ -218,9 +218,6 @@
     <xf numFmtId="2" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -228,6 +225,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,7 +636,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>截至 2026-10-26  2026-10-26 14:55｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：成分股等权还原（东财板块日线不完整）</t>
+          <t>截至 2026-10-26  2026-10-26 18:11｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：成分股等权还原（东财板块日线不完整）</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="12" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>1</v>
@@ -1007,7 +1007,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>快递概念</t>
+          <t>可燃冰</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>2</v>
@@ -1055,7 +1055,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>快递概念</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="12" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>3</v>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>3</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="L11" s="10" t="n">
         <v>4</v>
@@ -1151,7 +1151,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>可燃冰</t>
+          <t>乳业</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="12" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>5</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>5</v>
@@ -1995,7 +1995,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         <v>7.79</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="P4" s="16" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="Q4" s="16" t="n">
         <v>1.12</v>
@@ -2068,14 +2068,14 @@
       </c>
       <c r="T4" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.78%</t>
+          <t>SPD概念 +2.81%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         <v>12.62</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="P5" s="16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" s="16" t="n">
         <v>0.77</v>
@@ -2148,14 +2148,14 @@
       </c>
       <c r="T5" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.78%</t>
+          <t>SPD概念 +2.81%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
@@ -2203,519 +2203,519 @@
         </is>
       </c>
       <c r="L6" s="16" t="n">
-        <v>16.83</v>
+        <v>16.8</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="N6" s="19" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" s="16" t="n">
         <v>1.06</v>
       </c>
       <c r="R6" s="16" t="n">
-        <v>-5.66</v>
+        <v>-5.83</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>13.41</v>
+        <v>13.21</v>
       </c>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>SPD概念 +2.78%</t>
+          <t>SPD概念 +2.81%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>601808</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>中海油服</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>油服工程</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰、天然气、油气设服、油气资源、海工装备、行业龙头、资源开采概念</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P7" s="20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q7" s="20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R7" s="20" t="n">
+        <v>-33.87</v>
+      </c>
+      <c r="S7" s="20" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰 +2.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>002278</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>神开股份</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰、无人机、氢能源、碳纤维、页岩气、低空经济、商业航天、油气设服、油气资源、海工装备、长江三角、中俄贸易概念</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O8" s="20" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="P8" s="20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q8" s="20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R8" s="20" t="n">
+        <v>-50.06</v>
+      </c>
+      <c r="S8" s="20" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰 +2.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>000039</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>中集集团</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>通用设备</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>风能、可燃冰、天然气、氢能源、物联网、冷链物流、商业航天、数据中心、油气资源、海工装备、深圳特区、社保新进、雄安新区</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="O9" s="20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P9" s="20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q9" s="20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R9" s="20" t="n">
+        <v>-36.32</v>
+      </c>
+      <c r="S9" s="20" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>可燃冰 +2.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>快递概念</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>001317</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>铁路公路</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="23" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="O10" s="16" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="P10" s="16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Q10" s="16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R10" s="16" t="n">
+        <v>-21.36</v>
+      </c>
+      <c r="S10" s="16" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>领涨前三</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>002468</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>申通快递</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>大数据、小盘价值、快递概念、阿里概念</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P11" s="16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q11" s="16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R11" s="16" t="n">
+        <v>-18.13</v>
+      </c>
+      <c r="S11" s="16" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>10-26收盘</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>快递概念</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="C12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>快递概念</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>领涨前三</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>001317</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>三羊马</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>铁路公路</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>快递概念、跨境电商、统一大市场、西部大开发</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>53.68</v>
-      </c>
-      <c r="M7" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="20" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="O7" s="16" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="P7" s="16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Q7" s="16" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="R7" s="16" t="n">
-        <v>-21.36</v>
-      </c>
-      <c r="S7" s="16" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +2.08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>002468</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>申通快递</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="G12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>601598</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>中国外运</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>物流</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>大数据、小盘价值、快递概念、阿里概念</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="N8" s="19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O8" s="16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P8" s="16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q8" s="16" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="R8" s="16" t="n">
-        <v>-18.01</v>
-      </c>
-      <c r="S8" s="16" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +2.08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>快递概念</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>601598</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>中国外运</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>中盘价值、冷链物流、快递概念、跨境电商、统一大市场</t>
         </is>
       </c>
-      <c r="L9" s="16" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="M9" s="19" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="N9" s="20" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="O9" s="16" t="n">
+      <c r="L12" s="16" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>0.36</v>
       </c>
-      <c r="P9" s="16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q9" s="16" t="n">
+      <c r="P12" s="16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q12" s="16" t="n">
         <v>0.87</v>
       </c>
-      <c r="R9" s="16" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="S9" s="16" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>快递概念 +2.08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>001219</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>青岛食品</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>休闲食品</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>乳业、婴童概念、电商概念、网红经济、调味品概念</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="M10" s="23" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="N10" s="23" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="O10" s="21" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P10" s="21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R10" s="21" t="n">
-        <v>-12.36</v>
-      </c>
-      <c r="S10" s="21" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>乳业 +1.96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>001318</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>阳光乳业</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>饮料乳品</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>乳业、味蕾经济、婴童概念</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="24" t="n">
-        <v>-11.94</v>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="P11" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q11" s="21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R11" s="21" t="n">
-        <v>-30.22</v>
-      </c>
-      <c r="S11" s="21" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>乳业 +1.96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>10-26午盘</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>领涨前三</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>603719</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>良品铺子</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>休闲食品</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>乳业、内贸流通、电商概念、社区团购、网红经济、谷子经济</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="N12" s="23" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O12" s="21" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P12" s="21" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="Q12" s="21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R12" s="21" t="n">
-        <v>-26.35</v>
-      </c>
-      <c r="S12" s="21" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>乳业 +1.96%</t>
+      <c r="R12" s="16" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>快递概念 +2.11%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2731,8 +2731,8 @@
           <t>电子竞技</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
-        <v>1.94</v>
+      <c r="E13" s="20" t="n">
+        <v>2.01</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       <c r="G13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>603258</t>
         </is>
@@ -2762,40 +2762,40 @@
           <t>文娱消费、电子竞技、网络游戏、虚拟现实、谷子经济、AIGC概念、短剧互动游戏</t>
         </is>
       </c>
-      <c r="L13" s="21" t="n">
+      <c r="L13" s="20" t="n">
         <v>15.3</v>
       </c>
-      <c r="M13" s="23" t="n">
+      <c r="M13" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="N13" s="23" t="n">
+      <c r="N13" s="22" t="n">
         <v>4.37</v>
       </c>
-      <c r="O13" s="21" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="P13" s="21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q13" s="21" t="n">
+      <c r="O13" s="20" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P13" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q13" s="20" t="n">
         <v>1.18</v>
       </c>
-      <c r="R13" s="21" t="n">
+      <c r="R13" s="20" t="n">
         <v>-26.02</v>
       </c>
-      <c r="S13" s="21" t="n">
+      <c r="S13" s="20" t="n">
         <v>41.4</v>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>电子竞技 +1.94%</t>
+          <t>电子竞技 +2.01%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2811,8 +2811,8 @@
           <t>电子竞技</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
-        <v>1.94</v>
+      <c r="E14" s="20" t="n">
+        <v>2.01</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       <c r="G14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>001308</t>
         </is>
@@ -2842,40 +2842,40 @@
           <t>AIPC、AI眼镜、OLED、华为概念、小盘价值、智能电视、智能穿戴、深圳特区、电子竞技、虚拟现实、贬值受益、医疗器械概念、消费电子概念、MiniLED、抖音概念(字节概念)</t>
         </is>
       </c>
-      <c r="L14" s="21" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="M14" s="23" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="N14" s="23" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="21" t="n">
+      <c r="L14" s="20" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="O14" s="20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P14" s="20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q14" s="20" t="n">
         <v>1.47</v>
       </c>
-      <c r="R14" s="21" t="n">
-        <v>-12.91</v>
-      </c>
-      <c r="S14" s="21" t="n">
-        <v>17.7</v>
+      <c r="R14" s="20" t="n">
+        <v>-12.82</v>
+      </c>
+      <c r="S14" s="20" t="n">
+        <v>17.82</v>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>电子竞技 +1.94%</t>
+          <t>电子竞技 +2.01%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2891,8 +2891,8 @@
           <t>电子竞技</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
-        <v>1.94</v>
+      <c r="E15" s="20" t="n">
+        <v>2.01</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       <c r="G15" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>002517</t>
         </is>
@@ -2922,45 +2922,45 @@
           <t>AI眼镜、华为概念、文娱消费、电子竞技、网络游戏、虚拟现实、短剧互动游戏</t>
         </is>
       </c>
-      <c r="L15" s="21" t="n">
-        <v>15.55</v>
-      </c>
-      <c r="M15" s="23" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N15" s="23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O15" s="21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q15" s="21" t="n">
+      <c r="L15" s="20" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O15" s="20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P15" s="20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q15" s="20" t="n">
         <v>1.03</v>
       </c>
-      <c r="R15" s="21" t="n">
-        <v>-43.27</v>
-      </c>
-      <c r="S15" s="21" t="n">
-        <v>9.66</v>
+      <c r="R15" s="20" t="n">
+        <v>-43.2</v>
+      </c>
+      <c r="S15" s="20" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>电子竞技 +1.94%</t>
+          <t>电子竞技 +2.01%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
+          <t>乳业</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -2968,11 +2968,11 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>1.89</v>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>1.99</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
@@ -2982,65 +2982,65 @@
       <c r="G16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>601808</t>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>001219</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>中海油服</t>
+          <t>青岛食品</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>油服工程</t>
+          <t>休闲食品</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>可燃冰、天然气、油气设服、油气资源、海工装备、行业龙头、资源开采概念</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="M16" s="23" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="N16" s="23" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R16" s="21" t="n">
-        <v>-33.97</v>
-      </c>
-      <c r="S16" s="21" t="n">
-        <v>24.84</v>
+          <t>乳业、婴童概念、电商概念、网红经济、调味品概念</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="O16" s="20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P16" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q16" s="20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R16" s="20" t="n">
+        <v>-12.36</v>
+      </c>
+      <c r="S16" s="20" t="n">
+        <v>18.85</v>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>可燃冰 +1.89%</t>
+          <t>乳业 +1.99%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
+          <t>乳业</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>1.89</v>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>1.99</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
@@ -3062,65 +3062,65 @@
       <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>002278</t>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>001318</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>神开股份</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>饮料乳品</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>可燃冰、无人机、氢能源、碳纤维、页岩气、低空经济、商业航天、油气设服、油气资源、海工装备、长江三角、中俄贸易概念</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M17" s="23" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="N17" s="23" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q17" s="21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R17" s="21" t="n">
-        <v>-50.06</v>
-      </c>
-      <c r="S17" s="21" t="n">
-        <v>10.03</v>
+          <t>乳业、味蕾经济、婴童概念</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>-11.94</v>
+      </c>
+      <c r="O17" s="20" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="P17" s="20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q17" s="20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R17" s="20" t="n">
+        <v>-30.22</v>
+      </c>
+      <c r="S17" s="20" t="n">
+        <v>26.57</v>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>可燃冰 +1.89%</t>
+          <t>乳业 +1.99%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>10-26午盘</t>
+          <t>10-26收盘</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
+          <t>乳业</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>可燃冰</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>1.89</v>
+          <t>乳业</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>1.99</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
@@ -3142,53 +3142,53 @@
       <c r="G18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>000039</t>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>603719</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>中集集团</t>
+          <t>良品铺子</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>通用设备</t>
+          <t>休闲食品</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>风能、可燃冰、天然气、氢能源、物联网、冷链物流、商业航天、数据中心、油气资源、海工装备、深圳特区、社保新进、雄安新区</t>
-        </is>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N18" s="23" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P18" s="21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R18" s="21" t="n">
-        <v>-36.46</v>
-      </c>
-      <c r="S18" s="21" t="n">
-        <v>17.99</v>
+          <t>乳业、内贸流通、电商概念、社区团购、网红经济、谷子经济</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O18" s="20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P18" s="20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q18" s="20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R18" s="20" t="n">
+        <v>-26.35</v>
+      </c>
+      <c r="S18" s="20" t="n">
+        <v>14.65</v>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>可燃冰 +1.89%</t>
+          <t>乳业 +1.99%</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
           <t>虚拟机器人</t>
         </is>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="20" t="n">
         <v>5.59</v>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -4422,7 +4422,7 @@
       <c r="G34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>603528</t>
         </is>
@@ -4442,28 +4442,28 @@
           <t>大数据、物联网、华为昇腾、华为概念、卫星导航、国产芯片、国产软件、智慧城市、职业教育、虚拟机器人、车联网(车路云)</t>
         </is>
       </c>
-      <c r="L34" s="21" t="n">
+      <c r="L34" s="20" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="M34" s="23" t="n">
+      <c r="M34" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="N34" s="23" t="n">
+      <c r="N34" s="22" t="n">
         <v>24.66</v>
       </c>
-      <c r="O34" s="21" t="n">
+      <c r="O34" s="20" t="n">
         <v>12.51</v>
       </c>
-      <c r="P34" s="21" t="n">
+      <c r="P34" s="20" t="n">
         <v>3.14</v>
       </c>
-      <c r="Q34" s="21" t="n">
+      <c r="Q34" s="20" t="n">
         <v>1.6</v>
       </c>
-      <c r="R34" s="21" t="n">
+      <c r="R34" s="20" t="n">
         <v>-28.47</v>
       </c>
-      <c r="S34" s="21" t="n">
+      <c r="S34" s="20" t="n">
         <v>49.91</v>
       </c>
       <c r="T34" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
           <t>虚拟机器人</t>
         </is>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="E35" s="20" t="n">
         <v>5.59</v>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -4502,7 +4502,7 @@
       <c r="G35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>601519</t>
         </is>
@@ -4522,28 +4522,28 @@
           <t>大数据、华为概念、国产软件、小盘成长、数据中心、私募重仓、网红经济、长江三角、阿里概念、高市净率、鸿蒙概念、互联网金融、虚拟机器人</t>
         </is>
       </c>
-      <c r="L35" s="21" t="n">
+      <c r="L35" s="20" t="n">
         <v>9.25</v>
       </c>
-      <c r="M35" s="23" t="n">
+      <c r="M35" s="22" t="n">
         <v>9.99</v>
       </c>
       <c r="N35" s="24" t="n">
         <v>-2.43</v>
       </c>
-      <c r="O35" s="21" t="n">
+      <c r="O35" s="20" t="n">
         <v>6.2</v>
       </c>
-      <c r="P35" s="21" t="n">
+      <c r="P35" s="20" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q35" s="21" t="n">
+      <c r="Q35" s="20" t="n">
         <v>1.02</v>
       </c>
-      <c r="R35" s="21" t="n">
+      <c r="R35" s="20" t="n">
         <v>-39.62</v>
       </c>
-      <c r="S35" s="21" t="n">
+      <c r="S35" s="20" t="n">
         <v>24.33</v>
       </c>
       <c r="T35" s="5" t="inlineStr">
@@ -4571,7 +4571,7 @@
           <t>虚拟机器人</t>
         </is>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="20" t="n">
         <v>5.59</v>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -4582,7 +4582,7 @@
       <c r="G36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>001314</t>
         </is>
@@ -4602,28 +4602,28 @@
           <t>PCB、物联网、AIPC、AI眼镜、在线教育、增强现实、智能穿戴、虚拟现实、虚拟机器人、消费电子概念</t>
         </is>
       </c>
-      <c r="L36" s="21" t="n">
+      <c r="L36" s="20" t="n">
         <v>45.33</v>
       </c>
-      <c r="M36" s="23" t="n">
+      <c r="M36" s="22" t="n">
         <v>5.62</v>
       </c>
-      <c r="N36" s="23" t="n">
+      <c r="N36" s="22" t="n">
         <v>6.66</v>
       </c>
-      <c r="O36" s="21" t="n">
+      <c r="O36" s="20" t="n">
         <v>4.67</v>
       </c>
-      <c r="P36" s="21" t="n">
+      <c r="P36" s="20" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q36" s="21" t="n">
+      <c r="Q36" s="20" t="n">
         <v>1.09</v>
       </c>
-      <c r="R36" s="21" t="n">
+      <c r="R36" s="20" t="n">
         <v>-29.48</v>
       </c>
-      <c r="S36" s="21" t="n">
+      <c r="S36" s="20" t="n">
         <v>18.05</v>
       </c>
       <c r="T36" s="5" t="inlineStr">
@@ -4688,7 +4688,7 @@
       <c r="M37" s="19" t="n">
         <v>3.85</v>
       </c>
-      <c r="N37" s="20" t="n">
+      <c r="N37" s="23" t="n">
         <v>-0.53</v>
       </c>
       <c r="O37" s="16" t="n">
@@ -4765,10 +4765,10 @@
       <c r="L38" s="16" t="n">
         <v>14.3</v>
       </c>
-      <c r="M38" s="20" t="n">
+      <c r="M38" s="23" t="n">
         <v>-4.41</v>
       </c>
-      <c r="N38" s="20" t="n">
+      <c r="N38" s="23" t="n">
         <v>-6.9</v>
       </c>
       <c r="O38" s="16" t="n">
@@ -4811,7 +4811,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="20" t="n">
         <v>5.2</v>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       <c r="G39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>603466</t>
         </is>
@@ -4842,28 +4842,28 @@
           <t>全息技术、华为概念、数字孪生、旅游概念、百度概念、网红经济、网络游戏、职业教育、脑机接口、虚拟现实、裸眼3D、超清视频、首发经济、新型城镇化、虚拟数字人、AIGC概念、ChatGPT概念、DeepSeek概念</t>
         </is>
       </c>
-      <c r="L39" s="21" t="n">
+      <c r="L39" s="20" t="n">
         <v>14.69</v>
       </c>
-      <c r="M39" s="23" t="n">
+      <c r="M39" s="22" t="n">
         <v>10.04</v>
       </c>
-      <c r="N39" s="23" t="n">
+      <c r="N39" s="22" t="n">
         <v>16.22</v>
       </c>
-      <c r="O39" s="21" t="n">
+      <c r="O39" s="20" t="n">
         <v>16.7</v>
       </c>
-      <c r="P39" s="21" t="n">
+      <c r="P39" s="20" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q39" s="21" t="n">
+      <c r="Q39" s="20" t="n">
         <v>1.47</v>
       </c>
-      <c r="R39" s="21" t="n">
+      <c r="R39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="21" t="n">
+      <c r="S39" s="20" t="n">
         <v>66.36</v>
       </c>
       <c r="T39" s="5" t="inlineStr">
@@ -4891,7 +4891,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="20" t="n">
         <v>5.2</v>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -4902,7 +4902,7 @@
       <c r="G40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>002354</t>
         </is>
@@ -4922,28 +4922,28 @@
           <t>信创、AI语料、东数西算、国产芯片、在线教育、小盘价值、文娱消费、电子竞技、百度概念、网络游戏、股权分散、虚拟现实、谷子经济、跨境电商、互联网服务、互联网金融、多模态AI、小红书概念、虚拟数字人、AIGC概念、Web3.0、短剧互动游戏、ChatGPT概念、DeepSeek概念、抖音概念(字节概念)</t>
         </is>
       </c>
-      <c r="L40" s="21" t="n">
+      <c r="L40" s="20" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="M40" s="23" t="n">
+      <c r="M40" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="N40" s="23" t="n">
+      <c r="N40" s="22" t="n">
         <v>11.37</v>
       </c>
-      <c r="O40" s="21" t="n">
+      <c r="O40" s="20" t="n">
         <v>17.93</v>
       </c>
-      <c r="P40" s="21" t="n">
+      <c r="P40" s="20" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q40" s="21" t="n">
+      <c r="Q40" s="20" t="n">
         <v>1.25</v>
       </c>
-      <c r="R40" s="21" t="n">
+      <c r="R40" s="20" t="n">
         <v>-22.34</v>
       </c>
-      <c r="S40" s="21" t="n">
+      <c r="S40" s="20" t="n">
         <v>48.43</v>
       </c>
       <c r="T40" s="5" t="inlineStr">
@@ -4971,7 +4971,7 @@
           <t>ChatGPT概念</t>
         </is>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="20" t="n">
         <v>5.2</v>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="G41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>600446</t>
         </is>
@@ -5002,28 +5002,28 @@
           <t>信创、国产软件、数据安全、智慧城市、深圳特区、电商概念、网络安全、股权分散、互联网服务、虚拟机器人、ChatGPT概念</t>
         </is>
       </c>
-      <c r="L41" s="21" t="n">
+      <c r="L41" s="20" t="n">
         <v>10.6</v>
       </c>
-      <c r="M41" s="23" t="n">
+      <c r="M41" s="22" t="n">
         <v>5.37</v>
       </c>
-      <c r="N41" s="23" t="n">
+      <c r="N41" s="22" t="n">
         <v>3.01</v>
       </c>
-      <c r="O41" s="21" t="n">
+      <c r="O41" s="20" t="n">
         <v>3.2</v>
       </c>
-      <c r="P41" s="21" t="n">
+      <c r="P41" s="20" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q41" s="21" t="n">
+      <c r="Q41" s="20" t="n">
         <v>1.14</v>
       </c>
-      <c r="R41" s="21" t="n">
+      <c r="R41" s="20" t="n">
         <v>-40.62</v>
       </c>
-      <c r="S41" s="21" t="n">
+      <c r="S41" s="20" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="T41" s="5" t="inlineStr">
@@ -5485,7 +5485,7 @@
       <c r="L47" s="16" t="n">
         <v>7.29</v>
       </c>
-      <c r="M47" s="20" t="n">
+      <c r="M47" s="23" t="n">
         <v>-1.62</v>
       </c>
       <c r="N47" s="19" t="n">
@@ -5691,7 +5691,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="20" t="n">
         <v>0.16</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -5702,7 +5702,7 @@
       <c r="G50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="22" t="inlineStr">
+      <c r="H50" s="21" t="inlineStr">
         <is>
           <t>603350</t>
         </is>
@@ -5722,28 +5722,28 @@
           <t>传感器、轮毂电机</t>
         </is>
       </c>
-      <c r="L50" s="21" t="n">
+      <c r="L50" s="20" t="n">
         <v>29.48</v>
       </c>
-      <c r="M50" s="23" t="n">
+      <c r="M50" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="N50" s="23" t="n">
+      <c r="N50" s="22" t="n">
         <v>12.01</v>
       </c>
-      <c r="O50" s="21" t="n">
+      <c r="O50" s="20" t="n">
         <v>5.79</v>
       </c>
-      <c r="P50" s="21" t="n">
+      <c r="P50" s="20" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q50" s="21" t="n">
+      <c r="Q50" s="20" t="n">
         <v>1.55</v>
       </c>
-      <c r="R50" s="21" t="n">
+      <c r="R50" s="20" t="n">
         <v>-27.28</v>
       </c>
-      <c r="S50" s="21" t="n">
+      <c r="S50" s="20" t="n">
         <v>13.65</v>
       </c>
       <c r="T50" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E51" s="21" t="n">
+      <c r="E51" s="20" t="n">
         <v>0.16</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="G51" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="H51" s="21" t="inlineStr">
         <is>
           <t>603489</t>
         </is>
@@ -5802,28 +5802,28 @@
           <t>交运设备、共享经济、轮毂电机</t>
         </is>
       </c>
-      <c r="L51" s="21" t="n">
+      <c r="L51" s="20" t="n">
         <v>27.5</v>
       </c>
-      <c r="M51" s="23" t="n">
+      <c r="M51" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="N51" s="23" t="n">
+      <c r="N51" s="22" t="n">
         <v>6.51</v>
       </c>
-      <c r="O51" s="21" t="n">
+      <c r="O51" s="20" t="n">
         <v>1.31</v>
       </c>
-      <c r="P51" s="21" t="n">
+      <c r="P51" s="20" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q51" s="21" t="n">
+      <c r="Q51" s="20" t="n">
         <v>1.06</v>
       </c>
-      <c r="R51" s="21" t="n">
+      <c r="R51" s="20" t="n">
         <v>-31.13</v>
       </c>
-      <c r="S51" s="21" t="n">
+      <c r="S51" s="20" t="n">
         <v>16.48</v>
       </c>
       <c r="T51" s="5" t="inlineStr">
@@ -5851,7 +5851,7 @@
           <t>轮毂电机</t>
         </is>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="E52" s="20" t="n">
         <v>0.16</v>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -5862,7 +5862,7 @@
       <c r="G52" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="22" t="inlineStr">
+      <c r="H52" s="21" t="inlineStr">
         <is>
           <t>002284</t>
         </is>
@@ -5882,28 +5882,28 @@
           <t>华为汽车、胎压监测、轮毂电机、长江三角、车联网(车路云)</t>
         </is>
       </c>
-      <c r="L52" s="21" t="n">
+      <c r="L52" s="20" t="n">
         <v>8.57</v>
       </c>
       <c r="M52" s="24" t="n">
         <v>-0.58</v>
       </c>
-      <c r="N52" s="23" t="n">
+      <c r="N52" s="22" t="n">
         <v>3.38</v>
       </c>
-      <c r="O52" s="21" t="n">
+      <c r="O52" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="P52" s="21" t="n">
+      <c r="P52" s="20" t="n">
         <v>0.64</v>
       </c>
-      <c r="Q52" s="21" t="n">
+      <c r="Q52" s="20" t="n">
         <v>0.77</v>
       </c>
-      <c r="R52" s="21" t="n">
+      <c r="R52" s="20" t="n">
         <v>-50.58</v>
       </c>
-      <c r="S52" s="21" t="n">
+      <c r="S52" s="20" t="n">
         <v>3.38</v>
       </c>
       <c r="T52" s="5" t="inlineStr">
@@ -6205,7 +6205,7 @@
       <c r="L56" s="16" t="n">
         <v>13.27</v>
       </c>
-      <c r="M56" s="20" t="n">
+      <c r="M56" s="23" t="n">
         <v>-9.970000000000001</v>
       </c>
       <c r="N56" s="19" t="n">
@@ -6525,7 +6525,7 @@
       <c r="L60" s="16" t="n">
         <v>7.29</v>
       </c>
-      <c r="M60" s="20" t="n">
+      <c r="M60" s="23" t="n">
         <v>-1.62</v>
       </c>
       <c r="N60" s="19" t="n">
@@ -7005,7 +7005,7 @@
       <c r="L66" s="16" t="n">
         <v>10.61</v>
       </c>
-      <c r="M66" s="20" t="n">
+      <c r="M66" s="23" t="n">
         <v>-0.47</v>
       </c>
       <c r="N66" s="19" t="n">
@@ -7248,7 +7248,7 @@
       <c r="M69" s="19" t="n">
         <v>1.51</v>
       </c>
-      <c r="N69" s="20" t="n">
+      <c r="N69" s="23" t="n">
         <v>-2.44</v>
       </c>
       <c r="O69" s="16" t="n">
@@ -7291,7 +7291,7 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E70" s="21" t="n">
+      <c r="E70" s="20" t="n">
         <v>2.34</v>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="G70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="22" t="inlineStr">
+      <c r="H70" s="21" t="inlineStr">
         <is>
           <t>603999</t>
         </is>
@@ -7322,28 +7322,28 @@
           <t>快手概念、知识产权、西部大开发</t>
         </is>
       </c>
-      <c r="L70" s="21" t="n">
+      <c r="L70" s="20" t="n">
         <v>7.47</v>
       </c>
-      <c r="M70" s="23" t="n">
+      <c r="M70" s="22" t="n">
         <v>10.01</v>
       </c>
-      <c r="N70" s="23" t="n">
+      <c r="N70" s="22" t="n">
         <v>7.79</v>
       </c>
-      <c r="O70" s="21" t="n">
+      <c r="O70" s="20" t="n">
         <v>11.65</v>
       </c>
-      <c r="P70" s="21" t="n">
+      <c r="P70" s="20" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q70" s="21" t="n">
+      <c r="Q70" s="20" t="n">
         <v>1.55</v>
       </c>
-      <c r="R70" s="21" t="n">
+      <c r="R70" s="20" t="n">
         <v>-15.21</v>
       </c>
-      <c r="S70" s="21" t="n">
+      <c r="S70" s="20" t="n">
         <v>51.21</v>
       </c>
       <c r="T70" s="5" t="inlineStr">
@@ -7371,7 +7371,7 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E71" s="21" t="n">
+      <c r="E71" s="20" t="n">
         <v>2.34</v>
       </c>
       <c r="F71" s="17" t="inlineStr">
@@ -7382,7 +7382,7 @@
       <c r="G71" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="H71" s="21" t="inlineStr">
         <is>
           <t>601999</t>
         </is>
@@ -7402,28 +7402,28 @@
           <t>东北振兴、在线教育、基金减仓、知识产权</t>
         </is>
       </c>
-      <c r="L71" s="21" t="n">
+      <c r="L71" s="20" t="n">
         <v>7.8</v>
       </c>
-      <c r="M71" s="23" t="n">
+      <c r="M71" s="22" t="n">
         <v>10.01</v>
       </c>
-      <c r="N71" s="23" t="n">
+      <c r="N71" s="22" t="n">
         <v>6.7</v>
       </c>
-      <c r="O71" s="21" t="n">
+      <c r="O71" s="20" t="n">
         <v>3.24</v>
       </c>
-      <c r="P71" s="21" t="n">
+      <c r="P71" s="20" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q71" s="21" t="n">
+      <c r="Q71" s="20" t="n">
         <v>1.23</v>
       </c>
-      <c r="R71" s="21" t="n">
+      <c r="R71" s="20" t="n">
         <v>-7.14</v>
       </c>
-      <c r="S71" s="21" t="n">
+      <c r="S71" s="20" t="n">
         <v>44.44</v>
       </c>
       <c r="T71" s="5" t="inlineStr">
@@ -7451,7 +7451,7 @@
           <t>知识产权</t>
         </is>
       </c>
-      <c r="E72" s="21" t="n">
+      <c r="E72" s="20" t="n">
         <v>2.34</v>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -7462,7 +7462,7 @@
       <c r="G72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="22" t="inlineStr">
+      <c r="H72" s="21" t="inlineStr">
         <is>
           <t>603721</t>
         </is>
@@ -7482,28 +7482,28 @@
           <t>AI语料、体育产业、影视概念、数字水印、文娱消费、旅游概念、知识产权、网红经济、职业教育、虚拟现实、超清视频、小红书概念、短剧互动游戏</t>
         </is>
       </c>
-      <c r="L72" s="21" t="n">
+      <c r="L72" s="20" t="n">
         <v>20.82</v>
       </c>
-      <c r="M72" s="23" t="n">
+      <c r="M72" s="22" t="n">
         <v>9.98</v>
       </c>
-      <c r="N72" s="23" t="n">
+      <c r="N72" s="22" t="n">
         <v>3.22</v>
       </c>
-      <c r="O72" s="21" t="n">
+      <c r="O72" s="20" t="n">
         <v>9.44</v>
       </c>
-      <c r="P72" s="21" t="n">
+      <c r="P72" s="20" t="n">
         <v>1.37</v>
       </c>
-      <c r="Q72" s="21" t="n">
+      <c r="Q72" s="20" t="n">
         <v>1.18</v>
       </c>
-      <c r="R72" s="21" t="n">
+      <c r="R72" s="20" t="n">
         <v>-19.49</v>
       </c>
-      <c r="S72" s="21" t="n">
+      <c r="S72" s="20" t="n">
         <v>44.58</v>
       </c>
       <c r="T72" s="5" t="inlineStr">
@@ -7648,7 +7648,7 @@
       <c r="M74" s="19" t="n">
         <v>2.9</v>
       </c>
-      <c r="N74" s="20" t="n">
+      <c r="N74" s="23" t="n">
         <v>-0.93</v>
       </c>
       <c r="O74" s="16" t="n">
@@ -8125,7 +8125,7 @@
       <c r="L80" s="16" t="n">
         <v>11.75</v>
       </c>
-      <c r="M80" s="20" t="n">
+      <c r="M80" s="23" t="n">
         <v>-6.52</v>
       </c>
       <c r="N80" s="19" t="n">
@@ -8571,7 +8571,7 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E86" s="21" t="n">
+      <c r="E86" s="20" t="n">
         <v>4.02</v>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -8582,7 +8582,7 @@
       <c r="G86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H86" s="22" t="inlineStr">
+      <c r="H86" s="21" t="inlineStr">
         <is>
           <t>603068</t>
         </is>
@@ -8602,28 +8602,28 @@
           <t>ETC、无人机、物联网、AI眼镜、WiFi、华为概念、卫星导航、国产芯片、小米概念、无线耳机、汽车芯片、算力概念、通信技术、阿里概念、半导体概念、消费电子概念</t>
         </is>
       </c>
-      <c r="L86" s="21" t="n">
+      <c r="L86" s="20" t="n">
         <v>41.67</v>
       </c>
-      <c r="M86" s="23" t="n">
+      <c r="M86" s="22" t="n">
         <v>10.01</v>
       </c>
-      <c r="N86" s="23" t="n">
+      <c r="N86" s="22" t="n">
         <v>1.51</v>
       </c>
-      <c r="O86" s="21" t="n">
+      <c r="O86" s="20" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="P86" s="21" t="n">
+      <c r="P86" s="20" t="n">
         <v>0.83</v>
       </c>
-      <c r="Q86" s="21" t="n">
+      <c r="Q86" s="20" t="n">
         <v>0.83</v>
       </c>
-      <c r="R86" s="21" t="n">
+      <c r="R86" s="20" t="n">
         <v>-14.1</v>
       </c>
-      <c r="S86" s="21" t="n">
+      <c r="S86" s="20" t="n">
         <v>37.52</v>
       </c>
       <c r="T86" s="5" t="inlineStr">
@@ -8651,7 +8651,7 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E87" s="21" t="n">
+      <c r="E87" s="20" t="n">
         <v>4.02</v>
       </c>
       <c r="F87" s="17" t="inlineStr">
@@ -8662,7 +8662,7 @@
       <c r="G87" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H87" s="22" t="inlineStr">
+      <c r="H87" s="21" t="inlineStr">
         <is>
           <t>001388</t>
         </is>
@@ -8682,28 +8682,28 @@
           <t>PCB、物联网、特高压、5G概念、WiFi、国产软件、基金减仓、智能电网、机器视觉、激光雷达、算力概念、通信技术、多模态AI、工业互联网、新型工业化、电子身份证、中俄贸易概念</t>
         </is>
       </c>
-      <c r="L87" s="21" t="n">
+      <c r="L87" s="20" t="n">
         <v>20.37</v>
       </c>
-      <c r="M87" s="23" t="n">
+      <c r="M87" s="22" t="n">
         <v>9.99</v>
       </c>
-      <c r="N87" s="23" t="n">
+      <c r="N87" s="22" t="n">
         <v>3.56</v>
       </c>
-      <c r="O87" s="21" t="n">
+      <c r="O87" s="20" t="n">
         <v>8.44</v>
       </c>
-      <c r="P87" s="21" t="n">
+      <c r="P87" s="20" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q87" s="21" t="n">
+      <c r="Q87" s="20" t="n">
         <v>0.97</v>
       </c>
-      <c r="R87" s="21" t="n">
+      <c r="R87" s="20" t="n">
         <v>-36.9</v>
       </c>
-      <c r="S87" s="21" t="n">
+      <c r="S87" s="20" t="n">
         <v>19.75</v>
       </c>
       <c r="T87" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
           <t>WiFi</t>
         </is>
       </c>
-      <c r="E88" s="21" t="n">
+      <c r="E88" s="20" t="n">
         <v>4.02</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -8742,7 +8742,7 @@
       <c r="G88" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H88" s="22" t="inlineStr">
+      <c r="H88" s="21" t="inlineStr">
         <is>
           <t>002792</t>
         </is>
@@ -8762,28 +8762,28 @@
           <t>5G概念、6G概念、WiFi、低空经济、储能概念、卫星导航、商业航天、通信技术、F5G概念、UWB概念、光通信模块、卫星互联网、毫米波概念、中俄贸易概念</t>
         </is>
       </c>
-      <c r="L88" s="21" t="n">
+      <c r="L88" s="20" t="n">
         <v>29.17</v>
       </c>
-      <c r="M88" s="23" t="n">
+      <c r="M88" s="22" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="N88" s="23" t="n">
+      <c r="N88" s="22" t="n">
         <v>6.3</v>
       </c>
-      <c r="O88" s="21" t="n">
+      <c r="O88" s="20" t="n">
         <v>12.75</v>
       </c>
-      <c r="P88" s="21" t="n">
+      <c r="P88" s="20" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q88" s="21" t="n">
+      <c r="Q88" s="20" t="n">
         <v>0.79</v>
       </c>
-      <c r="R88" s="21" t="n">
+      <c r="R88" s="20" t="n">
         <v>-58.3</v>
       </c>
-      <c r="S88" s="21" t="n">
+      <c r="S88" s="20" t="n">
         <v>70.78</v>
       </c>
       <c r="T88" s="5" t="inlineStr">
@@ -8848,7 +8848,7 @@
       <c r="M89" s="19" t="n">
         <v>0.57</v>
       </c>
-      <c r="N89" s="20" t="n">
+      <c r="N89" s="23" t="n">
         <v>-3.7</v>
       </c>
       <c r="O89" s="16" t="n">
@@ -8925,10 +8925,10 @@
       <c r="L90" s="16" t="n">
         <v>15.63</v>
       </c>
-      <c r="M90" s="20" t="n">
+      <c r="M90" s="23" t="n">
         <v>-0.13</v>
       </c>
-      <c r="N90" s="20" t="n">
+      <c r="N90" s="23" t="n">
         <v>-3.28</v>
       </c>
       <c r="O90" s="16" t="n">
@@ -8971,7 +8971,7 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E91" s="21" t="n">
+      <c r="E91" s="20" t="n">
         <v>3.86</v>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -8982,7 +8982,7 @@
       <c r="G91" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H91" s="22" t="inlineStr">
+      <c r="H91" s="21" t="inlineStr">
         <is>
           <t>603893</t>
         </is>
@@ -9002,28 +9002,28 @@
           <t>物联网、AI眼镜、AI芯片、华为概念、国产芯片、大盘成长、百度概念、虚拟现实、高市净率、EDR概念、半导体概念</t>
         </is>
       </c>
-      <c r="L91" s="21" t="n">
+      <c r="L91" s="20" t="n">
         <v>189.04</v>
       </c>
-      <c r="M91" s="23" t="n">
+      <c r="M91" s="22" t="n">
         <v>10</v>
       </c>
       <c r="N91" s="24" t="n">
         <v>-3.84</v>
       </c>
-      <c r="O91" s="21" t="n">
+      <c r="O91" s="20" t="n">
         <v>4.96</v>
       </c>
-      <c r="P91" s="21" t="n">
+      <c r="P91" s="20" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q91" s="21" t="n">
+      <c r="Q91" s="20" t="n">
         <v>1.17</v>
       </c>
-      <c r="R91" s="21" t="n">
+      <c r="R91" s="20" t="n">
         <v>-16.96</v>
       </c>
-      <c r="S91" s="21" t="n">
+      <c r="S91" s="20" t="n">
         <v>30.62</v>
       </c>
       <c r="T91" s="5" t="inlineStr">
@@ -9051,7 +9051,7 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E92" s="21" t="n">
+      <c r="E92" s="20" t="n">
         <v>3.86</v>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -9062,7 +9062,7 @@
       <c r="G92" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H92" s="22" t="inlineStr">
+      <c r="H92" s="21" t="inlineStr">
         <is>
           <t>002195</t>
         </is>
@@ -9082,28 +9082,28 @@
           <t>大数据、AIPC、AI芯片、AI语料、中盘成长、华为概念、国产软件、百度概念、网络安全、网络游戏、股权分散、脑机接口、长江三角、阿里概念、首发经济、鸿蒙概念、互联网服务、互联网金融、多模态AI、AIGC概念、短剧互动游戏、AI制药（医疗）、抖音概念(字节概念)</t>
         </is>
       </c>
-      <c r="L92" s="21" t="n">
+      <c r="L92" s="20" t="n">
         <v>5.88</v>
       </c>
-      <c r="M92" s="23" t="n">
+      <c r="M92" s="22" t="n">
         <v>2.62</v>
       </c>
       <c r="N92" s="24" t="n">
         <v>-2.49</v>
       </c>
-      <c r="O92" s="21" t="n">
+      <c r="O92" s="20" t="n">
         <v>1.79</v>
       </c>
-      <c r="P92" s="21" t="n">
+      <c r="P92" s="20" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q92" s="21" t="n">
+      <c r="Q92" s="20" t="n">
         <v>1.12</v>
       </c>
-      <c r="R92" s="21" t="n">
+      <c r="R92" s="20" t="n">
         <v>-55.42</v>
       </c>
-      <c r="S92" s="21" t="n">
+      <c r="S92" s="20" t="n">
         <v>2.8</v>
       </c>
       <c r="T92" s="5" t="inlineStr">
@@ -9131,7 +9131,7 @@
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="E93" s="21" t="n">
+      <c r="E93" s="20" t="n">
         <v>3.86</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
@@ -9142,7 +9142,7 @@
       <c r="G93" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H93" s="22" t="inlineStr">
+      <c r="H93" s="21" t="inlineStr">
         <is>
           <t>002049</t>
         </is>
@@ -9162,28 +9162,28 @@
           <t>军工、ETC、大飞机、碳化硅、蓝宝石、5G概念、AI芯片、商业航天、国产芯片、存储芯片、汽车芯片、算力概念、通信技术、半导体概念、卫星互联网、高带宽内存、IGBT概念、车联网(车路云)</t>
         </is>
       </c>
-      <c r="L93" s="21" t="n">
+      <c r="L93" s="20" t="n">
         <v>53.97</v>
       </c>
-      <c r="M93" s="23" t="n">
+      <c r="M93" s="22" t="n">
         <v>2.6</v>
       </c>
       <c r="N93" s="24" t="n">
         <v>-2.55</v>
       </c>
-      <c r="O93" s="21" t="n">
+      <c r="O93" s="20" t="n">
         <v>1.24</v>
       </c>
-      <c r="P93" s="21" t="n">
+      <c r="P93" s="20" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q93" s="21" t="n">
+      <c r="Q93" s="20" t="n">
         <v>1.03</v>
       </c>
-      <c r="R93" s="21" t="n">
+      <c r="R93" s="20" t="n">
         <v>-41.64</v>
       </c>
-      <c r="S93" s="21" t="n">
+      <c r="S93" s="20" t="n">
         <v>3.49</v>
       </c>
       <c r="T93" s="5" t="inlineStr">
@@ -9485,7 +9485,7 @@
       <c r="L97" s="16" t="n">
         <v>28.18</v>
       </c>
-      <c r="M97" s="20" t="n">
+      <c r="M97" s="23" t="n">
         <v>-1.88</v>
       </c>
       <c r="N97" s="19" t="n">
@@ -9885,7 +9885,7 @@
       <c r="L102" s="16" t="n">
         <v>15.77</v>
       </c>
-      <c r="M102" s="20" t="n">
+      <c r="M102" s="23" t="n">
         <v>-0.88</v>
       </c>
       <c r="N102" s="19" t="n">

--- a/data/theme_strength_latest.xlsx
+++ b/data/theme_strength_latest.xlsx
@@ -650,7 +650,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>截至 2026-10-27  2026-10-27 14:55｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：成分股等权还原（东财板块日线不完整）</t>
+          <t>截至 2026-10-27  2026-10-27 18:10｜每天单独取同类型已合并的题材涨幅前五；日期按降序排列，连续天数截至最新交易日｜板块数据：成分股等权还原（东财板块日线不完整）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4.5</v>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>4</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>1.5</v>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="L8" s="14" t="n">
         <v>1</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr"/>
       <c r="F9" s="16" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>2</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="L9" s="17" t="n">
         <v>2</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>3</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="L10" s="14" t="n">
         <v>3</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="E11" s="16" t="inlineStr"/>
       <c r="F11" s="16" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>5</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="L11" s="17" t="n">
         <v>5</v>
@@ -2013,7 +2013,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="E4" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
         <v>10.51</v>
       </c>
       <c r="O4" s="19" t="n">
-        <v>6.81</v>
+        <v>6.79</v>
       </c>
       <c r="P4" s="19" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="Q4" s="19" t="n">
         <v>1.34</v>
@@ -2086,14 +2086,14 @@
       </c>
       <c r="T4" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
@@ -2141,39 +2141,39 @@
         </is>
       </c>
       <c r="L5" s="19" t="n">
-        <v>29.93</v>
+        <v>29.9</v>
       </c>
       <c r="M5" s="22" t="n">
-        <v>9.390000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N5" s="22" t="n">
-        <v>9.07</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="Q5" s="19" t="n">
         <v>1.6</v>
       </c>
       <c r="R5" s="19" t="n">
-        <v>-25.04</v>
+        <v>-25.12</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>26.77</v>
+        <v>26.64</v>
       </c>
       <c r="T5" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="E6" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
@@ -2221,39 +2221,39 @@
         </is>
       </c>
       <c r="L6" s="19" t="n">
-        <v>30.13</v>
+        <v>30.17</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>5.94</v>
+        <v>6.08</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="O6" s="19" t="n">
-        <v>15.01</v>
+        <v>15.15</v>
       </c>
       <c r="P6" s="19" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="Q6" s="19" t="n">
         <v>2.96</v>
       </c>
       <c r="R6" s="19" t="n">
-        <v>-25.68</v>
+        <v>-25.58</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>16.15</v>
+        <v>16.31</v>
       </c>
       <c r="T6" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
@@ -2301,39 +2301,39 @@
         </is>
       </c>
       <c r="L7" s="19" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="M7" s="22" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="N7" s="22" t="n">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>6.34</v>
+        <v>6.39</v>
       </c>
       <c r="P7" s="19" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="Q7" s="19" t="n">
         <v>1.65</v>
       </c>
       <c r="R7" s="19" t="n">
-        <v>-37.22</v>
+        <v>-37.34</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>18.22</v>
+        <v>17.99</v>
       </c>
       <c r="T7" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
@@ -2381,39 +2381,39 @@
         </is>
       </c>
       <c r="L8" s="19" t="n">
-        <v>30.13</v>
+        <v>30.17</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>5.94</v>
+        <v>6.08</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="O8" s="19" t="n">
-        <v>15.01</v>
+        <v>15.15</v>
       </c>
       <c r="P8" s="19" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="Q8" s="19" t="n">
         <v>2.96</v>
       </c>
       <c r="R8" s="19" t="n">
-        <v>-25.68</v>
+        <v>-25.58</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>16.15</v>
+        <v>16.31</v>
       </c>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         <v>10.51</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>6.81</v>
+        <v>6.79</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="Q9" s="19" t="n">
         <v>1.34</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="T9" s="12" t="inlineStr">
         <is>
-          <t>轮毂电机 +2.48%</t>
+          <t>轮毂电机 +2.43%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>10.64</v>
       </c>
       <c r="O10" s="24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P10" s="24" t="n">
         <v>1.26</v>
@@ -2566,14 +2566,14 @@
       </c>
       <c r="T10" s="15" t="inlineStr">
         <is>
-          <t>退税商店 +1.05%</t>
+          <t>退税商店 +0.99%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         <v>12.33</v>
       </c>
       <c r="O11" s="24" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="P11" s="24" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="Q11" s="24" t="n">
         <v>1.46</v>
@@ -2646,14 +2646,14 @@
       </c>
       <c r="T11" s="15" t="inlineStr">
         <is>
-          <t>退税商店 +1.05%</t>
+          <t>退税商店 +0.99%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="T12" s="15" t="inlineStr">
         <is>
-          <t>退税商店 +1.05%</t>
+          <t>退税商店 +0.99%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
@@ -2781,39 +2781,39 @@
         </is>
       </c>
       <c r="L13" s="19" t="n">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="M13" s="22" t="n">
-        <v>5.57</v>
+        <v>5.39</v>
       </c>
       <c r="N13" s="22" t="n">
-        <v>4.01</v>
+        <v>3.83</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R13" s="19" t="n">
-        <v>-40.54</v>
+        <v>-40.64</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>15.14</v>
+        <v>14.95</v>
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>大盘价值 +0.27%</t>
+          <t>大盘价值 +0.13%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="E14" s="19" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
@@ -2842,58 +2842,58 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>601825</t>
+          <t>002379</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>沪农商行</t>
+          <t>宏桥控股</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>银行Ⅱ</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>低市净率、大盘价值</t>
+          <t>大盘价值、股权集中</t>
         </is>
       </c>
       <c r="L14" s="19" t="n">
-        <v>9.19</v>
+        <v>14.55</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>4.91</v>
+        <v>4.45</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>6.37</v>
+        <v>1.75</v>
       </c>
       <c r="O14" s="19" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.53</v>
       </c>
       <c r="P14" s="19" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" s="19" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="R14" s="19" t="n">
-        <v>0</v>
+        <v>-54.93</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>26.93</v>
+        <v>6.05</v>
       </c>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>大盘价值 +0.27%</t>
+          <t>大盘价值 +0.13%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
@@ -2922,58 +2922,58 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>002379</t>
+          <t>000708</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>宏桥控股</t>
+          <t>中信特钢</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>特钢Ⅱ</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>大盘价值、股权集中</t>
+          <t>地下管网、大盘价值、社保新进、股权集中、行业龙头</t>
         </is>
       </c>
       <c r="L15" s="19" t="n">
-        <v>14.6</v>
+        <v>12.09</v>
       </c>
       <c r="M15" s="22" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="N15" s="22" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
+      </c>
+      <c r="N15" s="27" t="n">
+        <v>-8.48</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>3.51</v>
+        <v>0.62</v>
       </c>
       <c r="P15" s="19" t="n">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>0.99</v>
+        <v>1.61</v>
       </c>
       <c r="R15" s="19" t="n">
-        <v>-54.77</v>
+        <v>-30.44</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>6.41</v>
+        <v>4.4</v>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>大盘价值 +0.27%</t>
+          <t>大盘价值 +0.13%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         <v>12.33</v>
       </c>
       <c r="O16" s="19" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="P16" s="19" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="Q16" s="19" t="n">
         <v>1.46</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="T16" s="12" t="inlineStr">
         <is>
-          <t>免税概念 -0.15%</t>
+          <t>免税概念 -0.26%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="E17" s="19" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
@@ -3082,58 +3082,58 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>600029</t>
+          <t>600694</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>南方航空</t>
+          <t>大商股份</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>航空机场</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>免税概念、大盘成长、零售概念</t>
+          <t>东北振兴、低市净率、免税概念、内贸流通、社保新进、零售概念</t>
         </is>
       </c>
       <c r="L17" s="19" t="n">
-        <v>4.81</v>
+        <v>15.15</v>
       </c>
       <c r="M17" s="22" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="N17" s="22" t="n">
-        <v>2.78</v>
+        <v>3.84</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>0.42</v>
+        <v>1.51</v>
       </c>
       <c r="P17" s="19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q17" s="19" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q17" s="19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="R17" s="19" t="n">
-        <v>-41.98</v>
+        <v>-12.53</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>3</v>
+        <v>14.51</v>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>免税概念 -0.15%</t>
+          <t>免税概念 -0.26%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="E18" s="19" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
@@ -3162,58 +3162,58 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>600694</t>
+          <t>600029</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>大商股份</t>
+          <t>南方航空</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>航空机场</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>东北振兴、低市净率、免税概念、内贸流通、社保新进、零售概念</t>
+          <t>免税概念、大盘成长、零售概念</t>
         </is>
       </c>
       <c r="L18" s="19" t="n">
-        <v>15.16</v>
+        <v>4.8</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>3.91</v>
+        <v>2.56</v>
       </c>
       <c r="O18" s="19" t="n">
-        <v>1.44</v>
+        <v>0.43</v>
       </c>
       <c r="P18" s="19" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>-12.47</v>
+        <v>-42.1</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>14.59</v>
+        <v>2.78</v>
       </c>
       <c r="T18" s="12" t="inlineStr">
         <is>
-          <t>免税概念 -0.15%</t>
+          <t>免税概念 -0.26%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="E19" s="19" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
@@ -3270,10 +3270,10 @@
         <v>8.359999999999999</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>12.18</v>
+        <v>12.08</v>
       </c>
       <c r="P19" s="19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q19" s="19" t="n">
         <v>1.27</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>汽车整车 -0.39%</t>
+          <t>汽车整车 -0.47%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E20" s="19" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
@@ -3341,39 +3341,39 @@
         </is>
       </c>
       <c r="L20" s="19" t="n">
-        <v>20.8</v>
+        <v>20.84</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="O20" s="19" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P20" s="19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" s="19" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="R20" s="19" t="n">
-        <v>-19.75</v>
+        <v>-19.6</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>31.4</v>
+        <v>31.65</v>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>汽车整车 -0.39%</t>
+          <t>汽车整车 -0.47%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>10-27午盘</t>
+          <t>10-27收盘</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="E21" s="19" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         <v>0.28</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="Q21" s="19" t="n">
         <v>0.8100000000000001</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>汽车整车 -0.39%</t>
+          <t>汽车整车 -0.47%</t>
         </is>
       </c>
     </row>
